--- a/public/data/Russian_Words_Cards.xlsx
+++ b/public/data/Russian_Words_Cards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CB510C-69C4-4851-8A80-D7D86685948C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504CA6E8-B8A4-4777-A327-DEFDB64A4647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="1727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="1722">
   <si>
     <t>Topic</t>
   </si>
@@ -3506,9 +3506,6 @@
     <t>לאטה</t>
   </si>
   <si>
-    <t>אין כמו לשתות קפה לאטה חם ולהתחמם כאילו לֵטַה</t>
-  </si>
-  <si>
     <t>весна</t>
   </si>
   <si>
@@ -3531,12 +3528,6 @@
   </si>
   <si>
     <t>סתיו</t>
-  </si>
-  <si>
-    <t>Ocean</t>
-  </si>
-  <si>
-    <t>האוֹסֵן מגיע כמו ה ocean (אוקיינוס). הוא רגוע ושליו, אבל כולם יודעים שהחורף הסוער מעבר לפינה.</t>
   </si>
   <si>
     <t>зима</t>
@@ -5099,12 +5090,6 @@
   </si>
   <si>
     <t>❄️</t>
-  </si>
-  <si>
-    <t>🌸</t>
-  </si>
-  <si>
-    <t>🍂</t>
   </si>
   <si>
     <t>⛄</t>
@@ -5528,7 +5513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -5548,7 +5533,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5851,7 +5835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L298"/>
+  <dimension ref="A1:L294"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -5868,27 +5852,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1658</v>
+        <v>1653</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>1410</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>1413</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -5900,7 +5884,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
@@ -5911,7 +5895,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -5923,7 +5907,7 @@
         <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>24</v>
@@ -5934,7 +5918,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -5946,18 +5930,18 @@
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -5969,18 +5953,18 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1686</v>
+        <v>1681</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1687</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -5992,18 +5976,18 @@
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1710</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B7" t="s">
         <v>37</v>
@@ -6015,30 +5999,30 @@
         <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1676</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1681</v>
+        <v>1676</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>43</v>
@@ -6049,30 +6033,30 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B9" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1678</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
@@ -6084,7 +6068,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>50</v>
@@ -6095,7 +6079,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B11" t="s">
         <v>52</v>
@@ -6107,41 +6091,41 @@
         <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1689</v>
+        <v>1684</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1688</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B12" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1682</v>
+        <v>1677</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B13" t="s">
         <v>58</v>
@@ -6153,18 +6137,18 @@
         <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1684</v>
+        <v>1679</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1685</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B14" t="s">
         <v>61</v>
@@ -6176,7 +6160,7 @@
         <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>64</v>
@@ -6187,7 +6171,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B15" t="s">
         <v>66</v>
@@ -6199,7 +6183,7 @@
         <v>68</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
@@ -6210,7 +6194,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
@@ -6222,7 +6206,7 @@
         <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>74</v>
@@ -6233,7 +6217,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B17" t="s">
         <v>76</v>
@@ -6245,7 +6229,7 @@
         <v>78</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
@@ -6256,7 +6240,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B18" t="s">
         <v>81</v>
@@ -6268,7 +6252,7 @@
         <v>83</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -6279,7 +6263,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B19" t="s">
         <v>86</v>
@@ -6291,7 +6275,7 @@
         <v>88</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
@@ -6302,7 +6286,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B20" t="s">
         <v>91</v>
@@ -6314,7 +6298,7 @@
         <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>94</v>
@@ -6325,7 +6309,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B21" t="s">
         <v>96</v>
@@ -6337,18 +6321,18 @@
         <v>98</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>99</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1671</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B22" t="s">
         <v>100</v>
@@ -6360,7 +6344,7 @@
         <v>102</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>103</v>
@@ -6371,30 +6355,30 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B23" t="s">
         <v>105</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>107</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B24" t="s">
         <v>108</v>
@@ -6406,7 +6390,7 @@
         <v>110</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>111</v>
@@ -6417,7 +6401,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B25" t="s">
         <v>113</v>
@@ -6429,7 +6413,7 @@
         <v>115</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>116</v>
@@ -6440,7 +6424,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B26" t="s">
         <v>118</v>
@@ -6452,7 +6436,7 @@
         <v>120</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>121</v>
@@ -6463,7 +6447,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B27" t="s">
         <v>123</v>
@@ -6475,7 +6459,7 @@
         <v>125</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>126</v>
@@ -6486,7 +6470,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B28" t="s">
         <v>128</v>
@@ -6498,7 +6482,7 @@
         <v>130</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>131</v>
@@ -6509,7 +6493,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B29" t="s">
         <v>133</v>
@@ -6521,7 +6505,7 @@
         <v>135</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>136</v>
@@ -6532,7 +6516,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B30" t="s">
         <v>138</v>
@@ -6544,7 +6528,7 @@
         <v>140</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>141</v>
@@ -6555,7 +6539,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B31" t="s">
         <v>143</v>
@@ -6567,7 +6551,7 @@
         <v>145</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>146</v>
@@ -6578,7 +6562,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B32" t="s">
         <v>148</v>
@@ -6590,18 +6574,18 @@
         <v>150</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>151</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1670</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B33" t="s">
         <v>152</v>
@@ -6613,7 +6597,7 @@
         <v>154</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>155</v>
@@ -6624,7 +6608,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B34" t="s">
         <v>157</v>
@@ -6636,7 +6620,7 @@
         <v>159</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>160</v>
@@ -6647,7 +6631,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B35" t="s">
         <v>162</v>
@@ -6659,7 +6643,7 @@
         <v>164</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>165</v>
@@ -6670,7 +6654,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B36" t="s">
         <v>167</v>
@@ -6682,7 +6666,7 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>169</v>
@@ -6693,7 +6677,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B37" t="s">
         <v>171</v>
@@ -6705,7 +6689,7 @@
         <v>173</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>174</v>
@@ -6716,7 +6700,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B38" t="s">
         <v>176</v>
@@ -6728,7 +6712,7 @@
         <v>178</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
@@ -6739,7 +6723,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B39" t="s">
         <v>180</v>
@@ -6751,7 +6735,7 @@
         <v>182</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>183</v>
@@ -6762,7 +6746,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B40" t="s">
         <v>185</v>
@@ -6774,7 +6758,7 @@
         <v>187</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>188</v>
@@ -6785,7 +6769,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B41" t="s">
         <v>190</v>
@@ -6797,7 +6781,7 @@
         <v>192</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>193</v>
@@ -6808,7 +6792,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B42" t="s">
         <v>195</v>
@@ -6820,7 +6804,7 @@
         <v>197</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>198</v>
@@ -6831,7 +6815,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B43" t="s">
         <v>200</v>
@@ -6843,7 +6827,7 @@
         <v>202</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>203</v>
@@ -6854,7 +6838,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B44" t="s">
         <v>205</v>
@@ -6866,7 +6850,7 @@
         <v>207</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>208</v>
@@ -6877,7 +6861,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B45" t="s">
         <v>210</v>
@@ -6889,18 +6873,18 @@
         <v>212</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1659</v>
+        <v>1654</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>213</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1669</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B46" t="s">
         <v>214</v>
@@ -6912,7 +6896,7 @@
         <v>216</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>217</v>
@@ -6923,7 +6907,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B47" t="s">
         <v>219</v>
@@ -6935,7 +6919,7 @@
         <v>221</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1660</v>
+        <v>1655</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>222</v>
@@ -6946,7 +6930,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B48" t="s">
         <v>224</v>
@@ -6958,7 +6942,7 @@
         <v>226</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>227</v>
@@ -6969,7 +6953,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B49" t="s">
         <v>229</v>
@@ -6981,7 +6965,7 @@
         <v>231</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>232</v>
@@ -6992,7 +6976,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B50" t="s">
         <v>234</v>
@@ -7004,7 +6988,7 @@
         <v>236</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>237</v>
@@ -7015,7 +6999,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B51" t="s">
         <v>239</v>
@@ -7027,7 +7011,7 @@
         <v>241</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>242</v>
@@ -7038,7 +7022,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B52" t="s">
         <v>244</v>
@@ -7050,7 +7034,7 @@
         <v>246</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>247</v>
@@ -7061,7 +7045,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B53" t="s">
         <v>249</v>
@@ -7073,18 +7057,18 @@
         <v>251</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1673</v>
+        <v>1668</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1672</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B54" t="s">
         <v>252</v>
@@ -7096,18 +7080,18 @@
         <v>254</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>255</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B55" t="s">
         <v>256</v>
@@ -7119,7 +7103,7 @@
         <v>258</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>259</v>
@@ -7130,7 +7114,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B56" t="s">
         <v>261</v>
@@ -7142,7 +7126,7 @@
         <v>263</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>264</v>
@@ -7153,7 +7137,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B57" t="s">
         <v>266</v>
@@ -7165,7 +7149,7 @@
         <v>268</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>269</v>
@@ -7176,7 +7160,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B58" t="s">
         <v>271</v>
@@ -7188,7 +7172,7 @@
         <v>273</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>274</v>
@@ -7199,7 +7183,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B59" t="s">
         <v>276</v>
@@ -7211,7 +7195,7 @@
         <v>278</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>279</v>
@@ -7222,7 +7206,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B60" t="s">
         <v>281</v>
@@ -7234,7 +7218,7 @@
         <v>283</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>284</v>
@@ -7245,7 +7229,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B61" t="s">
         <v>286</v>
@@ -7257,7 +7241,7 @@
         <v>288</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>289</v>
@@ -7268,7 +7252,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B62" t="s">
         <v>291</v>
@@ -7280,7 +7264,7 @@
         <v>293</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>294</v>
@@ -7291,7 +7275,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B63" t="s">
         <v>296</v>
@@ -7300,10 +7284,10 @@
         <v>297</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>298</v>
@@ -7314,7 +7298,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B64" t="s">
         <v>300</v>
@@ -7326,7 +7310,7 @@
         <v>302</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>2</v>
@@ -7337,7 +7321,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B65" t="s">
         <v>304</v>
@@ -7349,7 +7333,7 @@
         <v>306</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>307</v>
@@ -7360,7 +7344,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B66" t="s">
         <v>309</v>
@@ -7372,7 +7356,7 @@
         <v>311</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>312</v>
@@ -7383,7 +7367,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B67" t="s">
         <v>314</v>
@@ -7395,7 +7379,7 @@
         <v>316</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>317</v>
@@ -7406,7 +7390,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B68" t="s">
         <v>319</v>
@@ -7418,18 +7402,18 @@
         <v>321</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>322</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B69" t="s">
         <v>323</v>
@@ -7441,7 +7425,7 @@
         <v>325</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>326</v>
@@ -7452,7 +7436,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B70" t="s">
         <v>328</v>
@@ -7464,7 +7448,7 @@
         <v>330</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>331</v>
@@ -7475,7 +7459,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B71" t="s">
         <v>333</v>
@@ -7487,7 +7471,7 @@
         <v>335</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1661</v>
+        <v>1656</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>336</v>
@@ -7498,7 +7482,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B72" t="s">
         <v>338</v>
@@ -7510,7 +7494,7 @@
         <v>340</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>341</v>
@@ -7521,7 +7505,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B73" t="s">
         <v>343</v>
@@ -7533,7 +7517,7 @@
         <v>345</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>346</v>
@@ -7544,7 +7528,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B74" t="s">
         <v>348</v>
@@ -7556,7 +7540,7 @@
         <v>350</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>351</v>
@@ -7567,7 +7551,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B75" t="s">
         <v>353</v>
@@ -7579,18 +7563,18 @@
         <v>355</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>356</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1690</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B76" t="s">
         <v>357</v>
@@ -7602,7 +7586,7 @@
         <v>359</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>360</v>
@@ -7613,7 +7597,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B77" t="s">
         <v>362</v>
@@ -7625,7 +7609,7 @@
         <v>364</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>365</v>
@@ -7636,7 +7620,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B78" t="s">
         <v>367</v>
@@ -7648,7 +7632,7 @@
         <v>369</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>370</v>
@@ -7659,30 +7643,30 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B79" t="s">
         <v>372</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1691</v>
+        <v>1686</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>373</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>374</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1692</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B80" t="s">
         <v>375</v>
@@ -7694,7 +7678,7 @@
         <v>377</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>378</v>
@@ -7705,7 +7689,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B81" t="s">
         <v>380</v>
@@ -7717,18 +7701,18 @@
         <v>382</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>383</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1693</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B82" t="s">
         <v>384</v>
@@ -7740,7 +7724,7 @@
         <v>386</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>387</v>
@@ -7751,7 +7735,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B83" t="s">
         <v>389</v>
@@ -7763,7 +7747,7 @@
         <v>391</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>392</v>
@@ -7774,7 +7758,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B84" t="s">
         <v>394</v>
@@ -7786,7 +7770,7 @@
         <v>396</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>1</v>
@@ -7797,7 +7781,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B85" t="s">
         <v>398</v>
@@ -7809,7 +7793,7 @@
         <v>400</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>401</v>
@@ -7820,7 +7804,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B86" t="s">
         <v>403</v>
@@ -7832,7 +7816,7 @@
         <v>405</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>406</v>
@@ -7843,7 +7827,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B87" t="s">
         <v>408</v>
@@ -7855,7 +7839,7 @@
         <v>410</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>411</v>
@@ -7866,7 +7850,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B88" t="s">
         <v>413</v>
@@ -7878,18 +7862,18 @@
         <v>415</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1662</v>
+        <v>1657</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>416</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1694</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B89" t="s">
         <v>417</v>
@@ -7901,7 +7885,7 @@
         <v>419</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>420</v>
@@ -7912,7 +7896,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B90" t="s">
         <v>422</v>
@@ -7924,7 +7908,7 @@
         <v>424</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>425</v>
@@ -7935,7 +7919,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B91" t="s">
         <v>427</v>
@@ -7947,18 +7931,18 @@
         <v>429</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>430</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1695</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B92" t="s">
         <v>431</v>
@@ -7970,7 +7954,7 @@
         <v>433</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>434</v>
@@ -7981,7 +7965,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B93" t="s">
         <v>436</v>
@@ -7993,7 +7977,7 @@
         <v>438</v>
       </c>
       <c r="E93" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>439</v>
@@ -8004,7 +7988,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B94" t="s">
         <v>441</v>
@@ -8016,7 +8000,7 @@
         <v>443</v>
       </c>
       <c r="E94" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>444</v>
@@ -8027,7 +8011,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B95" t="s">
         <v>446</v>
@@ -8039,7 +8023,7 @@
         <v>448</v>
       </c>
       <c r="E95" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>449</v>
@@ -8050,7 +8034,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B96" t="s">
         <v>451</v>
@@ -8062,7 +8046,7 @@
         <v>453</v>
       </c>
       <c r="E96" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>454</v>
@@ -8073,7 +8057,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B97" t="s">
         <v>456</v>
@@ -8085,7 +8069,7 @@
         <v>458</v>
       </c>
       <c r="E97" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>459</v>
@@ -8096,7 +8080,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B98" t="s">
         <v>461</v>
@@ -8108,7 +8092,7 @@
         <v>463</v>
       </c>
       <c r="E98" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>464</v>
@@ -8119,7 +8103,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B99" t="s">
         <v>466</v>
@@ -8131,7 +8115,7 @@
         <v>468</v>
       </c>
       <c r="E99" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>469</v>
@@ -8142,7 +8126,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B100" t="s">
         <v>503</v>
@@ -8154,7 +8138,7 @@
         <v>505</v>
       </c>
       <c r="E100" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>506</v>
@@ -8165,7 +8149,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B101" t="s">
         <v>471</v>
@@ -8177,7 +8161,7 @@
         <v>473</v>
       </c>
       <c r="E101" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>474</v>
@@ -8188,7 +8172,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B102" t="s">
         <v>476</v>
@@ -8200,18 +8184,18 @@
         <v>478</v>
       </c>
       <c r="E102" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>479</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1696</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B103" t="s">
         <v>480</v>
@@ -8223,7 +8207,7 @@
         <v>482</v>
       </c>
       <c r="E103" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>483</v>
@@ -8234,7 +8218,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B104" t="s">
         <v>485</v>
@@ -8246,7 +8230,7 @@
         <v>487</v>
       </c>
       <c r="E104" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>488</v>
@@ -8257,7 +8241,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B105" t="s">
         <v>490</v>
@@ -8269,18 +8253,18 @@
         <v>492</v>
       </c>
       <c r="E105" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>493</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B106" t="s">
         <v>494</v>
@@ -8292,7 +8276,7 @@
         <v>496</v>
       </c>
       <c r="E106" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>497</v>
@@ -8303,7 +8287,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B107" t="s">
         <v>499</v>
@@ -8315,18 +8299,18 @@
         <v>501</v>
       </c>
       <c r="E107" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>502</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1698</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B108" t="s">
         <v>508</v>
@@ -8338,10 +8322,10 @@
         <v>510</v>
       </c>
       <c r="E108" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>1699</v>
+        <v>1694</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>511</v>
@@ -8349,7 +8333,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B109" t="s">
         <v>512</v>
@@ -8361,7 +8345,7 @@
         <v>514</v>
       </c>
       <c r="E109" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>515</v>
@@ -8372,7 +8356,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B110" t="s">
         <v>517</v>
@@ -8384,7 +8368,7 @@
         <v>519</v>
       </c>
       <c r="E110" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>13</v>
@@ -8395,7 +8379,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B111" t="s">
         <v>521</v>
@@ -8407,7 +8391,7 @@
         <v>523</v>
       </c>
       <c r="E111" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>524</v>
@@ -8418,7 +8402,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B112" t="s">
         <v>526</v>
@@ -8430,7 +8414,7 @@
         <v>528</v>
       </c>
       <c r="E112" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>529</v>
@@ -8441,7 +8425,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B113" t="s">
         <v>531</v>
@@ -8453,7 +8437,7 @@
         <v>533</v>
       </c>
       <c r="E113" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>534</v>
@@ -8464,7 +8448,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B114" t="s">
         <v>536</v>
@@ -8476,7 +8460,7 @@
         <v>538</v>
       </c>
       <c r="E114" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>14</v>
@@ -8487,7 +8471,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B115" t="s">
         <v>540</v>
@@ -8499,18 +8483,18 @@
         <v>542</v>
       </c>
       <c r="E115" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1700</v>
+        <v>1695</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1701</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B116" t="s">
         <v>543</v>
@@ -8522,7 +8506,7 @@
         <v>545</v>
       </c>
       <c r="E116" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>283</v>
@@ -8533,7 +8517,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B117" t="s">
         <v>547</v>
@@ -8545,7 +8529,7 @@
         <v>549</v>
       </c>
       <c r="E117" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>550</v>
@@ -8556,7 +8540,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B118" t="s">
         <v>552</v>
@@ -8568,7 +8552,7 @@
         <v>554</v>
       </c>
       <c r="E118" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>555</v>
@@ -8579,7 +8563,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B119" t="s">
         <v>557</v>
@@ -8591,7 +8575,7 @@
         <v>559</v>
       </c>
       <c r="E119" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
@@ -8602,7 +8586,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B120" t="s">
         <v>561</v>
@@ -8614,7 +8598,7 @@
         <v>563</v>
       </c>
       <c r="E120" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>564</v>
@@ -8625,7 +8609,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B121" t="s">
         <v>566</v>
@@ -8637,7 +8621,7 @@
         <v>568</v>
       </c>
       <c r="E121" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>569</v>
@@ -8648,7 +8632,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B122" t="s">
         <v>571</v>
@@ -8660,7 +8644,7 @@
         <v>573</v>
       </c>
       <c r="E122" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>574</v>
@@ -8671,7 +8655,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B123" t="s">
         <v>576</v>
@@ -8683,7 +8667,7 @@
         <v>578</v>
       </c>
       <c r="E123" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>579</v>
@@ -8694,7 +8678,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B124" t="s">
         <v>581</v>
@@ -8706,7 +8690,7 @@
         <v>583</v>
       </c>
       <c r="E124" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>12</v>
@@ -8717,7 +8701,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B125" t="s">
         <v>585</v>
@@ -8729,18 +8713,18 @@
         <v>587</v>
       </c>
       <c r="E125" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>588</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1702</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B126" t="s">
         <v>589</v>
@@ -8752,7 +8736,7 @@
         <v>591</v>
       </c>
       <c r="E126" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>592</v>
@@ -8763,7 +8747,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B127" t="s">
         <v>594</v>
@@ -8775,7 +8759,7 @@
         <v>596</v>
       </c>
       <c r="E127" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>597</v>
@@ -8786,7 +8770,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B128" t="s">
         <v>599</v>
@@ -8798,7 +8782,7 @@
         <v>601</v>
       </c>
       <c r="E128" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>602</v>
@@ -8809,7 +8793,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B129" t="s">
         <v>604</v>
@@ -8821,7 +8805,7 @@
         <v>606</v>
       </c>
       <c r="E129" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>607</v>
@@ -8832,7 +8816,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B130" t="s">
         <v>609</v>
@@ -8844,7 +8828,7 @@
         <v>611</v>
       </c>
       <c r="E130" t="s">
-        <v>1667</v>
+        <v>1662</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>612</v>
@@ -8855,7 +8839,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B131" t="s">
         <v>614</v>
@@ -8867,7 +8851,7 @@
         <v>616</v>
       </c>
       <c r="E131" t="s">
-        <v>1668</v>
+        <v>1663</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>293</v>
@@ -8878,7 +8862,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B132" t="s">
         <v>618</v>
@@ -8890,7 +8874,7 @@
         <v>620</v>
       </c>
       <c r="E132" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>621</v>
@@ -8901,7 +8885,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B133" t="s">
         <v>623</v>
@@ -8913,7 +8897,7 @@
         <v>625</v>
       </c>
       <c r="E133" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>626</v>
@@ -8924,7 +8908,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B134" t="s">
         <v>628</v>
@@ -8936,7 +8920,7 @@
         <v>630</v>
       </c>
       <c r="E134" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>631</v>
@@ -8947,7 +8931,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B135" t="s">
         <v>633</v>
@@ -8959,7 +8943,7 @@
         <v>635</v>
       </c>
       <c r="E135" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>636</v>
@@ -8970,7 +8954,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B136" t="s">
         <v>638</v>
@@ -8982,7 +8966,7 @@
         <v>640</v>
       </c>
       <c r="E136" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>641</v>
@@ -8993,7 +8977,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B137" t="s">
         <v>643</v>
@@ -9005,7 +8989,7 @@
         <v>645</v>
       </c>
       <c r="E137" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>646</v>
@@ -9016,7 +9000,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B138" t="s">
         <v>648</v>
@@ -9028,7 +9012,7 @@
         <v>650</v>
       </c>
       <c r="E138" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>651</v>
@@ -9039,7 +9023,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B139" t="s">
         <v>653</v>
@@ -9051,7 +9035,7 @@
         <v>655</v>
       </c>
       <c r="E139" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>656</v>
@@ -9062,7 +9046,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B140" t="s">
         <v>658</v>
@@ -9074,18 +9058,18 @@
         <v>660</v>
       </c>
       <c r="E140" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>661</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1703</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B141" t="s">
         <v>662</v>
@@ -9097,7 +9081,7 @@
         <v>664</v>
       </c>
       <c r="E141" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>665</v>
@@ -9108,7 +9092,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B142" t="s">
         <v>667</v>
@@ -9120,18 +9104,18 @@
         <v>669</v>
       </c>
       <c r="E142" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>670</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B143" t="s">
         <v>671</v>
@@ -9143,18 +9127,18 @@
         <v>673</v>
       </c>
       <c r="E143" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>674</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1705</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B144" t="s">
         <v>675</v>
@@ -9166,7 +9150,7 @@
         <v>677</v>
       </c>
       <c r="E144" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>678</v>
@@ -9177,7 +9161,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B145" t="s">
         <v>680</v>
@@ -9189,7 +9173,7 @@
         <v>682</v>
       </c>
       <c r="E145" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>683</v>
@@ -9200,7 +9184,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B146" t="s">
         <v>685</v>
@@ -9212,7 +9196,7 @@
         <v>687</v>
       </c>
       <c r="E146" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>688</v>
@@ -9223,7 +9207,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B147" t="s">
         <v>690</v>
@@ -9235,7 +9219,7 @@
         <v>692</v>
       </c>
       <c r="E147" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>693</v>
@@ -9246,7 +9230,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B148" t="s">
         <v>695</v>
@@ -9258,18 +9242,18 @@
         <v>697</v>
       </c>
       <c r="E148" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>1706</v>
+        <v>1701</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1707</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B149" t="s">
         <v>698</v>
@@ -9281,7 +9265,7 @@
         <v>274</v>
       </c>
       <c r="E149" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>700</v>
@@ -9292,7 +9276,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B150" t="s">
         <v>702</v>
@@ -9304,7 +9288,7 @@
         <v>704</v>
       </c>
       <c r="E150" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>4</v>
@@ -9315,7 +9299,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B151" t="s">
         <v>706</v>
@@ -9327,7 +9311,7 @@
         <v>708</v>
       </c>
       <c r="E151" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>709</v>
@@ -9338,7 +9322,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B152" t="s">
         <v>711</v>
@@ -9350,7 +9334,7 @@
         <v>713</v>
       </c>
       <c r="E152" t="s">
-        <v>1664</v>
+        <v>1659</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>714</v>
@@ -9361,7 +9345,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B153" t="s">
         <v>716</v>
@@ -9373,7 +9357,7 @@
         <v>718</v>
       </c>
       <c r="E153" t="s">
-        <v>1665</v>
+        <v>1660</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>719</v>
@@ -9384,7 +9368,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B154" t="s">
         <v>721</v>
@@ -9396,18 +9380,18 @@
         <v>723</v>
       </c>
       <c r="E154" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>724</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>1708</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B155" t="s">
         <v>725</v>
@@ -9419,18 +9403,18 @@
         <v>727</v>
       </c>
       <c r="E155" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>728</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B156" t="s">
         <v>729</v>
@@ -9442,7 +9426,7 @@
         <v>731</v>
       </c>
       <c r="E156" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>732</v>
@@ -9453,7 +9437,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B157" t="s">
         <v>734</v>
@@ -9465,7 +9449,7 @@
         <v>736</v>
       </c>
       <c r="E157" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>737</v>
@@ -9476,7 +9460,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B158" t="s">
         <v>739</v>
@@ -9488,7 +9472,7 @@
         <v>741</v>
       </c>
       <c r="E158" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>742</v>
@@ -9499,7 +9483,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B159" t="s">
         <v>744</v>
@@ -9511,7 +9495,7 @@
         <v>746</v>
       </c>
       <c r="E159" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>747</v>
@@ -9522,7 +9506,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B160" t="s">
         <v>749</v>
@@ -9534,7 +9518,7 @@
         <v>751</v>
       </c>
       <c r="E160" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>752</v>
@@ -9545,7 +9529,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B161" t="s">
         <v>754</v>
@@ -9557,7 +9541,7 @@
         <v>756</v>
       </c>
       <c r="E161" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>757</v>
@@ -9568,7 +9552,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B162" t="s">
         <v>759</v>
@@ -9580,7 +9564,7 @@
         <v>761</v>
       </c>
       <c r="E162" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>762</v>
@@ -9591,7 +9575,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B163" t="s">
         <v>764</v>
@@ -9603,7 +9587,7 @@
         <v>766</v>
       </c>
       <c r="E163" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>767</v>
@@ -9614,7 +9598,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B164" t="s">
         <v>769</v>
@@ -9626,7 +9610,7 @@
         <v>771</v>
       </c>
       <c r="E164" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>772</v>
@@ -9637,7 +9621,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B165" t="s">
         <v>774</v>
@@ -9649,7 +9633,7 @@
         <v>776</v>
       </c>
       <c r="E165" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>777</v>
@@ -9660,7 +9644,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B166" t="s">
         <v>779</v>
@@ -9672,7 +9656,7 @@
         <v>781</v>
       </c>
       <c r="E166" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>782</v>
@@ -9683,7 +9667,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B167" t="s">
         <v>784</v>
@@ -9695,7 +9679,7 @@
         <v>786</v>
       </c>
       <c r="E167" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>787</v>
@@ -9706,7 +9690,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B168" t="s">
         <v>789</v>
@@ -9718,7 +9702,7 @@
         <v>791</v>
       </c>
       <c r="E168" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>792</v>
@@ -9729,7 +9713,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B169" t="s">
         <v>794</v>
@@ -9741,7 +9725,7 @@
         <v>796</v>
       </c>
       <c r="E169" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>797</v>
@@ -9752,7 +9736,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B170" t="s">
         <v>799</v>
@@ -9764,7 +9748,7 @@
         <v>801</v>
       </c>
       <c r="E170" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>802</v>
@@ -9775,7 +9759,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B171" t="s">
         <v>804</v>
@@ -9787,7 +9771,7 @@
         <v>806</v>
       </c>
       <c r="E171" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>807</v>
@@ -9798,7 +9782,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B172" t="s">
         <v>809</v>
@@ -9810,18 +9794,18 @@
         <v>811</v>
       </c>
       <c r="E172" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>812</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>1725</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B173" t="s">
         <v>813</v>
@@ -9833,7 +9817,7 @@
         <v>815</v>
       </c>
       <c r="E173" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>816</v>
@@ -9844,7 +9828,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B174" t="s">
         <v>818</v>
@@ -9856,7 +9840,7 @@
         <v>820</v>
       </c>
       <c r="E174" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>821</v>
@@ -9867,7 +9851,7 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B175" t="s">
         <v>823</v>
@@ -9879,7 +9863,7 @@
         <v>825</v>
       </c>
       <c r="E175" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>826</v>
@@ -9890,7 +9874,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B176" t="s">
         <v>828</v>
@@ -9902,7 +9886,7 @@
         <v>830</v>
       </c>
       <c r="E176" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>831</v>
@@ -9913,7 +9897,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B177" t="s">
         <v>833</v>
@@ -9925,18 +9909,18 @@
         <v>835</v>
       </c>
       <c r="E177" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>836</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>1726</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B178" t="s">
         <v>837</v>
@@ -9948,7 +9932,7 @@
         <v>839</v>
       </c>
       <c r="E178" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>840</v>
@@ -9959,7 +9943,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B179" t="s">
         <v>842</v>
@@ -9971,7 +9955,7 @@
         <v>844</v>
       </c>
       <c r="E179" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>845</v>
@@ -9982,7 +9966,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B180" t="s">
         <v>847</v>
@@ -9994,7 +9978,7 @@
         <v>849</v>
       </c>
       <c r="E180" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>850</v>
@@ -10005,7 +9989,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B181" t="s">
         <v>852</v>
@@ -10017,7 +10001,7 @@
         <v>854</v>
       </c>
       <c r="E181" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>855</v>
@@ -10028,7 +10012,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B182" t="s">
         <v>857</v>
@@ -10040,7 +10024,7 @@
         <v>859</v>
       </c>
       <c r="E182" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>860</v>
@@ -10051,7 +10035,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B183" t="s">
         <v>862</v>
@@ -10063,7 +10047,7 @@
         <v>864</v>
       </c>
       <c r="E183" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>865</v>
@@ -10074,7 +10058,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B184" t="s">
         <v>867</v>
@@ -10086,7 +10070,7 @@
         <v>869</v>
       </c>
       <c r="E184" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>870</v>
@@ -10097,7 +10081,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B185" t="s">
         <v>872</v>
@@ -10109,7 +10093,7 @@
         <v>874</v>
       </c>
       <c r="E185" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>875</v>
@@ -10120,7 +10104,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B186" t="s">
         <v>877</v>
@@ -10132,7 +10116,7 @@
         <v>879</v>
       </c>
       <c r="E186" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>880</v>
@@ -10143,7 +10127,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B187" t="s">
         <v>882</v>
@@ -10155,7 +10139,7 @@
         <v>884</v>
       </c>
       <c r="E187" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>885</v>
@@ -10166,7 +10150,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B188" t="s">
         <v>887</v>
@@ -10178,7 +10162,7 @@
         <v>889</v>
       </c>
       <c r="E188" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>890</v>
@@ -10189,7 +10173,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B189" t="s">
         <v>892</v>
@@ -10201,7 +10185,7 @@
         <v>894</v>
       </c>
       <c r="E189" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>895</v>
@@ -10212,7 +10196,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B190" t="s">
         <v>897</v>
@@ -10224,7 +10208,7 @@
         <v>899</v>
       </c>
       <c r="E190" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>900</v>
@@ -10235,7 +10219,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B191" t="s">
         <v>902</v>
@@ -10247,7 +10231,7 @@
         <v>904</v>
       </c>
       <c r="E191" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>116</v>
@@ -10258,7 +10242,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B192" t="s">
         <v>906</v>
@@ -10270,7 +10254,7 @@
         <v>908</v>
       </c>
       <c r="E192" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>909</v>
@@ -10281,7 +10265,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B193" t="s">
         <v>911</v>
@@ -10293,7 +10277,7 @@
         <v>913</v>
       </c>
       <c r="E193" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>914</v>
@@ -10304,7 +10288,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B194" t="s">
         <v>916</v>
@@ -10316,7 +10300,7 @@
         <v>918</v>
       </c>
       <c r="E194" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>919</v>
@@ -10327,7 +10311,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B195" t="s">
         <v>921</v>
@@ -10339,7 +10323,7 @@
         <v>923</v>
       </c>
       <c r="E195" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>924</v>
@@ -10350,7 +10334,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B196" t="s">
         <v>926</v>
@@ -10362,7 +10346,7 @@
         <v>928</v>
       </c>
       <c r="E196" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>929</v>
@@ -10373,7 +10357,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B197" t="s">
         <v>931</v>
@@ -10385,7 +10369,7 @@
         <v>933</v>
       </c>
       <c r="E197" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>934</v>
@@ -10396,7 +10380,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B198" t="s">
         <v>936</v>
@@ -10408,7 +10392,7 @@
         <v>938</v>
       </c>
       <c r="E198" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>939</v>
@@ -10419,7 +10403,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B199" t="s">
         <v>941</v>
@@ -10431,7 +10415,7 @@
         <v>943</v>
       </c>
       <c r="E199" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>944</v>
@@ -10442,7 +10426,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B200" t="s">
         <v>946</v>
@@ -10454,7 +10438,7 @@
         <v>948</v>
       </c>
       <c r="E200" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>949</v>
@@ -10465,7 +10449,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B201" t="s">
         <v>951</v>
@@ -10477,7 +10461,7 @@
         <v>953</v>
       </c>
       <c r="E201" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>954</v>
@@ -10488,7 +10472,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B202" t="s">
         <v>956</v>
@@ -10500,7 +10484,7 @@
         <v>958</v>
       </c>
       <c r="E202" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>959</v>
@@ -10511,7 +10495,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B203" t="s">
         <v>961</v>
@@ -10523,7 +10507,7 @@
         <v>963</v>
       </c>
       <c r="E203" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>964</v>
@@ -10534,7 +10518,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B204" t="s">
         <v>966</v>
@@ -10546,7 +10530,7 @@
         <v>968</v>
       </c>
       <c r="E204" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>969</v>
@@ -10557,7 +10541,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B205" t="s">
         <v>971</v>
@@ -10569,7 +10553,7 @@
         <v>973</v>
       </c>
       <c r="E205" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>974</v>
@@ -10580,7 +10564,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B206" t="s">
         <v>976</v>
@@ -10592,7 +10576,7 @@
         <v>978</v>
       </c>
       <c r="E206" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>979</v>
@@ -10603,7 +10587,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B207" t="s">
         <v>981</v>
@@ -10615,7 +10599,7 @@
         <v>983</v>
       </c>
       <c r="E207" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>984</v>
@@ -10626,7 +10610,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B208" t="s">
         <v>986</v>
@@ -10638,7 +10622,7 @@
         <v>988</v>
       </c>
       <c r="E208" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>989</v>
@@ -10649,7 +10633,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B209" t="s">
         <v>991</v>
@@ -10661,7 +10645,7 @@
         <v>993</v>
       </c>
       <c r="E209" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>994</v>
@@ -10672,7 +10656,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B210" t="s">
         <v>996</v>
@@ -10684,7 +10668,7 @@
         <v>998</v>
       </c>
       <c r="E210" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>999</v>
@@ -10695,7 +10679,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B211" t="s">
         <v>1001</v>
@@ -10707,7 +10691,7 @@
         <v>1003</v>
       </c>
       <c r="E211" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>1004</v>
@@ -10718,7 +10702,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B212" t="s">
         <v>1006</v>
@@ -10730,7 +10714,7 @@
         <v>1008</v>
       </c>
       <c r="E212" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>1009</v>
@@ -10741,7 +10725,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B213" t="s">
         <v>1011</v>
@@ -10753,7 +10737,7 @@
         <v>1013</v>
       </c>
       <c r="E213" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>1014</v>
@@ -10764,7 +10748,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B214" t="s">
         <v>1016</v>
@@ -10776,7 +10760,7 @@
         <v>1018</v>
       </c>
       <c r="E214" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>1019</v>
@@ -10787,7 +10771,7 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B215" t="s">
         <v>1021</v>
@@ -10799,7 +10783,7 @@
         <v>1023</v>
       </c>
       <c r="E215" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>1024</v>
@@ -10810,7 +10794,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B216" t="s">
         <v>1026</v>
@@ -10822,7 +10806,7 @@
         <v>1028</v>
       </c>
       <c r="E216" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>11</v>
@@ -10833,7 +10817,7 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B217" t="s">
         <v>1030</v>
@@ -10845,7 +10829,7 @@
         <v>1032</v>
       </c>
       <c r="E217" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>1033</v>
@@ -10856,7 +10840,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B218" t="s">
         <v>1035</v>
@@ -10868,7 +10852,7 @@
         <v>1037</v>
       </c>
       <c r="E218" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>1038</v>
@@ -10879,7 +10863,7 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B219" t="s">
         <v>1040</v>
@@ -10891,7 +10875,7 @@
         <v>1042</v>
       </c>
       <c r="E219" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>1043</v>
@@ -10902,7 +10886,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B220" t="s">
         <v>1045</v>
@@ -10914,7 +10898,7 @@
         <v>1047</v>
       </c>
       <c r="E220" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>1048</v>
@@ -10925,7 +10909,7 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B221" t="s">
         <v>1050</v>
@@ -10937,7 +10921,7 @@
         <v>1052</v>
       </c>
       <c r="E221" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>1053</v>
@@ -10948,7 +10932,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B222" t="s">
         <v>1055</v>
@@ -10960,7 +10944,7 @@
         <v>1057</v>
       </c>
       <c r="E222" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>1058</v>
@@ -10971,7 +10955,7 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B223" t="s">
         <v>1060</v>
@@ -10983,7 +10967,7 @@
         <v>1062</v>
       </c>
       <c r="E223" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>482</v>
@@ -10994,7 +10978,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B224" t="s">
         <v>1064</v>
@@ -11006,7 +10990,7 @@
         <v>1066</v>
       </c>
       <c r="E224" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>1067</v>
@@ -11017,7 +11001,7 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B225" t="s">
         <v>1069</v>
@@ -11029,7 +11013,7 @@
         <v>1071</v>
       </c>
       <c r="E225" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>1072</v>
@@ -11040,7 +11024,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B226" t="s">
         <v>1074</v>
@@ -11052,7 +11036,7 @@
         <v>15</v>
       </c>
       <c r="E226" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>1076</v>
@@ -11063,7 +11047,7 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B227" t="s">
         <v>1078</v>
@@ -11075,7 +11059,7 @@
         <v>1080</v>
       </c>
       <c r="E227" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>1081</v>
@@ -11086,7 +11070,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B228" t="s">
         <v>1083</v>
@@ -11098,7 +11082,7 @@
         <v>1085</v>
       </c>
       <c r="E228" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>1086</v>
@@ -11109,7 +11093,7 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B229" t="s">
         <v>1088</v>
@@ -11121,18 +11105,18 @@
         <v>1090</v>
       </c>
       <c r="E229" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>732</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1722</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B230" t="s">
         <v>1091</v>
@@ -11144,7 +11128,7 @@
         <v>1093</v>
       </c>
       <c r="E230" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>1094</v>
@@ -11155,7 +11139,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B231" t="s">
         <v>1096</v>
@@ -11167,7 +11151,7 @@
         <v>1098</v>
       </c>
       <c r="E231" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>1099</v>
@@ -11178,7 +11162,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B233" t="s">
         <v>1101</v>
@@ -11190,7 +11174,7 @@
         <v>1103</v>
       </c>
       <c r="E233" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>1104</v>
@@ -11201,7 +11185,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B234" t="s">
         <v>1106</v>
@@ -11213,7 +11197,7 @@
         <v>1108</v>
       </c>
       <c r="E234" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>1109</v>
@@ -11224,7 +11208,7 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B235" t="s">
         <v>1111</v>
@@ -11236,7 +11220,7 @@
         <v>1113</v>
       </c>
       <c r="E235" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>1114</v>
@@ -11247,7 +11231,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B236" t="s">
         <v>1118</v>
@@ -11259,7 +11243,7 @@
         <v>1120</v>
       </c>
       <c r="E236" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>1121</v>
@@ -11270,7 +11254,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B237" t="s">
         <v>1123</v>
@@ -11282,7 +11266,7 @@
         <v>1125</v>
       </c>
       <c r="E237" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>1126</v>
@@ -11293,7 +11277,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B238" t="s">
         <v>1128</v>
@@ -11305,7 +11289,7 @@
         <v>1130</v>
       </c>
       <c r="E238" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>1131</v>
@@ -11316,7 +11300,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B239" t="s">
         <v>1133</v>
@@ -11328,7 +11312,7 @@
         <v>1135</v>
       </c>
       <c r="E239" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>1136</v>
@@ -11339,7 +11323,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B240" t="s">
         <v>1138</v>
@@ -11351,7 +11335,7 @@
         <v>1140</v>
       </c>
       <c r="E240" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>1141</v>
@@ -11362,7 +11346,7 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B241" t="s">
         <v>1143</v>
@@ -11374,7 +11358,7 @@
         <v>8</v>
       </c>
       <c r="E241" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>1145</v>
@@ -11385,1057 +11369,1057 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B242" t="s">
-        <v>1147</v>
+        <v>1169</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>1148</v>
+        <v>1170</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="E242" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>1150</v>
+        <v>1172</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>1151</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B243" t="s">
-        <v>1152</v>
+        <v>1174</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>1153</v>
+        <v>1175</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>1154</v>
+        <v>1176</v>
       </c>
       <c r="E243" t="s">
-        <v>1486</v>
+        <v>1616</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>1155</v>
+        <v>1177</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>1156</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B244" t="s">
-        <v>1157</v>
+        <v>1179</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>1158</v>
+        <v>1180</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>1159</v>
+        <v>688</v>
       </c>
       <c r="E244" t="s">
         <v>1617</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>1160</v>
+        <v>1181</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1161</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B245" t="s">
-        <v>1162</v>
+        <v>1183</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>1163</v>
+        <v>1184</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>1164</v>
+        <v>1185</v>
       </c>
       <c r="E245" t="s">
         <v>1618</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>1165</v>
+        <v>6</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1166</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B246" t="s">
-        <v>1172</v>
+        <v>1187</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>1173</v>
+        <v>1188</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>1174</v>
+        <v>1189</v>
       </c>
       <c r="E246" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>1175</v>
+        <v>1190</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1176</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B247" t="s">
-        <v>1177</v>
+        <v>1192</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1178</v>
+        <v>1193</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1179</v>
+        <v>1194</v>
       </c>
       <c r="E247" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>1180</v>
+        <v>1195</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1181</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B248" t="s">
-        <v>1182</v>
+        <v>1197</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>1183</v>
+        <v>1198</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>688</v>
+        <v>1199</v>
       </c>
       <c r="E248" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>1184</v>
+        <v>1200</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>1185</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B249" t="s">
-        <v>1186</v>
+        <v>1202</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>1187</v>
+        <v>1203</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1188</v>
+        <v>1204</v>
       </c>
       <c r="E249" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>6</v>
+        <v>1205</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1189</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B250" t="s">
-        <v>1190</v>
+        <v>1207</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>1191</v>
+        <v>1208</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
       <c r="E250" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1194</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B251" t="s">
-        <v>1195</v>
+        <v>1212</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1196</v>
+        <v>1213</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>1197</v>
+        <v>1214</v>
       </c>
       <c r="E251" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>1198</v>
+        <v>7</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1199</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B252" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>1202</v>
+        <v>3</v>
       </c>
       <c r="E252" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>1203</v>
+        <v>1218</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>1204</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B253" t="s">
-        <v>1205</v>
+        <v>1220</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>1206</v>
+        <v>1221</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>1207</v>
+        <v>1222</v>
       </c>
       <c r="E253" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>1208</v>
+        <v>1103</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>1209</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B254" t="s">
-        <v>1210</v>
+        <v>1224</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>1211</v>
+        <v>1225</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>1212</v>
+        <v>1226</v>
       </c>
       <c r="E254" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>1213</v>
+        <v>1227</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1214</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B255" t="s">
-        <v>1215</v>
+        <v>1229</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>1216</v>
+        <v>1230</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>1217</v>
+        <v>1231</v>
       </c>
       <c r="E255" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>7</v>
+        <v>1232</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1218</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B256" t="s">
-        <v>1219</v>
+        <v>1234</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1220</v>
+        <v>1235</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>3</v>
+        <v>1236</v>
       </c>
       <c r="E256" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>1221</v>
+        <v>1237</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>1222</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B257" t="s">
-        <v>1223</v>
+        <v>1239</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1224</v>
+        <v>1240</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>1225</v>
+        <v>1241</v>
       </c>
       <c r="E257" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>1103</v>
+        <v>1242</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>1226</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B258" t="s">
-        <v>1227</v>
+        <v>1244</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>1228</v>
+        <v>1245</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>1229</v>
+        <v>1246</v>
       </c>
       <c r="E258" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>1230</v>
+        <v>1247</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>1231</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B259" t="s">
-        <v>1232</v>
+        <v>1249</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1233</v>
+        <v>1250</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>1234</v>
+        <v>1251</v>
       </c>
       <c r="E259" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>1235</v>
+        <v>1252</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>1236</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B260" t="s">
-        <v>1237</v>
+        <v>1254</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>1238</v>
+        <v>1255</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>1239</v>
+        <v>1256</v>
       </c>
       <c r="E260" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>1240</v>
+        <v>1257</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>1241</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B261" t="s">
-        <v>1242</v>
+        <v>1260</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>1243</v>
+        <v>1261</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>1244</v>
+        <v>1262</v>
       </c>
       <c r="E261" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>1245</v>
+        <v>1263</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>1246</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B262" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C262" s="1" t="s">
         <v>1403</v>
       </c>
-      <c r="B262" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>1248</v>
-      </c>
       <c r="D262" s="1" t="s">
-        <v>1249</v>
+        <v>1266</v>
       </c>
       <c r="E262" t="s">
-        <v>1636</v>
+        <v>1651</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>1250</v>
+        <v>1267</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>1251</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1403</v>
+        <v>1394</v>
       </c>
       <c r="B263" t="s">
-        <v>1252</v>
+        <v>1268</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1254</v>
+        <v>1270</v>
       </c>
       <c r="E263" t="s">
-        <v>1637</v>
+        <v>1652</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>1255</v>
+        <v>1271</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>1256</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1403</v>
+        <v>1392</v>
       </c>
       <c r="B264" t="s">
-        <v>1257</v>
+        <v>1273</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>1258</v>
+        <v>1274</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>1259</v>
+        <v>1242</v>
       </c>
       <c r="E264" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>1260</v>
+        <v>4</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1261</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B265" t="s">
-        <v>1263</v>
+        <v>1276</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1264</v>
+        <v>1277</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1265</v>
+        <v>1278</v>
       </c>
       <c r="E265" t="s">
-        <v>1639</v>
+        <v>1522</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>1266</v>
+        <v>1279</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1267</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="B266" t="s">
-        <v>1268</v>
+        <v>1281</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>1406</v>
+        <v>1282</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>1269</v>
+        <v>1283</v>
       </c>
       <c r="E266" t="s">
-        <v>1656</v>
+        <v>1636</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>1270</v>
+        <v>1284</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1407</v>
+        <v>1285</v>
+      </c>
+      <c r="L266" t="s">
+        <v>1387</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="B267" t="s">
-        <v>1271</v>
+        <v>1286</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>1272</v>
+        <v>1287</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1273</v>
+        <v>1288</v>
       </c>
       <c r="E267" t="s">
-        <v>1657</v>
+        <v>1637</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>1274</v>
+        <v>1289</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1275</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1395</v>
+        <v>1402</v>
       </c>
       <c r="B268" t="s">
-        <v>1276</v>
+        <v>1291</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>1277</v>
+        <v>1292</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1245</v>
+        <v>1293</v>
       </c>
       <c r="E268" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>4</v>
+        <v>1294</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1278</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1404</v>
+        <v>1394</v>
       </c>
       <c r="B269" t="s">
-        <v>1279</v>
+        <v>1296</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>1280</v>
+        <v>1297</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1281</v>
+        <v>1298</v>
       </c>
       <c r="E269" t="s">
-        <v>1525</v>
+        <v>1639</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>1282</v>
+        <v>1299</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1283</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B270" t="s">
-        <v>1284</v>
+        <v>1300</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>1285</v>
+        <v>1301</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1286</v>
+        <v>1302</v>
       </c>
       <c r="E270" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>1287</v>
+        <v>1303</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1288</v>
-      </c>
-      <c r="L270" t="s">
-        <v>1390</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1405</v>
+        <v>1392</v>
       </c>
       <c r="B271" t="s">
-        <v>1289</v>
+        <v>1305</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>1290</v>
+        <v>1306</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>1291</v>
+        <v>1307</v>
       </c>
       <c r="E271" t="s">
-        <v>1642</v>
+        <v>1489</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>1292</v>
+        <v>1308</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1293</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1405</v>
+        <v>1393</v>
       </c>
       <c r="B272" t="s">
-        <v>1294</v>
+        <v>1310</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>1295</v>
+        <v>1311</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>1296</v>
+        <v>1312</v>
       </c>
       <c r="E272" t="s">
-        <v>1643</v>
+        <v>1587</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>1297</v>
+        <v>1313</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1298</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
-        <v>1397</v>
-      </c>
       <c r="B273" t="s">
-        <v>1299</v>
+        <v>1315</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>1300</v>
+        <v>1316</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>1301</v>
+        <v>1317</v>
       </c>
       <c r="E273" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>1302</v>
+        <v>1259</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1717</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="B274" t="s">
-        <v>1303</v>
+        <v>1319</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>1304</v>
+        <v>1320</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>1305</v>
+        <v>1321</v>
       </c>
       <c r="E274" t="s">
-        <v>1645</v>
+        <v>1481</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>1306</v>
+        <v>1322</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B275" t="s">
-        <v>1308</v>
+        <v>1324</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>1309</v>
+        <v>1325</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>1310</v>
+        <v>1326</v>
       </c>
       <c r="E275" t="s">
-        <v>1492</v>
+        <v>1481</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>1311</v>
+        <v>1327</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B276" t="s">
-        <v>1313</v>
+        <v>1329</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>1314</v>
+        <v>1330</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1315</v>
+        <v>1331</v>
       </c>
       <c r="E276" t="s">
-        <v>1590</v>
+        <v>1642</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>1316</v>
+        <v>1332</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>1390</v>
+      </c>
       <c r="B277" t="s">
-        <v>1318</v>
+        <v>1334</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>1319</v>
+        <v>1335</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>1320</v>
+        <v>1336</v>
       </c>
       <c r="E277" t="s">
-        <v>1646</v>
+        <v>1494</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>1262</v>
+        <v>1337</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1321</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="B278" t="s">
-        <v>1322</v>
+        <v>1339</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>1323</v>
+        <v>1340</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>1324</v>
+        <v>1341</v>
       </c>
       <c r="E278" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>1325</v>
+        <v>1342</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>1326</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="B279" t="s">
-        <v>1327</v>
+        <v>1343</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>1328</v>
+        <v>1344</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1329</v>
+        <v>1345</v>
       </c>
       <c r="E279" t="s">
-        <v>1484</v>
+        <v>1517</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>1330</v>
+        <v>1346</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="B280" t="s">
-        <v>1332</v>
+        <v>1348</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>1333</v>
+        <v>1349</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>1334</v>
+        <v>1350</v>
       </c>
       <c r="E280" t="s">
-        <v>1647</v>
+        <v>1643</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>1335</v>
+        <v>1351</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>1336</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="B281" t="s">
-        <v>1337</v>
+        <v>1353</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>1338</v>
+        <v>1354</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>1339</v>
+        <v>1355</v>
       </c>
       <c r="E281" t="s">
-        <v>1497</v>
+        <v>1644</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>1340</v>
+        <v>154</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
-        <v>1393</v>
-      </c>
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B282" t="s">
-        <v>1342</v>
+        <v>1357</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>1343</v>
+        <v>1358</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>1344</v>
+        <v>1359</v>
       </c>
       <c r="E282" t="s">
-        <v>1482</v>
+        <v>1645</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>1345</v>
+        <v>1360</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1716</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1393</v>
+        <v>1401</v>
       </c>
       <c r="B283" t="s">
-        <v>1346</v>
+        <v>1362</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>1347</v>
+        <v>1363</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>1348</v>
+        <v>1364</v>
       </c>
       <c r="E283" t="s">
-        <v>1520</v>
+        <v>1646</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>1349</v>
+        <v>1365</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
       <c r="B284" t="s">
-        <v>1351</v>
+        <v>1116</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>1352</v>
+        <v>1367</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>1353</v>
+        <v>1117</v>
       </c>
       <c r="E284" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>1354</v>
+        <v>1368</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>1355</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B285" t="s">
-        <v>1356</v>
+        <v>1370</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>1357</v>
+        <v>1709</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="E285" t="s">
-        <v>1649</v>
+        <v>1501</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>154</v>
+        <v>1372</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>1392</v>
+      </c>
       <c r="B286" t="s">
-        <v>1360</v>
+        <v>1373</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>1361</v>
+        <v>1374</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>1362</v>
+        <v>1375</v>
       </c>
       <c r="E286" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>1363</v>
+        <v>1376</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1364</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1404</v>
+        <v>1394</v>
       </c>
       <c r="B287" t="s">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>1366</v>
+        <v>1379</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="E287" t="s">
-        <v>1651</v>
+        <v>1522</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>1368</v>
+        <v>1381</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1369</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
@@ -12443,252 +12427,160 @@
         <v>1398</v>
       </c>
       <c r="B288" t="s">
-        <v>1116</v>
+        <v>1207</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>1117</v>
+        <v>1384</v>
       </c>
       <c r="E288" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>1371</v>
+        <v>1385</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="B289" t="s">
-        <v>1373</v>
+        <v>1147</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>1714</v>
+        <v>1148</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1374</v>
+        <v>1149</v>
       </c>
       <c r="E289" t="s">
-        <v>1504</v>
+        <v>1613</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>1375</v>
+        <v>1150</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1715</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A290" t="s">
-        <v>1395</v>
-      </c>
-      <c r="B290" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C290" s="1" t="s">
-        <v>1377</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>1378</v>
-      </c>
-      <c r="E290" t="s">
-        <v>1653</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G290" s="1" t="s">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A290" s="5" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C290" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D290" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F290" s="8" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G290" s="7" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>1397</v>
       </c>
       <c r="B291" t="s">
-        <v>1381</v>
+        <v>1152</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>1382</v>
+        <v>1153</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>1383</v>
+        <v>1154</v>
       </c>
       <c r="E291" t="s">
-        <v>1525</v>
+        <v>1483</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>1384</v>
+        <v>1155</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>1385</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B292" t="s">
-        <v>1210</v>
+        <v>1156</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>1386</v>
+        <v>1157</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>1387</v>
+        <v>1158</v>
       </c>
       <c r="E292" t="s">
-        <v>1654</v>
+        <v>1635</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>1388</v>
+        <v>1159</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1389</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B293" t="s">
-        <v>1147</v>
+        <v>1161</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>1148</v>
+        <v>1162</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>1149</v>
+        <v>1163</v>
       </c>
       <c r="E293" t="s">
-        <v>1616</v>
+        <v>1650</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>1150</v>
+        <v>1706</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1151</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A294" s="5" t="s">
-        <v>1400</v>
-      </c>
-      <c r="B294" s="6" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C294" s="7" t="s">
-        <v>1168</v>
-      </c>
-      <c r="D294" s="7" t="s">
-        <v>1169</v>
-      </c>
-      <c r="E294" s="6" t="s">
-        <v>1619</v>
-      </c>
-      <c r="F294" s="8" t="s">
-        <v>1170</v>
-      </c>
-      <c r="G294" s="7" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
-        <v>1400</v>
-      </c>
-      <c r="B295" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C295" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>1154</v>
-      </c>
-      <c r="E295" t="s">
-        <v>1486</v>
-      </c>
-      <c r="F295" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G295" s="1" t="s">
+      <c r="A294" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B294" t="s">
         <v>1713</v>
       </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A296" t="s">
-        <v>1400</v>
-      </c>
-      <c r="B296" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C296" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E296" t="s">
-        <v>1640</v>
-      </c>
-      <c r="F296" s="2" t="s">
-        <v>1160</v>
-      </c>
-      <c r="G296" s="1" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
-        <v>1400</v>
-      </c>
-      <c r="B297" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C297" s="1" t="s">
-        <v>1163</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>1164</v>
-      </c>
-      <c r="E297" t="s">
-        <v>1655</v>
-      </c>
-      <c r="F297" s="2" t="s">
-        <v>1711</v>
-      </c>
-      <c r="G297" s="1" t="s">
-        <v>1712</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
-        <v>1397</v>
-      </c>
-      <c r="B298" t="s">
+      <c r="C294" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E294" t="s">
         <v>1718</v>
       </c>
-      <c r="C298" s="1" t="s">
+      <c r="F294" s="2" t="s">
+        <v>1716</v>
+      </c>
+      <c r="G294" t="s">
         <v>1719</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>1720</v>
-      </c>
-      <c r="E298" s="9" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>1721</v>
-      </c>
-      <c r="G298" t="s">
-        <v>1724</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Russian_Words_Cards.xlsx
+++ b/public/data/Russian_Words_Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504CA6E8-B8A4-4777-A327-DEFDB64A4647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B9969C-21F0-4133-BFD2-35D794900658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3096,9 +3096,6 @@
   </si>
   <si>
     <t>Strange</t>
-  </si>
-  <si>
-    <t>לכל סְטְרָנָה תרבות משלה. לפעמים כשמבקרים זה מרגיש קצת סטראנג'ר</t>
   </si>
   <si>
     <t>библиотека</t>
@@ -5437,6 +5434,9 @@
   </si>
   <si>
     <t>כשיש קריסה של מבנה ישן, עדיין אפשר לראות קְרִיסָה מסתובבת לידו</t>
+  </si>
+  <si>
+    <t>לכל סְטְרָנָה תרבות משלה. לפעמים כשמבקרים זה מרגיש קצת strange</t>
   </si>
 </sst>
 </file>
@@ -5852,27 +5852,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -5884,7 +5884,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
@@ -5895,7 +5895,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -5907,7 +5907,7 @@
         <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>24</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -5930,18 +5930,18 @@
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -5953,18 +5953,18 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>1681</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>1682</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -5976,18 +5976,18 @@
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B7" t="s">
         <v>37</v>
@@ -5999,30 +5999,30 @@
         <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>43</v>
@@ -6033,30 +6033,30 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B9" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
@@ -6068,7 +6068,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>50</v>
@@ -6079,7 +6079,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B11" t="s">
         <v>52</v>
@@ -6091,41 +6091,41 @@
         <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B12" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B13" t="s">
         <v>58</v>
@@ -6137,18 +6137,18 @@
         <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>1679</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>1680</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B14" t="s">
         <v>61</v>
@@ -6160,7 +6160,7 @@
         <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>64</v>
@@ -6171,7 +6171,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B15" t="s">
         <v>66</v>
@@ -6183,7 +6183,7 @@
         <v>68</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
@@ -6206,7 +6206,7 @@
         <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>74</v>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B17" t="s">
         <v>76</v>
@@ -6229,7 +6229,7 @@
         <v>78</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B18" t="s">
         <v>81</v>
@@ -6252,7 +6252,7 @@
         <v>83</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -6263,7 +6263,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B19" t="s">
         <v>86</v>
@@ -6275,7 +6275,7 @@
         <v>88</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
@@ -6286,7 +6286,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B20" t="s">
         <v>91</v>
@@ -6298,7 +6298,7 @@
         <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>94</v>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B21" t="s">
         <v>96</v>
@@ -6321,18 +6321,18 @@
         <v>98</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>99</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B22" t="s">
         <v>100</v>
@@ -6344,7 +6344,7 @@
         <v>102</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>103</v>
@@ -6355,30 +6355,30 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B23" t="s">
         <v>105</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>107</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B24" t="s">
         <v>108</v>
@@ -6390,7 +6390,7 @@
         <v>110</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>111</v>
@@ -6401,7 +6401,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B25" t="s">
         <v>113</v>
@@ -6413,7 +6413,7 @@
         <v>115</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>116</v>
@@ -6424,7 +6424,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B26" t="s">
         <v>118</v>
@@ -6436,7 +6436,7 @@
         <v>120</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>121</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B27" t="s">
         <v>123</v>
@@ -6459,7 +6459,7 @@
         <v>125</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>126</v>
@@ -6470,7 +6470,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B28" t="s">
         <v>128</v>
@@ -6482,7 +6482,7 @@
         <v>130</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>131</v>
@@ -6493,7 +6493,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B29" t="s">
         <v>133</v>
@@ -6505,7 +6505,7 @@
         <v>135</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>136</v>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B30" t="s">
         <v>138</v>
@@ -6528,7 +6528,7 @@
         <v>140</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>141</v>
@@ -6539,7 +6539,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B31" t="s">
         <v>143</v>
@@ -6551,7 +6551,7 @@
         <v>145</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>146</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B32" t="s">
         <v>148</v>
@@ -6574,18 +6574,18 @@
         <v>150</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>151</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B33" t="s">
         <v>152</v>
@@ -6597,7 +6597,7 @@
         <v>154</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>155</v>
@@ -6608,7 +6608,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B34" t="s">
         <v>157</v>
@@ -6620,7 +6620,7 @@
         <v>159</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>160</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B35" t="s">
         <v>162</v>
@@ -6643,7 +6643,7 @@
         <v>164</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>165</v>
@@ -6654,7 +6654,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B36" t="s">
         <v>167</v>
@@ -6666,7 +6666,7 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>169</v>
@@ -6677,7 +6677,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B37" t="s">
         <v>171</v>
@@ -6689,7 +6689,7 @@
         <v>173</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>174</v>
@@ -6700,7 +6700,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B38" t="s">
         <v>176</v>
@@ -6712,7 +6712,7 @@
         <v>178</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
@@ -6723,7 +6723,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B39" t="s">
         <v>180</v>
@@ -6735,7 +6735,7 @@
         <v>182</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>183</v>
@@ -6746,7 +6746,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B40" t="s">
         <v>185</v>
@@ -6758,7 +6758,7 @@
         <v>187</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>188</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B41" t="s">
         <v>190</v>
@@ -6781,7 +6781,7 @@
         <v>192</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>193</v>
@@ -6792,7 +6792,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B42" t="s">
         <v>195</v>
@@ -6804,7 +6804,7 @@
         <v>197</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>198</v>
@@ -6815,7 +6815,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B43" t="s">
         <v>200</v>
@@ -6827,7 +6827,7 @@
         <v>202</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>203</v>
@@ -6838,7 +6838,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B44" t="s">
         <v>205</v>
@@ -6850,7 +6850,7 @@
         <v>207</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>208</v>
@@ -6861,7 +6861,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B45" t="s">
         <v>210</v>
@@ -6873,18 +6873,18 @@
         <v>212</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>213</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B46" t="s">
         <v>214</v>
@@ -6896,7 +6896,7 @@
         <v>216</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>217</v>
@@ -6907,7 +6907,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B47" t="s">
         <v>219</v>
@@ -6919,7 +6919,7 @@
         <v>221</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>222</v>
@@ -6930,7 +6930,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B48" t="s">
         <v>224</v>
@@ -6942,7 +6942,7 @@
         <v>226</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>227</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B49" t="s">
         <v>229</v>
@@ -6965,7 +6965,7 @@
         <v>231</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>232</v>
@@ -6976,7 +6976,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B50" t="s">
         <v>234</v>
@@ -6988,7 +6988,7 @@
         <v>236</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>237</v>
@@ -6999,7 +6999,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B51" t="s">
         <v>239</v>
@@ -7011,7 +7011,7 @@
         <v>241</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>242</v>
@@ -7022,7 +7022,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B52" t="s">
         <v>244</v>
@@ -7034,7 +7034,7 @@
         <v>246</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>247</v>
@@ -7045,7 +7045,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B53" t="s">
         <v>249</v>
@@ -7057,18 +7057,18 @@
         <v>251</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B54" t="s">
         <v>252</v>
@@ -7080,18 +7080,18 @@
         <v>254</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>255</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B55" t="s">
         <v>256</v>
@@ -7103,7 +7103,7 @@
         <v>258</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>259</v>
@@ -7114,7 +7114,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B56" t="s">
         <v>261</v>
@@ -7126,7 +7126,7 @@
         <v>263</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>264</v>
@@ -7137,7 +7137,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B57" t="s">
         <v>266</v>
@@ -7149,7 +7149,7 @@
         <v>268</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>269</v>
@@ -7160,7 +7160,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B58" t="s">
         <v>271</v>
@@ -7172,7 +7172,7 @@
         <v>273</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>274</v>
@@ -7183,7 +7183,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B59" t="s">
         <v>276</v>
@@ -7195,7 +7195,7 @@
         <v>278</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>279</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B60" t="s">
         <v>281</v>
@@ -7218,7 +7218,7 @@
         <v>283</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>284</v>
@@ -7229,7 +7229,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B61" t="s">
         <v>286</v>
@@ -7241,7 +7241,7 @@
         <v>288</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>289</v>
@@ -7252,7 +7252,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B62" t="s">
         <v>291</v>
@@ -7264,7 +7264,7 @@
         <v>293</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>294</v>
@@ -7275,7 +7275,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B63" t="s">
         <v>296</v>
@@ -7284,10 +7284,10 @@
         <v>297</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>298</v>
@@ -7298,7 +7298,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B64" t="s">
         <v>300</v>
@@ -7310,7 +7310,7 @@
         <v>302</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>2</v>
@@ -7321,7 +7321,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B65" t="s">
         <v>304</v>
@@ -7333,7 +7333,7 @@
         <v>306</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>307</v>
@@ -7344,7 +7344,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B66" t="s">
         <v>309</v>
@@ -7356,7 +7356,7 @@
         <v>311</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>312</v>
@@ -7367,7 +7367,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B67" t="s">
         <v>314</v>
@@ -7379,7 +7379,7 @@
         <v>316</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>317</v>
@@ -7390,7 +7390,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B68" t="s">
         <v>319</v>
@@ -7402,18 +7402,18 @@
         <v>321</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>322</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B69" t="s">
         <v>323</v>
@@ -7425,7 +7425,7 @@
         <v>325</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>326</v>
@@ -7436,7 +7436,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B70" t="s">
         <v>328</v>
@@ -7448,7 +7448,7 @@
         <v>330</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>331</v>
@@ -7459,7 +7459,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B71" t="s">
         <v>333</v>
@@ -7471,7 +7471,7 @@
         <v>335</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>336</v>
@@ -7482,7 +7482,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B72" t="s">
         <v>338</v>
@@ -7494,7 +7494,7 @@
         <v>340</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>341</v>
@@ -7505,7 +7505,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B73" t="s">
         <v>343</v>
@@ -7517,7 +7517,7 @@
         <v>345</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>346</v>
@@ -7528,7 +7528,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B74" t="s">
         <v>348</v>
@@ -7540,7 +7540,7 @@
         <v>350</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>351</v>
@@ -7551,7 +7551,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B75" t="s">
         <v>353</v>
@@ -7563,18 +7563,18 @@
         <v>355</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>356</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B76" t="s">
         <v>357</v>
@@ -7586,7 +7586,7 @@
         <v>359</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>360</v>
@@ -7597,7 +7597,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B77" t="s">
         <v>362</v>
@@ -7609,7 +7609,7 @@
         <v>364</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>365</v>
@@ -7620,7 +7620,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B78" t="s">
         <v>367</v>
@@ -7632,7 +7632,7 @@
         <v>369</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>370</v>
@@ -7643,30 +7643,30 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B79" t="s">
         <v>372</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>373</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>374</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B80" t="s">
         <v>375</v>
@@ -7678,7 +7678,7 @@
         <v>377</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>378</v>
@@ -7689,7 +7689,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B81" t="s">
         <v>380</v>
@@ -7701,18 +7701,18 @@
         <v>382</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>383</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B82" t="s">
         <v>384</v>
@@ -7724,7 +7724,7 @@
         <v>386</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>387</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B83" t="s">
         <v>389</v>
@@ -7747,7 +7747,7 @@
         <v>391</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>392</v>
@@ -7758,7 +7758,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B84" t="s">
         <v>394</v>
@@ -7770,7 +7770,7 @@
         <v>396</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>1</v>
@@ -7781,7 +7781,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B85" t="s">
         <v>398</v>
@@ -7793,7 +7793,7 @@
         <v>400</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>401</v>
@@ -7804,7 +7804,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B86" t="s">
         <v>403</v>
@@ -7816,7 +7816,7 @@
         <v>405</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>406</v>
@@ -7827,7 +7827,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B87" t="s">
         <v>408</v>
@@ -7839,7 +7839,7 @@
         <v>410</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>411</v>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B88" t="s">
         <v>413</v>
@@ -7862,18 +7862,18 @@
         <v>415</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>416</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B89" t="s">
         <v>417</v>
@@ -7885,7 +7885,7 @@
         <v>419</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>420</v>
@@ -7896,7 +7896,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B90" t="s">
         <v>422</v>
@@ -7908,7 +7908,7 @@
         <v>424</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>425</v>
@@ -7919,7 +7919,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B91" t="s">
         <v>427</v>
@@ -7931,18 +7931,18 @@
         <v>429</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>430</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B92" t="s">
         <v>431</v>
@@ -7954,7 +7954,7 @@
         <v>433</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>434</v>
@@ -7965,7 +7965,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B93" t="s">
         <v>436</v>
@@ -7977,7 +7977,7 @@
         <v>438</v>
       </c>
       <c r="E93" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>439</v>
@@ -7988,7 +7988,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B94" t="s">
         <v>441</v>
@@ -8000,7 +8000,7 @@
         <v>443</v>
       </c>
       <c r="E94" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>444</v>
@@ -8011,7 +8011,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B95" t="s">
         <v>446</v>
@@ -8023,7 +8023,7 @@
         <v>448</v>
       </c>
       <c r="E95" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>449</v>
@@ -8034,7 +8034,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B96" t="s">
         <v>451</v>
@@ -8046,7 +8046,7 @@
         <v>453</v>
       </c>
       <c r="E96" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>454</v>
@@ -8057,7 +8057,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B97" t="s">
         <v>456</v>
@@ -8069,7 +8069,7 @@
         <v>458</v>
       </c>
       <c r="E97" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>459</v>
@@ -8080,7 +8080,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B98" t="s">
         <v>461</v>
@@ -8092,7 +8092,7 @@
         <v>463</v>
       </c>
       <c r="E98" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>464</v>
@@ -8103,7 +8103,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B99" t="s">
         <v>466</v>
@@ -8115,7 +8115,7 @@
         <v>468</v>
       </c>
       <c r="E99" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>469</v>
@@ -8126,7 +8126,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B100" t="s">
         <v>503</v>
@@ -8138,7 +8138,7 @@
         <v>505</v>
       </c>
       <c r="E100" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>506</v>
@@ -8149,7 +8149,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B101" t="s">
         <v>471</v>
@@ -8161,7 +8161,7 @@
         <v>473</v>
       </c>
       <c r="E101" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>474</v>
@@ -8172,7 +8172,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B102" t="s">
         <v>476</v>
@@ -8184,18 +8184,18 @@
         <v>478</v>
       </c>
       <c r="E102" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>479</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B103" t="s">
         <v>480</v>
@@ -8207,7 +8207,7 @@
         <v>482</v>
       </c>
       <c r="E103" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>483</v>
@@ -8218,7 +8218,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B104" t="s">
         <v>485</v>
@@ -8230,7 +8230,7 @@
         <v>487</v>
       </c>
       <c r="E104" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>488</v>
@@ -8241,7 +8241,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B105" t="s">
         <v>490</v>
@@ -8253,18 +8253,18 @@
         <v>492</v>
       </c>
       <c r="E105" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>493</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B106" t="s">
         <v>494</v>
@@ -8276,7 +8276,7 @@
         <v>496</v>
       </c>
       <c r="E106" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>497</v>
@@ -8287,7 +8287,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B107" t="s">
         <v>499</v>
@@ -8299,18 +8299,18 @@
         <v>501</v>
       </c>
       <c r="E107" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>502</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B108" t="s">
         <v>508</v>
@@ -8322,10 +8322,10 @@
         <v>510</v>
       </c>
       <c r="E108" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>511</v>
@@ -8333,7 +8333,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B109" t="s">
         <v>512</v>
@@ -8345,7 +8345,7 @@
         <v>514</v>
       </c>
       <c r="E109" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>515</v>
@@ -8356,7 +8356,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B110" t="s">
         <v>517</v>
@@ -8368,7 +8368,7 @@
         <v>519</v>
       </c>
       <c r="E110" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>13</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B111" t="s">
         <v>521</v>
@@ -8391,7 +8391,7 @@
         <v>523</v>
       </c>
       <c r="E111" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>524</v>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B112" t="s">
         <v>526</v>
@@ -8414,7 +8414,7 @@
         <v>528</v>
       </c>
       <c r="E112" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>529</v>
@@ -8425,7 +8425,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B113" t="s">
         <v>531</v>
@@ -8437,7 +8437,7 @@
         <v>533</v>
       </c>
       <c r="E113" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>534</v>
@@ -8448,7 +8448,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B114" t="s">
         <v>536</v>
@@ -8460,7 +8460,7 @@
         <v>538</v>
       </c>
       <c r="E114" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>14</v>
@@ -8471,7 +8471,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B115" t="s">
         <v>540</v>
@@ -8483,18 +8483,18 @@
         <v>542</v>
       </c>
       <c r="E115" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F115" s="2" t="s">
+        <v>1694</v>
+      </c>
+      <c r="G115" s="1" t="s">
         <v>1695</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>1696</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B116" t="s">
         <v>543</v>
@@ -8506,7 +8506,7 @@
         <v>545</v>
       </c>
       <c r="E116" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>283</v>
@@ -8517,7 +8517,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B117" t="s">
         <v>547</v>
@@ -8529,7 +8529,7 @@
         <v>549</v>
       </c>
       <c r="E117" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>550</v>
@@ -8540,7 +8540,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B118" t="s">
         <v>552</v>
@@ -8552,7 +8552,7 @@
         <v>554</v>
       </c>
       <c r="E118" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>555</v>
@@ -8563,7 +8563,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B119" t="s">
         <v>557</v>
@@ -8575,7 +8575,7 @@
         <v>559</v>
       </c>
       <c r="E119" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
@@ -8586,7 +8586,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B120" t="s">
         <v>561</v>
@@ -8598,7 +8598,7 @@
         <v>563</v>
       </c>
       <c r="E120" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>564</v>
@@ -8609,7 +8609,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B121" t="s">
         <v>566</v>
@@ -8621,7 +8621,7 @@
         <v>568</v>
       </c>
       <c r="E121" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>569</v>
@@ -8632,7 +8632,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B122" t="s">
         <v>571</v>
@@ -8644,7 +8644,7 @@
         <v>573</v>
       </c>
       <c r="E122" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>574</v>
@@ -8655,7 +8655,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B123" t="s">
         <v>576</v>
@@ -8667,7 +8667,7 @@
         <v>578</v>
       </c>
       <c r="E123" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>579</v>
@@ -8678,7 +8678,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B124" t="s">
         <v>581</v>
@@ -8690,7 +8690,7 @@
         <v>583</v>
       </c>
       <c r="E124" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>12</v>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B125" t="s">
         <v>585</v>
@@ -8713,18 +8713,18 @@
         <v>587</v>
       </c>
       <c r="E125" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>588</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B126" t="s">
         <v>589</v>
@@ -8736,7 +8736,7 @@
         <v>591</v>
       </c>
       <c r="E126" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>592</v>
@@ -8747,7 +8747,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B127" t="s">
         <v>594</v>
@@ -8759,7 +8759,7 @@
         <v>596</v>
       </c>
       <c r="E127" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>597</v>
@@ -8770,7 +8770,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B128" t="s">
         <v>599</v>
@@ -8782,7 +8782,7 @@
         <v>601</v>
       </c>
       <c r="E128" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>602</v>
@@ -8793,7 +8793,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B129" t="s">
         <v>604</v>
@@ -8805,7 +8805,7 @@
         <v>606</v>
       </c>
       <c r="E129" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>607</v>
@@ -8816,7 +8816,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B130" t="s">
         <v>609</v>
@@ -8828,7 +8828,7 @@
         <v>611</v>
       </c>
       <c r="E130" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>612</v>
@@ -8839,7 +8839,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B131" t="s">
         <v>614</v>
@@ -8851,7 +8851,7 @@
         <v>616</v>
       </c>
       <c r="E131" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>293</v>
@@ -8862,7 +8862,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B132" t="s">
         <v>618</v>
@@ -8874,7 +8874,7 @@
         <v>620</v>
       </c>
       <c r="E132" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>621</v>
@@ -8885,7 +8885,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B133" t="s">
         <v>623</v>
@@ -8897,7 +8897,7 @@
         <v>625</v>
       </c>
       <c r="E133" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>626</v>
@@ -8908,7 +8908,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B134" t="s">
         <v>628</v>
@@ -8920,7 +8920,7 @@
         <v>630</v>
       </c>
       <c r="E134" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>631</v>
@@ -8931,7 +8931,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B135" t="s">
         <v>633</v>
@@ -8943,7 +8943,7 @@
         <v>635</v>
       </c>
       <c r="E135" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>636</v>
@@ -8954,7 +8954,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B136" t="s">
         <v>638</v>
@@ -8966,7 +8966,7 @@
         <v>640</v>
       </c>
       <c r="E136" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>641</v>
@@ -8977,7 +8977,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B137" t="s">
         <v>643</v>
@@ -8989,7 +8989,7 @@
         <v>645</v>
       </c>
       <c r="E137" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>646</v>
@@ -9000,7 +9000,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B138" t="s">
         <v>648</v>
@@ -9012,7 +9012,7 @@
         <v>650</v>
       </c>
       <c r="E138" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>651</v>
@@ -9023,7 +9023,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B139" t="s">
         <v>653</v>
@@ -9035,7 +9035,7 @@
         <v>655</v>
       </c>
       <c r="E139" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>656</v>
@@ -9046,7 +9046,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B140" t="s">
         <v>658</v>
@@ -9058,18 +9058,18 @@
         <v>660</v>
       </c>
       <c r="E140" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>661</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B141" t="s">
         <v>662</v>
@@ -9081,7 +9081,7 @@
         <v>664</v>
       </c>
       <c r="E141" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>665</v>
@@ -9092,7 +9092,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B142" t="s">
         <v>667</v>
@@ -9104,18 +9104,18 @@
         <v>669</v>
       </c>
       <c r="E142" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>670</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B143" t="s">
         <v>671</v>
@@ -9127,18 +9127,18 @@
         <v>673</v>
       </c>
       <c r="E143" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>674</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B144" t="s">
         <v>675</v>
@@ -9150,7 +9150,7 @@
         <v>677</v>
       </c>
       <c r="E144" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>678</v>
@@ -9161,7 +9161,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B145" t="s">
         <v>680</v>
@@ -9173,7 +9173,7 @@
         <v>682</v>
       </c>
       <c r="E145" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>683</v>
@@ -9184,7 +9184,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B146" t="s">
         <v>685</v>
@@ -9196,7 +9196,7 @@
         <v>687</v>
       </c>
       <c r="E146" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>688</v>
@@ -9207,7 +9207,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B147" t="s">
         <v>690</v>
@@ -9219,7 +9219,7 @@
         <v>692</v>
       </c>
       <c r="E147" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>693</v>
@@ -9230,7 +9230,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B148" t="s">
         <v>695</v>
@@ -9242,18 +9242,18 @@
         <v>697</v>
       </c>
       <c r="E148" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="F148" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="G148" s="1" t="s">
         <v>1701</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>1702</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B149" t="s">
         <v>698</v>
@@ -9265,7 +9265,7 @@
         <v>274</v>
       </c>
       <c r="E149" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>700</v>
@@ -9276,7 +9276,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B150" t="s">
         <v>702</v>
@@ -9288,7 +9288,7 @@
         <v>704</v>
       </c>
       <c r="E150" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>4</v>
@@ -9299,7 +9299,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B151" t="s">
         <v>706</v>
@@ -9311,7 +9311,7 @@
         <v>708</v>
       </c>
       <c r="E151" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>709</v>
@@ -9322,7 +9322,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B152" t="s">
         <v>711</v>
@@ -9334,7 +9334,7 @@
         <v>713</v>
       </c>
       <c r="E152" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>714</v>
@@ -9345,7 +9345,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B153" t="s">
         <v>716</v>
@@ -9357,7 +9357,7 @@
         <v>718</v>
       </c>
       <c r="E153" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>719</v>
@@ -9368,7 +9368,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B154" t="s">
         <v>721</v>
@@ -9380,18 +9380,18 @@
         <v>723</v>
       </c>
       <c r="E154" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>724</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B155" t="s">
         <v>725</v>
@@ -9403,18 +9403,18 @@
         <v>727</v>
       </c>
       <c r="E155" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>728</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B156" t="s">
         <v>729</v>
@@ -9426,7 +9426,7 @@
         <v>731</v>
       </c>
       <c r="E156" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>732</v>
@@ -9437,7 +9437,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B157" t="s">
         <v>734</v>
@@ -9449,7 +9449,7 @@
         <v>736</v>
       </c>
       <c r="E157" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>737</v>
@@ -9460,7 +9460,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B158" t="s">
         <v>739</v>
@@ -9472,7 +9472,7 @@
         <v>741</v>
       </c>
       <c r="E158" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>742</v>
@@ -9483,7 +9483,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B159" t="s">
         <v>744</v>
@@ -9495,7 +9495,7 @@
         <v>746</v>
       </c>
       <c r="E159" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>747</v>
@@ -9506,7 +9506,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B160" t="s">
         <v>749</v>
@@ -9518,7 +9518,7 @@
         <v>751</v>
       </c>
       <c r="E160" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>752</v>
@@ -9529,7 +9529,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B161" t="s">
         <v>754</v>
@@ -9541,7 +9541,7 @@
         <v>756</v>
       </c>
       <c r="E161" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>757</v>
@@ -9552,7 +9552,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B162" t="s">
         <v>759</v>
@@ -9564,7 +9564,7 @@
         <v>761</v>
       </c>
       <c r="E162" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>762</v>
@@ -9575,7 +9575,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B163" t="s">
         <v>764</v>
@@ -9587,7 +9587,7 @@
         <v>766</v>
       </c>
       <c r="E163" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>767</v>
@@ -9598,7 +9598,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B164" t="s">
         <v>769</v>
@@ -9610,7 +9610,7 @@
         <v>771</v>
       </c>
       <c r="E164" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>772</v>
@@ -9621,7 +9621,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B165" t="s">
         <v>774</v>
@@ -9633,7 +9633,7 @@
         <v>776</v>
       </c>
       <c r="E165" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>777</v>
@@ -9644,7 +9644,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B166" t="s">
         <v>779</v>
@@ -9656,7 +9656,7 @@
         <v>781</v>
       </c>
       <c r="E166" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>782</v>
@@ -9667,7 +9667,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B167" t="s">
         <v>784</v>
@@ -9679,7 +9679,7 @@
         <v>786</v>
       </c>
       <c r="E167" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>787</v>
@@ -9690,7 +9690,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B168" t="s">
         <v>789</v>
@@ -9702,7 +9702,7 @@
         <v>791</v>
       </c>
       <c r="E168" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>792</v>
@@ -9713,7 +9713,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B169" t="s">
         <v>794</v>
@@ -9725,7 +9725,7 @@
         <v>796</v>
       </c>
       <c r="E169" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>797</v>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B170" t="s">
         <v>799</v>
@@ -9748,7 +9748,7 @@
         <v>801</v>
       </c>
       <c r="E170" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>802</v>
@@ -9759,7 +9759,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B171" t="s">
         <v>804</v>
@@ -9771,7 +9771,7 @@
         <v>806</v>
       </c>
       <c r="E171" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>807</v>
@@ -9782,7 +9782,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B172" t="s">
         <v>809</v>
@@ -9794,18 +9794,18 @@
         <v>811</v>
       </c>
       <c r="E172" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>812</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B173" t="s">
         <v>813</v>
@@ -9817,7 +9817,7 @@
         <v>815</v>
       </c>
       <c r="E173" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>816</v>
@@ -9828,7 +9828,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B174" t="s">
         <v>818</v>
@@ -9840,7 +9840,7 @@
         <v>820</v>
       </c>
       <c r="E174" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>821</v>
@@ -9851,7 +9851,7 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B175" t="s">
         <v>823</v>
@@ -9863,7 +9863,7 @@
         <v>825</v>
       </c>
       <c r="E175" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>826</v>
@@ -9874,7 +9874,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B176" t="s">
         <v>828</v>
@@ -9886,7 +9886,7 @@
         <v>830</v>
       </c>
       <c r="E176" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>831</v>
@@ -9897,7 +9897,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B177" t="s">
         <v>833</v>
@@ -9909,18 +9909,18 @@
         <v>835</v>
       </c>
       <c r="E177" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>836</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B178" t="s">
         <v>837</v>
@@ -9932,7 +9932,7 @@
         <v>839</v>
       </c>
       <c r="E178" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>840</v>
@@ -9943,7 +9943,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B179" t="s">
         <v>842</v>
@@ -9955,7 +9955,7 @@
         <v>844</v>
       </c>
       <c r="E179" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>845</v>
@@ -9966,7 +9966,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B180" t="s">
         <v>847</v>
@@ -9978,7 +9978,7 @@
         <v>849</v>
       </c>
       <c r="E180" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>850</v>
@@ -9989,7 +9989,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B181" t="s">
         <v>852</v>
@@ -10001,7 +10001,7 @@
         <v>854</v>
       </c>
       <c r="E181" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>855</v>
@@ -10012,7 +10012,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B182" t="s">
         <v>857</v>
@@ -10024,7 +10024,7 @@
         <v>859</v>
       </c>
       <c r="E182" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>860</v>
@@ -10035,7 +10035,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B183" t="s">
         <v>862</v>
@@ -10047,7 +10047,7 @@
         <v>864</v>
       </c>
       <c r="E183" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>865</v>
@@ -10058,7 +10058,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B184" t="s">
         <v>867</v>
@@ -10070,7 +10070,7 @@
         <v>869</v>
       </c>
       <c r="E184" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>870</v>
@@ -10081,7 +10081,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B185" t="s">
         <v>872</v>
@@ -10093,7 +10093,7 @@
         <v>874</v>
       </c>
       <c r="E185" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>875</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B186" t="s">
         <v>877</v>
@@ -10116,7 +10116,7 @@
         <v>879</v>
       </c>
       <c r="E186" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>880</v>
@@ -10127,7 +10127,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B187" t="s">
         <v>882</v>
@@ -10139,7 +10139,7 @@
         <v>884</v>
       </c>
       <c r="E187" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>885</v>
@@ -10150,7 +10150,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B188" t="s">
         <v>887</v>
@@ -10162,7 +10162,7 @@
         <v>889</v>
       </c>
       <c r="E188" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>890</v>
@@ -10173,7 +10173,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B189" t="s">
         <v>892</v>
@@ -10185,7 +10185,7 @@
         <v>894</v>
       </c>
       <c r="E189" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>895</v>
@@ -10196,7 +10196,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B190" t="s">
         <v>897</v>
@@ -10208,7 +10208,7 @@
         <v>899</v>
       </c>
       <c r="E190" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>900</v>
@@ -10219,7 +10219,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B191" t="s">
         <v>902</v>
@@ -10231,7 +10231,7 @@
         <v>904</v>
       </c>
       <c r="E191" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>116</v>
@@ -10242,7 +10242,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B192" t="s">
         <v>906</v>
@@ -10254,7 +10254,7 @@
         <v>908</v>
       </c>
       <c r="E192" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>909</v>
@@ -10265,7 +10265,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B193" t="s">
         <v>911</v>
@@ -10277,7 +10277,7 @@
         <v>913</v>
       </c>
       <c r="E193" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>914</v>
@@ -10288,7 +10288,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B194" t="s">
         <v>916</v>
@@ -10300,7 +10300,7 @@
         <v>918</v>
       </c>
       <c r="E194" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>919</v>
@@ -10311,7 +10311,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B195" t="s">
         <v>921</v>
@@ -10323,7 +10323,7 @@
         <v>923</v>
       </c>
       <c r="E195" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>924</v>
@@ -10334,7 +10334,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B196" t="s">
         <v>926</v>
@@ -10346,7 +10346,7 @@
         <v>928</v>
       </c>
       <c r="E196" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>929</v>
@@ -10357,7 +10357,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B197" t="s">
         <v>931</v>
@@ -10369,7 +10369,7 @@
         <v>933</v>
       </c>
       <c r="E197" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>934</v>
@@ -10380,7 +10380,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B198" t="s">
         <v>936</v>
@@ -10392,7 +10392,7 @@
         <v>938</v>
       </c>
       <c r="E198" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>939</v>
@@ -10403,7 +10403,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B199" t="s">
         <v>941</v>
@@ -10415,7 +10415,7 @@
         <v>943</v>
       </c>
       <c r="E199" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>944</v>
@@ -10426,7 +10426,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B200" t="s">
         <v>946</v>
@@ -10438,7 +10438,7 @@
         <v>948</v>
       </c>
       <c r="E200" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>949</v>
@@ -10449,7 +10449,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B201" t="s">
         <v>951</v>
@@ -10461,7 +10461,7 @@
         <v>953</v>
       </c>
       <c r="E201" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>954</v>
@@ -10472,7 +10472,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B202" t="s">
         <v>956</v>
@@ -10484,7 +10484,7 @@
         <v>958</v>
       </c>
       <c r="E202" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>959</v>
@@ -10495,7 +10495,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B203" t="s">
         <v>961</v>
@@ -10507,7 +10507,7 @@
         <v>963</v>
       </c>
       <c r="E203" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>964</v>
@@ -10518,7 +10518,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B204" t="s">
         <v>966</v>
@@ -10530,7 +10530,7 @@
         <v>968</v>
       </c>
       <c r="E204" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>969</v>
@@ -10541,7 +10541,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B205" t="s">
         <v>971</v>
@@ -10553,7 +10553,7 @@
         <v>973</v>
       </c>
       <c r="E205" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>974</v>
@@ -10564,7 +10564,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B206" t="s">
         <v>976</v>
@@ -10576,7 +10576,7 @@
         <v>978</v>
       </c>
       <c r="E206" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>979</v>
@@ -10587,7 +10587,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B207" t="s">
         <v>981</v>
@@ -10599,7 +10599,7 @@
         <v>983</v>
       </c>
       <c r="E207" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>984</v>
@@ -10610,7 +10610,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B208" t="s">
         <v>986</v>
@@ -10622,7 +10622,7 @@
         <v>988</v>
       </c>
       <c r="E208" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>989</v>
@@ -10633,7 +10633,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B209" t="s">
         <v>991</v>
@@ -10645,7 +10645,7 @@
         <v>993</v>
       </c>
       <c r="E209" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>994</v>
@@ -10656,7 +10656,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B210" t="s">
         <v>996</v>
@@ -10668,7 +10668,7 @@
         <v>998</v>
       </c>
       <c r="E210" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>999</v>
@@ -10679,7 +10679,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B211" t="s">
         <v>1001</v>
@@ -10691,7 +10691,7 @@
         <v>1003</v>
       </c>
       <c r="E211" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>1004</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B212" t="s">
         <v>1006</v>
@@ -10714,7 +10714,7 @@
         <v>1008</v>
       </c>
       <c r="E212" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>1009</v>
@@ -10725,7 +10725,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B213" t="s">
         <v>1011</v>
@@ -10737,7 +10737,7 @@
         <v>1013</v>
       </c>
       <c r="E213" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>1014</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B214" t="s">
         <v>1016</v>
@@ -10760,1827 +10760,1827 @@
         <v>1018</v>
       </c>
       <c r="E214" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>1019</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1020</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B215" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C215" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="C215" s="1" t="s">
+      <c r="D215" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="E215" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F215" s="2" t="s">
         <v>1023</v>
       </c>
-      <c r="E215" t="s">
-        <v>1515</v>
-      </c>
-      <c r="F215" s="2" t="s">
+      <c r="G215" s="1" t="s">
         <v>1024</v>
-      </c>
-      <c r="G215" s="1" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B216" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="C216" s="1" t="s">
+      <c r="D216" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="D216" s="1" t="s">
-        <v>1028</v>
-      </c>
       <c r="E216" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B217" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C217" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="C217" s="1" t="s">
+      <c r="D217" s="1" t="s">
         <v>1031</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="E217" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F217" s="2" t="s">
         <v>1032</v>
       </c>
-      <c r="E217" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F217" s="2" t="s">
+      <c r="G217" s="1" t="s">
         <v>1033</v>
-      </c>
-      <c r="G217" s="1" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B218" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C218" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="C218" s="1" t="s">
+      <c r="D218" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="E218" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F218" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="E218" t="s">
-        <v>1592</v>
-      </c>
-      <c r="F218" s="2" t="s">
+      <c r="G218" s="1" t="s">
         <v>1038</v>
-      </c>
-      <c r="G218" s="1" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B219" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C219" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="C219" s="1" t="s">
+      <c r="D219" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="E219" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F219" s="2" t="s">
         <v>1042</v>
       </c>
-      <c r="E219" t="s">
-        <v>1593</v>
-      </c>
-      <c r="F219" s="2" t="s">
+      <c r="G219" s="1" t="s">
         <v>1043</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B220" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C220" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="C220" s="1" t="s">
+      <c r="D220" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="D220" s="1" t="s">
+      <c r="E220" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F220" s="2" t="s">
         <v>1047</v>
       </c>
-      <c r="E220" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F220" s="2" t="s">
+      <c r="G220" s="1" t="s">
         <v>1048</v>
-      </c>
-      <c r="G220" s="1" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B221" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C221" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="C221" s="1" t="s">
+      <c r="D221" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="D221" s="1" t="s">
+      <c r="E221" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="E221" t="s">
-        <v>1595</v>
-      </c>
-      <c r="F221" s="2" t="s">
+      <c r="G221" s="1" t="s">
         <v>1053</v>
-      </c>
-      <c r="G221" s="1" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B222" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C222" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="C222" s="1" t="s">
+      <c r="D222" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="D222" s="1" t="s">
+      <c r="E222" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>1057</v>
       </c>
-      <c r="E222" t="s">
-        <v>1596</v>
-      </c>
-      <c r="F222" s="2" t="s">
+      <c r="G222" s="1" t="s">
         <v>1058</v>
-      </c>
-      <c r="G222" s="1" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B223" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C223" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="C223" s="1" t="s">
+      <c r="D223" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="D223" s="1" t="s">
-        <v>1062</v>
-      </c>
       <c r="E223" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>482</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B224" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C224" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="C224" s="1" t="s">
+      <c r="D224" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="D224" s="1" t="s">
+      <c r="E224" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="E224" t="s">
-        <v>1598</v>
-      </c>
-      <c r="F224" s="2" t="s">
+      <c r="G224" s="1" t="s">
         <v>1067</v>
-      </c>
-      <c r="G224" s="1" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B225" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C225" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="C225" s="1" t="s">
+      <c r="D225" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="D225" s="1" t="s">
+      <c r="E225" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F225" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="E225" t="s">
-        <v>1599</v>
-      </c>
-      <c r="F225" s="2" t="s">
+      <c r="G225" s="1" t="s">
         <v>1072</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B226" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C226" s="1" t="s">
         <v>1074</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>1075</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E226" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F226" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G226" s="1" t="s">
         <v>1076</v>
-      </c>
-      <c r="G226" s="1" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B227" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C227" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="C227" s="1" t="s">
+      <c r="D227" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="D227" s="1" t="s">
+      <c r="E227" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F227" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="E227" t="s">
-        <v>1601</v>
-      </c>
-      <c r="F227" s="2" t="s">
+      <c r="G227" s="1" t="s">
         <v>1081</v>
-      </c>
-      <c r="G227" s="1" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B228" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C228" s="1" t="s">
         <v>1083</v>
       </c>
-      <c r="C228" s="1" t="s">
+      <c r="D228" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="D228" s="1" t="s">
+      <c r="E228" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F228" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="E228" t="s">
-        <v>1602</v>
-      </c>
-      <c r="F228" s="2" t="s">
+      <c r="G228" s="1" t="s">
         <v>1086</v>
-      </c>
-      <c r="G228" s="1" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B229" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C229" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="C229" s="1" t="s">
+      <c r="D229" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="D229" s="1" t="s">
-        <v>1090</v>
-      </c>
       <c r="E229" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>732</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B230" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C230" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="C230" s="1" t="s">
+      <c r="D230" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="D230" s="1" t="s">
+      <c r="E230" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F230" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="E230" t="s">
-        <v>1604</v>
-      </c>
-      <c r="F230" s="2" t="s">
+      <c r="G230" s="1" t="s">
         <v>1094</v>
-      </c>
-      <c r="G230" s="1" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B231" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C231" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="C231" s="1" t="s">
+      <c r="D231" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="D231" s="1" t="s">
+      <c r="E231" t="s">
+        <v>1604</v>
+      </c>
+      <c r="F231" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="E231" t="s">
-        <v>1605</v>
-      </c>
-      <c r="F231" s="2" t="s">
+      <c r="G231" s="1" t="s">
         <v>1099</v>
-      </c>
-      <c r="G231" s="1" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B233" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C233" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="C233" s="1" t="s">
+      <c r="D233" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="D233" s="1" t="s">
+      <c r="E233" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F233" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="E233" t="s">
-        <v>1606</v>
-      </c>
-      <c r="F233" s="2" t="s">
+      <c r="G233" s="1" t="s">
         <v>1104</v>
-      </c>
-      <c r="G233" s="1" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B234" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C234" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="C234" s="1" t="s">
+      <c r="D234" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="D234" s="1" t="s">
+      <c r="E234" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F234" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="E234" t="s">
-        <v>1607</v>
-      </c>
-      <c r="F234" s="2" t="s">
+      <c r="G234" s="1" t="s">
         <v>1109</v>
-      </c>
-      <c r="G234" s="1" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B235" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C235" s="1" t="s">
         <v>1111</v>
       </c>
-      <c r="C235" s="1" t="s">
+      <c r="D235" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="D235" s="1" t="s">
+      <c r="E235" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>1113</v>
       </c>
-      <c r="E235" t="s">
-        <v>1608</v>
-      </c>
-      <c r="F235" s="2" t="s">
+      <c r="G235" s="1" t="s">
         <v>1114</v>
-      </c>
-      <c r="G235" s="1" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B236" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C236" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="C236" s="1" t="s">
+      <c r="D236" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="D236" s="1" t="s">
+      <c r="E236" t="s">
+        <v>1608</v>
+      </c>
+      <c r="F236" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="E236" t="s">
-        <v>1609</v>
-      </c>
-      <c r="F236" s="2" t="s">
+      <c r="G236" s="1" t="s">
         <v>1121</v>
-      </c>
-      <c r="G236" s="1" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B237" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C237" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="C237" s="1" t="s">
+      <c r="D237" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="D237" s="1" t="s">
+      <c r="E237" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F237" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="E237" t="s">
-        <v>1610</v>
-      </c>
-      <c r="F237" s="2" t="s">
+      <c r="G237" s="1" t="s">
         <v>1126</v>
-      </c>
-      <c r="G237" s="1" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B238" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C238" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="C238" s="1" t="s">
+      <c r="D238" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="D238" s="1" t="s">
+      <c r="E238" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F238" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="E238" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F238" s="2" t="s">
+      <c r="G238" s="1" t="s">
         <v>1131</v>
-      </c>
-      <c r="G238" s="1" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B239" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C239" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="C239" s="1" t="s">
+      <c r="D239" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="D239" s="1" t="s">
+      <c r="E239" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F239" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="E239" t="s">
-        <v>1515</v>
-      </c>
-      <c r="F239" s="2" t="s">
+      <c r="G239" s="1" t="s">
         <v>1136</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B240" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C240" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="C240" s="1" t="s">
+      <c r="D240" s="1" t="s">
         <v>1139</v>
       </c>
-      <c r="D240" s="1" t="s">
+      <c r="E240" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="E240" t="s">
-        <v>1611</v>
-      </c>
-      <c r="F240" s="2" t="s">
+      <c r="G240" s="1" t="s">
         <v>1141</v>
-      </c>
-      <c r="G240" s="1" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B241" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C241" s="1" t="s">
         <v>1143</v>
-      </c>
-      <c r="C241" s="1" t="s">
-        <v>1144</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E241" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="F241" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G241" s="1" t="s">
         <v>1145</v>
-      </c>
-      <c r="G241" s="1" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B242" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C242" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="C242" s="1" t="s">
+      <c r="D242" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="D242" s="1" t="s">
+      <c r="E242" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F242" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="E242" t="s">
-        <v>1615</v>
-      </c>
-      <c r="F242" s="2" t="s">
+      <c r="G242" s="1" t="s">
         <v>1172</v>
-      </c>
-      <c r="G242" s="1" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B243" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C243" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="C243" s="1" t="s">
+      <c r="D243" s="1" t="s">
         <v>1175</v>
       </c>
-      <c r="D243" s="1" t="s">
+      <c r="E243" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F243" s="2" t="s">
         <v>1176</v>
       </c>
-      <c r="E243" t="s">
-        <v>1616</v>
-      </c>
-      <c r="F243" s="2" t="s">
+      <c r="G243" s="1" t="s">
         <v>1177</v>
-      </c>
-      <c r="G243" s="1" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B244" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C244" s="1" t="s">
         <v>1179</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>1180</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>688</v>
       </c>
       <c r="E244" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="F244" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G244" s="1" t="s">
         <v>1181</v>
-      </c>
-      <c r="G244" s="1" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B245" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C245" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="C245" s="1" t="s">
+      <c r="D245" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="D245" s="1" t="s">
-        <v>1185</v>
-      </c>
       <c r="E245" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B246" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C246" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="C246" s="1" t="s">
+      <c r="D246" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="D246" s="1" t="s">
+      <c r="E246" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F246" s="2" t="s">
         <v>1189</v>
       </c>
-      <c r="E246" t="s">
-        <v>1619</v>
-      </c>
-      <c r="F246" s="2" t="s">
+      <c r="G246" s="1" t="s">
         <v>1190</v>
-      </c>
-      <c r="G246" s="1" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B247" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C247" s="1" t="s">
         <v>1192</v>
       </c>
-      <c r="C247" s="1" t="s">
+      <c r="D247" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="D247" s="1" t="s">
+      <c r="E247" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F247" s="2" t="s">
         <v>1194</v>
       </c>
-      <c r="E247" t="s">
-        <v>1620</v>
-      </c>
-      <c r="F247" s="2" t="s">
+      <c r="G247" s="1" t="s">
         <v>1195</v>
-      </c>
-      <c r="G247" s="1" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B248" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C248" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="C248" s="1" t="s">
+      <c r="D248" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="D248" s="1" t="s">
+      <c r="E248" t="s">
+        <v>1620</v>
+      </c>
+      <c r="F248" s="2" t="s">
         <v>1199</v>
       </c>
-      <c r="E248" t="s">
-        <v>1621</v>
-      </c>
-      <c r="F248" s="2" t="s">
+      <c r="G248" s="1" t="s">
         <v>1200</v>
-      </c>
-      <c r="G248" s="1" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B249" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C249" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="C249" s="1" t="s">
+      <c r="D249" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="D249" s="1" t="s">
+      <c r="E249" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F249" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="E249" t="s">
-        <v>1622</v>
-      </c>
-      <c r="F249" s="2" t="s">
+      <c r="G249" s="1" t="s">
         <v>1205</v>
-      </c>
-      <c r="G249" s="1" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B250" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C250" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="C250" s="1" t="s">
+      <c r="D250" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="D250" s="1" t="s">
+      <c r="E250" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F250" s="2" t="s">
         <v>1209</v>
       </c>
-      <c r="E250" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F250" s="2" t="s">
+      <c r="G250" s="1" t="s">
         <v>1210</v>
-      </c>
-      <c r="G250" s="1" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B251" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C251" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="C251" s="1" t="s">
+      <c r="D251" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="D251" s="1" t="s">
-        <v>1214</v>
-      </c>
       <c r="E251" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="B252" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C252" s="1" t="s">
         <v>1216</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>1217</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E252" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="F252" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G252" s="1" t="s">
         <v>1218</v>
-      </c>
-      <c r="G252" s="1" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B253" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C253" s="1" t="s">
         <v>1220</v>
       </c>
-      <c r="C253" s="1" t="s">
+      <c r="D253" s="1" t="s">
         <v>1221</v>
       </c>
-      <c r="D253" s="1" t="s">
+      <c r="E253" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G253" s="1" t="s">
         <v>1222</v>
-      </c>
-      <c r="E253" t="s">
-        <v>1626</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="G253" s="1" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B254" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C254" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="C254" s="1" t="s">
+      <c r="D254" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="D254" s="1" t="s">
+      <c r="E254" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="E254" t="s">
-        <v>1627</v>
-      </c>
-      <c r="F254" s="2" t="s">
+      <c r="G254" s="1" t="s">
         <v>1227</v>
-      </c>
-      <c r="G254" s="1" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B255" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C255" s="1" t="s">
         <v>1229</v>
       </c>
-      <c r="C255" s="1" t="s">
+      <c r="D255" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="D255" s="1" t="s">
+      <c r="E255" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F255" s="2" t="s">
         <v>1231</v>
       </c>
-      <c r="E255" t="s">
-        <v>1628</v>
-      </c>
-      <c r="F255" s="2" t="s">
+      <c r="G255" s="1" t="s">
         <v>1232</v>
-      </c>
-      <c r="G255" s="1" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B256" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C256" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="C256" s="1" t="s">
+      <c r="D256" s="1" t="s">
         <v>1235</v>
       </c>
-      <c r="D256" s="1" t="s">
+      <c r="E256" t="s">
+        <v>1628</v>
+      </c>
+      <c r="F256" s="2" t="s">
         <v>1236</v>
       </c>
-      <c r="E256" t="s">
-        <v>1629</v>
-      </c>
-      <c r="F256" s="2" t="s">
+      <c r="G256" s="1" t="s">
         <v>1237</v>
-      </c>
-      <c r="G256" s="1" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B257" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C257" s="1" t="s">
         <v>1239</v>
       </c>
-      <c r="C257" s="1" t="s">
+      <c r="D257" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="D257" s="1" t="s">
+      <c r="E257" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F257" s="2" t="s">
         <v>1241</v>
       </c>
-      <c r="E257" t="s">
-        <v>1630</v>
-      </c>
-      <c r="F257" s="2" t="s">
+      <c r="G257" s="1" t="s">
         <v>1242</v>
-      </c>
-      <c r="G257" s="1" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B258" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C258" s="1" t="s">
         <v>1244</v>
       </c>
-      <c r="C258" s="1" t="s">
+      <c r="D258" s="1" t="s">
         <v>1245</v>
       </c>
-      <c r="D258" s="1" t="s">
+      <c r="E258" t="s">
+        <v>1630</v>
+      </c>
+      <c r="F258" s="2" t="s">
         <v>1246</v>
       </c>
-      <c r="E258" t="s">
-        <v>1631</v>
-      </c>
-      <c r="F258" s="2" t="s">
+      <c r="G258" s="1" t="s">
         <v>1247</v>
-      </c>
-      <c r="G258" s="1" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B259" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C259" s="1" t="s">
         <v>1249</v>
       </c>
-      <c r="C259" s="1" t="s">
+      <c r="D259" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="D259" s="1" t="s">
+      <c r="E259" t="s">
+        <v>1631</v>
+      </c>
+      <c r="F259" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="E259" t="s">
-        <v>1632</v>
-      </c>
-      <c r="F259" s="2" t="s">
+      <c r="G259" s="1" t="s">
         <v>1252</v>
-      </c>
-      <c r="G259" s="1" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B260" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C260" s="1" t="s">
         <v>1254</v>
       </c>
-      <c r="C260" s="1" t="s">
+      <c r="D260" s="1" t="s">
         <v>1255</v>
       </c>
-      <c r="D260" s="1" t="s">
+      <c r="E260" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F260" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="E260" t="s">
-        <v>1633</v>
-      </c>
-      <c r="F260" s="2" t="s">
+      <c r="G260" s="1" t="s">
         <v>1257</v>
-      </c>
-      <c r="G260" s="1" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B261" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C261" s="1" t="s">
         <v>1260</v>
       </c>
-      <c r="C261" s="1" t="s">
+      <c r="D261" s="1" t="s">
         <v>1261</v>
       </c>
-      <c r="D261" s="1" t="s">
+      <c r="E261" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F261" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="E261" t="s">
-        <v>1634</v>
-      </c>
-      <c r="F261" s="2" t="s">
+      <c r="G261" s="1" t="s">
         <v>1263</v>
-      </c>
-      <c r="G261" s="1" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B262" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="C262" s="1" t="s">
+      <c r="E262" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="G262" s="1" t="s">
         <v>1403</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>1266</v>
-      </c>
-      <c r="E262" t="s">
-        <v>1651</v>
-      </c>
-      <c r="F262" s="2" t="s">
-        <v>1267</v>
-      </c>
-      <c r="G262" s="1" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B263" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C263" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="C263" s="1" t="s">
+      <c r="D263" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="D263" s="1" t="s">
+      <c r="E263" t="s">
+        <v>1651</v>
+      </c>
+      <c r="F263" s="2" t="s">
         <v>1270</v>
       </c>
-      <c r="E263" t="s">
-        <v>1652</v>
-      </c>
-      <c r="F263" s="2" t="s">
+      <c r="G263" s="1" t="s">
         <v>1271</v>
-      </c>
-      <c r="G263" s="1" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B264" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C264" s="1" t="s">
         <v>1273</v>
       </c>
-      <c r="C264" s="1" t="s">
-        <v>1274</v>
-      </c>
       <c r="D264" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E264" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B265" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C265" s="1" t="s">
         <v>1276</v>
       </c>
-      <c r="C265" s="1" t="s">
+      <c r="D265" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="D265" s="1" t="s">
+      <c r="E265" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F265" s="2" t="s">
         <v>1278</v>
       </c>
-      <c r="E265" t="s">
-        <v>1522</v>
-      </c>
-      <c r="F265" s="2" t="s">
+      <c r="G265" s="1" t="s">
         <v>1279</v>
-      </c>
-      <c r="G265" s="1" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B266" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C266" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="C266" s="1" t="s">
+      <c r="D266" s="1" t="s">
         <v>1282</v>
       </c>
-      <c r="D266" s="1" t="s">
+      <c r="E266" t="s">
+        <v>1635</v>
+      </c>
+      <c r="F266" s="2" t="s">
         <v>1283</v>
       </c>
-      <c r="E266" t="s">
-        <v>1636</v>
-      </c>
-      <c r="F266" s="2" t="s">
+      <c r="G266" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="G266" s="1" t="s">
-        <v>1285</v>
-      </c>
       <c r="L266" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B267" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C267" s="1" t="s">
         <v>1286</v>
       </c>
-      <c r="C267" s="1" t="s">
+      <c r="D267" s="1" t="s">
         <v>1287</v>
       </c>
-      <c r="D267" s="1" t="s">
+      <c r="E267" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F267" s="2" t="s">
         <v>1288</v>
       </c>
-      <c r="E267" t="s">
-        <v>1637</v>
-      </c>
-      <c r="F267" s="2" t="s">
+      <c r="G267" s="1" t="s">
         <v>1289</v>
-      </c>
-      <c r="G267" s="1" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B268" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C268" s="1" t="s">
         <v>1291</v>
       </c>
-      <c r="C268" s="1" t="s">
+      <c r="D268" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="D268" s="1" t="s">
+      <c r="E268" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F268" s="2" t="s">
         <v>1293</v>
       </c>
-      <c r="E268" t="s">
-        <v>1638</v>
-      </c>
-      <c r="F268" s="2" t="s">
+      <c r="G268" s="1" t="s">
         <v>1294</v>
-      </c>
-      <c r="G268" s="1" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B269" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C269" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="C269" s="1" t="s">
+      <c r="D269" s="1" t="s">
         <v>1297</v>
       </c>
-      <c r="D269" s="1" t="s">
+      <c r="E269" t="s">
+        <v>1638</v>
+      </c>
+      <c r="F269" s="2" t="s">
         <v>1298</v>
       </c>
-      <c r="E269" t="s">
-        <v>1639</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>1299</v>
-      </c>
       <c r="G269" s="1" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B270" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C270" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="C270" s="1" t="s">
+      <c r="D270" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="D270" s="1" t="s">
+      <c r="E270" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F270" s="2" t="s">
         <v>1302</v>
       </c>
-      <c r="E270" t="s">
-        <v>1640</v>
-      </c>
-      <c r="F270" s="2" t="s">
+      <c r="G270" s="1" t="s">
         <v>1303</v>
-      </c>
-      <c r="G270" s="1" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B271" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C271" s="1" t="s">
         <v>1305</v>
       </c>
-      <c r="C271" s="1" t="s">
+      <c r="D271" s="1" t="s">
         <v>1306</v>
       </c>
-      <c r="D271" s="1" t="s">
+      <c r="E271" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F271" s="2" t="s">
         <v>1307</v>
       </c>
-      <c r="E271" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F271" s="2" t="s">
+      <c r="G271" s="1" t="s">
         <v>1308</v>
-      </c>
-      <c r="G271" s="1" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B272" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C272" s="1" t="s">
         <v>1310</v>
       </c>
-      <c r="C272" s="1" t="s">
+      <c r="D272" s="1" t="s">
         <v>1311</v>
       </c>
-      <c r="D272" s="1" t="s">
+      <c r="E272" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F272" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="E272" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F272" s="2" t="s">
+      <c r="G272" s="1" t="s">
         <v>1313</v>
-      </c>
-      <c r="G272" s="1" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B273" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C273" s="1" t="s">
         <v>1315</v>
       </c>
-      <c r="C273" s="1" t="s">
+      <c r="D273" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="D273" s="1" t="s">
+      <c r="E273" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F273" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G273" s="1" t="s">
         <v>1317</v>
-      </c>
-      <c r="E273" t="s">
-        <v>1641</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>1259</v>
-      </c>
-      <c r="G273" s="1" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B274" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C274" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="C274" s="1" t="s">
+      <c r="D274" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="D274" s="1" t="s">
+      <c r="E274" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F274" s="2" t="s">
         <v>1321</v>
       </c>
-      <c r="E274" t="s">
-        <v>1481</v>
-      </c>
-      <c r="F274" s="2" t="s">
+      <c r="G274" s="1" t="s">
         <v>1322</v>
-      </c>
-      <c r="G274" s="1" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="275" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B275" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C275" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="C275" s="1" t="s">
+      <c r="D275" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="D275" s="1" t="s">
+      <c r="E275" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>1326</v>
       </c>
-      <c r="E275" t="s">
-        <v>1481</v>
-      </c>
-      <c r="F275" s="2" t="s">
+      <c r="G275" s="1" t="s">
         <v>1327</v>
-      </c>
-      <c r="G275" s="1" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="276" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B276" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C276" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="C276" s="1" t="s">
+      <c r="D276" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="D276" s="1" t="s">
+      <c r="E276" t="s">
+        <v>1641</v>
+      </c>
+      <c r="F276" s="2" t="s">
         <v>1331</v>
       </c>
-      <c r="E276" t="s">
-        <v>1642</v>
-      </c>
-      <c r="F276" s="2" t="s">
+      <c r="G276" s="1" t="s">
         <v>1332</v>
-      </c>
-      <c r="G276" s="1" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B277" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C277" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="C277" s="1" t="s">
+      <c r="D277" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="D277" s="1" t="s">
+      <c r="E277" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F277" s="2" t="s">
         <v>1336</v>
       </c>
-      <c r="E277" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F277" s="2" t="s">
+      <c r="G277" s="1" t="s">
         <v>1337</v>
-      </c>
-      <c r="G277" s="1" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B278" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C278" s="1" t="s">
         <v>1339</v>
       </c>
-      <c r="C278" s="1" t="s">
+      <c r="D278" s="1" t="s">
         <v>1340</v>
       </c>
-      <c r="D278" s="1" t="s">
+      <c r="E278" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>1341</v>
       </c>
-      <c r="E278" t="s">
-        <v>1479</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>1342</v>
-      </c>
       <c r="G278" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B279" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C279" s="1" t="s">
         <v>1343</v>
       </c>
-      <c r="C279" s="1" t="s">
+      <c r="D279" s="1" t="s">
         <v>1344</v>
       </c>
-      <c r="D279" s="1" t="s">
+      <c r="E279" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F279" s="2" t="s">
         <v>1345</v>
       </c>
-      <c r="E279" t="s">
-        <v>1517</v>
-      </c>
-      <c r="F279" s="2" t="s">
+      <c r="G279" s="1" t="s">
         <v>1346</v>
-      </c>
-      <c r="G279" s="1" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B280" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C280" s="1" t="s">
         <v>1348</v>
       </c>
-      <c r="C280" s="1" t="s">
+      <c r="D280" s="1" t="s">
         <v>1349</v>
       </c>
-      <c r="D280" s="1" t="s">
+      <c r="E280" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F280" s="2" t="s">
         <v>1350</v>
       </c>
-      <c r="E280" t="s">
-        <v>1643</v>
-      </c>
-      <c r="F280" s="2" t="s">
+      <c r="G280" s="1" t="s">
         <v>1351</v>
-      </c>
-      <c r="G280" s="1" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B281" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C281" s="1" t="s">
         <v>1353</v>
       </c>
-      <c r="C281" s="1" t="s">
+      <c r="D281" s="1" t="s">
         <v>1354</v>
       </c>
-      <c r="D281" s="1" t="s">
-        <v>1355</v>
-      </c>
       <c r="E281" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="F281" s="2" t="s">
         <v>154</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B282" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C282" s="1" t="s">
         <v>1357</v>
       </c>
-      <c r="C282" s="1" t="s">
+      <c r="D282" s="1" t="s">
         <v>1358</v>
       </c>
-      <c r="D282" s="1" t="s">
+      <c r="E282" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F282" s="2" t="s">
         <v>1359</v>
       </c>
-      <c r="E282" t="s">
-        <v>1645</v>
-      </c>
-      <c r="F282" s="2" t="s">
+      <c r="G282" s="1" t="s">
         <v>1360</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>1361</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B283" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C283" s="1" t="s">
         <v>1362</v>
       </c>
-      <c r="C283" s="1" t="s">
+      <c r="D283" s="1" t="s">
         <v>1363</v>
       </c>
-      <c r="D283" s="1" t="s">
+      <c r="E283" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F283" s="2" t="s">
         <v>1364</v>
       </c>
-      <c r="E283" t="s">
-        <v>1646</v>
-      </c>
-      <c r="F283" s="2" t="s">
+      <c r="G283" s="1" t="s">
         <v>1365</v>
-      </c>
-      <c r="G283" s="1" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="284" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B284" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D284" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="C284" s="1" t="s">
+      <c r="E284" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F284" s="2" t="s">
         <v>1367</v>
       </c>
-      <c r="D284" s="1" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E284" t="s">
-        <v>1647</v>
-      </c>
-      <c r="F284" s="2" t="s">
+      <c r="G284" s="1" t="s">
         <v>1368</v>
-      </c>
-      <c r="G284" s="1" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B285" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="C285" s="1" t="s">
+      <c r="E285" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F285" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G285" s="1" t="s">
         <v>1709</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>1371</v>
-      </c>
-      <c r="E285" t="s">
-        <v>1501</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>1372</v>
-      </c>
-      <c r="G285" s="1" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B286" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C286" s="1" t="s">
         <v>1373</v>
       </c>
-      <c r="C286" s="1" t="s">
+      <c r="D286" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="D286" s="1" t="s">
+      <c r="E286" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F286" s="2" t="s">
         <v>1375</v>
       </c>
-      <c r="E286" t="s">
-        <v>1648</v>
-      </c>
-      <c r="F286" s="2" t="s">
+      <c r="G286" s="1" t="s">
         <v>1376</v>
-      </c>
-      <c r="G286" s="1" t="s">
-        <v>1377</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B287" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C287" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="C287" s="1" t="s">
+      <c r="D287" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="D287" s="1" t="s">
+      <c r="E287" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F287" s="2" t="s">
         <v>1380</v>
       </c>
-      <c r="E287" t="s">
-        <v>1522</v>
-      </c>
-      <c r="F287" s="2" t="s">
+      <c r="G287" s="1" t="s">
         <v>1381</v>
-      </c>
-      <c r="G287" s="1" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B288" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C288" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D288" s="1" t="s">
         <v>1383</v>
       </c>
-      <c r="D288" s="1" t="s">
+      <c r="E288" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F288" s="2" t="s">
         <v>1384</v>
       </c>
-      <c r="E288" t="s">
-        <v>1649</v>
-      </c>
-      <c r="F288" s="2" t="s">
+      <c r="G288" s="1" t="s">
         <v>1385</v>
-      </c>
-      <c r="G288" s="1" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B289" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C289" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="C289" s="1" t="s">
+      <c r="D289" s="1" t="s">
         <v>1148</v>
       </c>
-      <c r="D289" s="1" t="s">
+      <c r="E289" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F289" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="E289" t="s">
-        <v>1613</v>
-      </c>
-      <c r="F289" s="2" t="s">
+      <c r="G289" s="1" t="s">
         <v>1150</v>
-      </c>
-      <c r="G289" s="1" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" s="5" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B290" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C290" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="C290" s="7" t="s">
+      <c r="D290" s="7" t="s">
         <v>1165</v>
       </c>
-      <c r="D290" s="7" t="s">
+      <c r="E290" s="6" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F290" s="8" t="s">
         <v>1166</v>
       </c>
-      <c r="E290" s="6" t="s">
-        <v>1614</v>
-      </c>
-      <c r="F290" s="8" t="s">
+      <c r="G290" s="7" t="s">
         <v>1167</v>
-      </c>
-      <c r="G290" s="7" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B291" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C291" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="C291" s="1" t="s">
+      <c r="D291" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="D291" s="1" t="s">
+      <c r="E291" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F291" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="E291" t="s">
-        <v>1483</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>1155</v>
-      </c>
       <c r="G291" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B292" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C292" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="C292" s="1" t="s">
+      <c r="D292" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="D292" s="1" t="s">
+      <c r="E292" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F292" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="E292" t="s">
-        <v>1635</v>
-      </c>
-      <c r="F292" s="2" t="s">
+      <c r="G292" s="1" t="s">
         <v>1159</v>
-      </c>
-      <c r="G292" s="1" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B293" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C293" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="C293" s="1" t="s">
+      <c r="D293" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="D293" s="1" t="s">
-        <v>1163</v>
-      </c>
       <c r="E293" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="F293" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="G293" s="1" t="s">
         <v>1706</v>
-      </c>
-      <c r="G293" s="1" t="s">
-        <v>1707</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B294" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C294" s="1" t="s">
         <v>1713</v>
       </c>
-      <c r="C294" s="1" t="s">
+      <c r="D294" s="1" t="s">
         <v>1714</v>
       </c>
-      <c r="D294" s="1" t="s">
+      <c r="E294" t="s">
+        <v>1717</v>
+      </c>
+      <c r="F294" s="2" t="s">
         <v>1715</v>
       </c>
-      <c r="E294" t="s">
+      <c r="G294" t="s">
         <v>1718</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>1716</v>
-      </c>
-      <c r="G294" t="s">
-        <v>1719</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Russian_Words_Cards.xlsx
+++ b/public/data/Russian_Words_Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B9969C-21F0-4133-BFD2-35D794900658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4554F4C-F372-493B-BAE7-55468E077B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="1722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="1722">
   <si>
     <t>Topic</t>
   </si>
@@ -161,9 +161,6 @@
     <t>יציאה</t>
   </si>
   <si>
-    <t>Картошка</t>
-  </si>
-  <si>
     <t>תפוח אדמה</t>
   </si>
   <si>
@@ -737,9 +734,6 @@
     <t>butter + bread</t>
   </si>
   <si>
-    <t>בּוּטֶרְבְּרוֹד זה בעצם Butter על Bread עם כל מה שבא לך באמצע!</t>
-  </si>
-  <si>
     <t>винегрет</t>
   </si>
   <si>
@@ -2253,9 +2247,6 @@
   </si>
   <si>
     <t>סמיילי שנון זה דבר סְמִישְׁנוֹ</t>
-  </si>
-  <si>
-    <t>Усталый</t>
   </si>
   <si>
     <t>אוּסְטָלִי</t>
@@ -3816,9 +3807,6 @@
     <t>מילה</t>
   </si>
   <si>
-    <t>Газета</t>
-  </si>
-  <si>
     <t>גַאזֵטָה</t>
   </si>
   <si>
@@ -3831,18 +3819,12 @@
     <t>פעם הגָאזֵטָה היה רק גזע של עץ, אחר כך הוא הפך לנייר - ובסוף מצא את עצמו על השולחן שלנו, מלא בחדשות</t>
   </si>
   <si>
-    <t>Грудь</t>
-  </si>
-  <si>
     <t>חזה</t>
   </si>
   <si>
     <t>לגרד</t>
   </si>
   <si>
-    <t>Спина</t>
-  </si>
-  <si>
     <t>סְפִּינָה</t>
   </si>
   <si>
@@ -3855,18 +3837,12 @@
     <t>כשאני צף בים על הסְפִּינָה אני מרגיש כמו ספינה ששטה על הים.</t>
   </si>
   <si>
-    <t>Сад</t>
-  </si>
-  <si>
     <t>סָד</t>
   </si>
   <si>
     <t xml:space="preserve"> כששיחקנו מחבואים, התחבאתי  טוב בסָד ואחד לא גילה את הסוֹד שלי  - מקום המחבוא המושלם</t>
   </si>
   <si>
-    <t>Деньги</t>
-  </si>
-  <si>
     <t>דֵנְגִי</t>
   </si>
   <si>
@@ -3879,9 +3855,6 @@
     <t xml:space="preserve"> הוא כל כך רצה עוד דֵנְגִי, שהוא לא שם לב שהוא נכנס ל-danger עם האנשים הלא נכונים</t>
   </si>
   <si>
-    <t>Камин</t>
-  </si>
-  <si>
     <t>קָאמִין</t>
   </si>
   <si>
@@ -3894,9 +3867,6 @@
     <t>כדי לבנות קמין טוב, חייבים להשתמש בקָאמִין חסינה לחום</t>
   </si>
   <si>
-    <t>Письмо</t>
-  </si>
-  <si>
     <t>פִּיסְמוֹ</t>
   </si>
   <si>
@@ -3909,9 +3879,6 @@
     <t>הרבה פעמים כותבים פִּיסְמוֹ כדי להביא שלום או פיוס בין אנשים.</t>
   </si>
   <si>
-    <t>Конверт</t>
-  </si>
-  <si>
     <t>קָנְבֵרְט</t>
   </si>
   <si>
@@ -3924,9 +3891,6 @@
     <t xml:space="preserve"> הייתי צריך לשלוח אימייל, אבל החלטתי ל-convert אותו ולשים אותו בתוך קָנְבֵּרְט</t>
   </si>
   <si>
-    <t>Лицо</t>
-  </si>
-  <si>
     <t>לִיצוֹ</t>
   </si>
   <si>
@@ -3936,9 +3900,6 @@
     <t>ליצן</t>
   </si>
   <si>
-    <t>Палец</t>
-  </si>
-  <si>
     <t>פָּאלֶץ</t>
   </si>
   <si>
@@ -3951,9 +3912,6 @@
     <t>רציתי לבדוק אם המדף ישר, אז הנחתי עליו פָּאלֶץ כמו פלס!</t>
   </si>
   <si>
-    <t>Лёд</t>
-  </si>
-  <si>
     <t>לִיוֹד</t>
   </si>
   <si>
@@ -3966,9 +3924,6 @@
     <t>נפלתי על הלְיוֹד, קיבלתי שריטה, ומיד שמתי עליה יוד</t>
   </si>
   <si>
-    <t>Мост</t>
-  </si>
-  <si>
     <t>מוֹסְט</t>
   </si>
   <si>
@@ -3981,9 +3936,6 @@
     <t>אם אתה רוצה לעבור לצד השני של הנהר, אתה must לעבור על המוֹסְט</t>
   </si>
   <si>
-    <t>Мыло</t>
-  </si>
-  <si>
     <t>מִילָה</t>
   </si>
   <si>
@@ -3993,9 +3945,6 @@
     <t>אם אתה אומר מילה לא יפה, אמא תגיד לך לשטוף את הפה עם מִילָה</t>
   </si>
   <si>
-    <t>Костёр</t>
-  </si>
-  <si>
     <t>קוֹסְטְיוֹר</t>
   </si>
   <si>
@@ -4006,9 +3955,6 @@
   </si>
   <si>
     <t>ישבנו סביב הקָסְטְיוֹר, והפעלנו את הקסטה עם שירי קומזיץ ישנים</t>
-  </si>
-  <si>
-    <t>Огонь</t>
   </si>
   <si>
     <t>אָגוֹן</t>
@@ -4046,9 +3992,6 @@
     </r>
   </si>
   <si>
-    <t>Рад</t>
-  </si>
-  <si>
     <t>רָאד</t>
   </si>
   <si>
@@ -4082,9 +4025,6 @@
       </rPr>
       <t xml:space="preserve"> משמחה</t>
     </r>
-  </si>
-  <si>
-    <t>Раз</t>
   </si>
   <si>
     <t>רַז</t>
@@ -4133,9 +4073,6 @@
     </r>
   </si>
   <si>
-    <t>Рано</t>
-  </si>
-  <si>
     <t>רָנָה</t>
   </si>
   <si>
@@ -4143,9 +4080,6 @@
   </si>
   <si>
     <t>Run</t>
-  </si>
-  <si>
-    <t>Поздно</t>
   </si>
   <si>
     <t>פּוֹזְדְנָה</t>
@@ -4183,9 +4117,6 @@
     </r>
   </si>
   <si>
-    <t>Фамилия</t>
-  </si>
-  <si>
     <t>פַאמִילִיָה</t>
   </si>
   <si>
@@ -4196,9 +4127,6 @@
   </si>
   <si>
     <t>כל הFamily שלי חולקים את אותה פָאמִילְיָה</t>
-  </si>
-  <si>
-    <t>Шум</t>
   </si>
   <si>
     <t>שוּם</t>
@@ -4233,9 +4161,6 @@
     </r>
   </si>
   <si>
-    <t>Запах</t>
-  </si>
-  <si>
     <t>זָאפַּח</t>
   </si>
   <si>
@@ -4345,9 +4270,6 @@
     <t>אם אתה רוצה tan מושלם, כדאי לך לזוז מה- טֵן</t>
   </si>
   <si>
-    <t>Бедный</t>
-  </si>
-  <si>
     <t>בֵּדְנִי</t>
   </si>
   <si>
@@ -5437,6 +5359,84 @@
   </si>
   <si>
     <t>לכל סְטְרָנָה תרבות משלה. לפעמים כשמבקרים זה מרגיש קצת strange</t>
+  </si>
+  <si>
+    <t>בּוּטֶרְבְּרוֹד זה בעצם Butter על Bread עם כל מה שבא לך!</t>
+  </si>
+  <si>
+    <t>картошка</t>
+  </si>
+  <si>
+    <t>газета</t>
+  </si>
+  <si>
+    <t>грудь</t>
+  </si>
+  <si>
+    <t>сад</t>
+  </si>
+  <si>
+    <t>спина</t>
+  </si>
+  <si>
+    <t>камин</t>
+  </si>
+  <si>
+    <t>конверт</t>
+  </si>
+  <si>
+    <t>деньги</t>
+  </si>
+  <si>
+    <t>письмо</t>
+  </si>
+  <si>
+    <t>палец</t>
+  </si>
+  <si>
+    <t>лицо</t>
+  </si>
+  <si>
+    <t>лёд</t>
+  </si>
+  <si>
+    <t>мост</t>
+  </si>
+  <si>
+    <t>мыло</t>
+  </si>
+  <si>
+    <t>костёр</t>
+  </si>
+  <si>
+    <t>огонь</t>
+  </si>
+  <si>
+    <t>шум</t>
+  </si>
+  <si>
+    <t>фамилия</t>
+  </si>
+  <si>
+    <t>усталый</t>
+  </si>
+  <si>
+    <t>рано</t>
+  </si>
+  <si>
+    <t>раз</t>
+  </si>
+  <si>
+    <t>рад</t>
+  </si>
+  <si>
+    <t>поздно</t>
+  </si>
+  <si>
+    <t>запах</t>
+  </si>
+  <si>
+    <t>бедный</t>
   </si>
 </sst>
 </file>
@@ -5835,7 +5835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L294"/>
+  <dimension ref="A1:L293"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -5852,6738 +5852,6744 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1652</v>
+        <v>1626</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1407</v>
+        <v>1381</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1406</v>
+        <v>1380</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1409</v>
+        <v>1383</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1405</v>
+        <v>1379</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1404</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1387</v>
+        <v>1365</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>894</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>895</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1410</v>
+        <v>896</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1542</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>19</v>
+        <v>897</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>898</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1411</v>
+        <v>1396</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>28</v>
+        <v>163</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1408</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1387</v>
+        <v>1365</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>918</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>919</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1413</v>
+        <v>920</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1547</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1680</v>
+        <v>921</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1681</v>
+        <v>922</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1387</v>
+        <v>1364</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>510</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>511</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1414</v>
+        <v>512</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1478</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>513</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1704</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>1387</v>
+        <v>1367</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>1721</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>1352</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1415</v>
+        <v>1353</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1495</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>40</v>
+        <v>1354</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1670</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1387</v>
+        <v>1365</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>884</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1675</v>
+        <v>885</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>1416</v>
+        <v>886</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1540</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>43</v>
+        <v>887</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>44</v>
+        <v>888</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1387</v>
+        <v>1364</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>1092</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1671</v>
+        <v>1093</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1417</v>
+        <v>1094</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1578</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>6</v>
+        <v>1095</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1672</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1387</v>
+        <v>1366</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>1017</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>48</v>
+        <v>1018</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1418</v>
+        <v>1019</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1488</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>50</v>
+        <v>1020</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>51</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1387</v>
+        <v>1363</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>696</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>53</v>
+        <v>697</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>1419</v>
+        <v>272</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1508</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1683</v>
+        <v>698</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1682</v>
+        <v>699</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1676</v>
+        <v>133</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1420</v>
+        <v>1409</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1677</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1387</v>
+        <v>1366</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>1026</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>59</v>
+        <v>1027</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>1421</v>
+        <v>1028</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1564</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1678</v>
+        <v>1029</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1679</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1387</v>
+        <v>1373</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>1240</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>62</v>
+        <v>1241</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>1422</v>
+        <v>1242</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1604</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>64</v>
+        <v>1243</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>65</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1387</v>
+        <v>1364</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>574</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>67</v>
+        <v>575</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>1423</v>
+        <v>576</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1491</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>577</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>70</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>228</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>72</v>
+        <v>229</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>73</v>
+        <v>230</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>74</v>
+        <v>231</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>75</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1387</v>
+        <v>1362</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>341</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1425</v>
+        <v>1446</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>79</v>
+        <v>344</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>80</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1426</v>
+        <v>1420</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1387</v>
+        <v>1363</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>683</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>87</v>
+        <v>684</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>1427</v>
+        <v>685</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1506</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>89</v>
+        <v>686</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>90</v>
+        <v>687</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1387</v>
+        <v>1365</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>933</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>92</v>
+        <v>934</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>1428</v>
+        <v>935</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1549</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>94</v>
+        <v>936</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>95</v>
+        <v>937</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1387</v>
+        <v>1370</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>1152</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>97</v>
+        <v>1153</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>1429</v>
+        <v>1154</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1608</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>99</v>
+        <v>1155</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1665</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1387</v>
+        <v>1370</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>1175</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>101</v>
+        <v>1176</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>1446</v>
+        <v>686</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1590</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>103</v>
+        <v>1177</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>104</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1387</v>
+        <v>1363</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>406</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1673</v>
+        <v>407</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>106</v>
+        <v>408</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1430</v>
+        <v>1457</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>107</v>
+        <v>409</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1674</v>
+        <v>410</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1387</v>
+        <v>1364</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>534</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>109</v>
+        <v>535</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>1431</v>
+        <v>536</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1483</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>112</v>
+        <v>537</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>114</v>
+        <v>233</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>115</v>
+        <v>234</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>116</v>
+        <v>235</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>117</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1433</v>
+        <v>1399</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1430</v>
+        <v>1417</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1387</v>
+        <v>1363</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>688</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>129</v>
+        <v>689</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>1434</v>
+        <v>690</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1507</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>131</v>
+        <v>691</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>132</v>
+        <v>692</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1435</v>
+        <v>1393</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>136</v>
+        <v>1657</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>137</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1387</v>
+        <v>1366</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>1031</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>139</v>
+        <v>1032</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>1436</v>
+        <v>1033</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1565</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>141</v>
+        <v>1034</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>142</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1387</v>
+        <v>1365</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>810</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>144</v>
+        <v>811</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>1437</v>
+        <v>812</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1525</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>146</v>
+        <v>813</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>147</v>
+        <v>814</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1387</v>
+        <v>1363</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>665</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>149</v>
+        <v>666</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>1438</v>
+        <v>667</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1464</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>151</v>
+        <v>668</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1664</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1387</v>
+        <v>1363</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>673</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>153</v>
+        <v>674</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>1439</v>
+        <v>675</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1504</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>155</v>
+        <v>676</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>156</v>
+        <v>677</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1387</v>
+        <v>1372</v>
       </c>
       <c r="B34" t="s">
-        <v>157</v>
+        <v>1212</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>158</v>
+        <v>1213</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>1440</v>
+        <v>3</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1598</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>160</v>
+        <v>1214</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>161</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1387</v>
+        <v>1363</v>
       </c>
       <c r="B35" t="s">
-        <v>162</v>
+        <v>434</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>163</v>
+        <v>435</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>1441</v>
+        <v>436</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1463</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>165</v>
+        <v>437</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>166</v>
+        <v>438</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1387</v>
+        <v>1375</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>1698</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>168</v>
+        <v>1256</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>1442</v>
+        <v>1257</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1607</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>169</v>
+        <v>1258</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>170</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1387</v>
+        <v>1364</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>469</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>172</v>
+        <v>470</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>1443</v>
+        <v>471</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1469</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>174</v>
+        <v>472</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>175</v>
+        <v>473</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1387</v>
+        <v>1363</v>
       </c>
       <c r="B38" t="s">
-        <v>176</v>
+        <v>429</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>177</v>
+        <v>430</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>178</v>
+        <v>431</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1444</v>
+        <v>1459</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>5</v>
+        <v>432</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>179</v>
+        <v>433</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1387</v>
+        <v>1365</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>938</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>181</v>
+        <v>939</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>1445</v>
+        <v>940</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1550</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>183</v>
+        <v>941</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>184</v>
+        <v>942</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1387</v>
+        <v>1366</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>1046</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>186</v>
+        <v>1047</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>1447</v>
+        <v>1048</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1568</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>188</v>
+        <v>1049</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>189</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1387</v>
+        <v>1366</v>
       </c>
       <c r="B41" t="s">
-        <v>190</v>
+        <v>968</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>191</v>
+        <v>969</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>1448</v>
+        <v>970</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1555</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>193</v>
+        <v>971</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>194</v>
+        <v>972</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>1449</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="G42" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B43" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>201</v>
+        <v>255</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1450</v>
+        <v>1438</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B44" t="s">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>206</v>
+        <v>157</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1451</v>
+        <v>1414</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1387</v>
+        <v>1370</v>
       </c>
       <c r="B45" t="s">
-        <v>210</v>
+        <v>1188</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>211</v>
+        <v>1189</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>1653</v>
+        <v>1190</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1593</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>213</v>
+        <v>1191</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1663</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1387</v>
+        <v>1367</v>
       </c>
       <c r="B46" t="s">
-        <v>214</v>
+        <v>1699</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>215</v>
+        <v>1376</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>1452</v>
+        <v>1260</v>
+      </c>
+      <c r="E46" t="s">
+        <v>1624</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>217</v>
+        <v>1261</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>218</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1387</v>
+        <v>1367</v>
       </c>
       <c r="B47" t="s">
-        <v>219</v>
+        <v>723</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>220</v>
+        <v>724</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>1654</v>
+        <v>725</v>
+      </c>
+      <c r="E47" t="s">
+        <v>1510</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>222</v>
+        <v>726</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>223</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1387</v>
+        <v>1361</v>
       </c>
       <c r="B48" t="s">
-        <v>224</v>
+        <v>90</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>225</v>
+        <v>91</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>226</v>
+        <v>92</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1453</v>
+        <v>1402</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>227</v>
+        <v>93</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>228</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1387</v>
+        <v>1367</v>
       </c>
       <c r="B49" t="s">
-        <v>229</v>
+        <v>1686</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>230</v>
+        <v>1687</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>1454</v>
+        <v>1688</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1691</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>233</v>
+        <v>1689</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1692</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1387</v>
+        <v>1363</v>
       </c>
       <c r="B50" t="s">
-        <v>234</v>
+        <v>693</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>235</v>
+        <v>694</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>1455</v>
+        <v>695</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1508</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>237</v>
+        <v>1674</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>238</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1387</v>
+        <v>1364</v>
       </c>
       <c r="B51" t="s">
-        <v>239</v>
+        <v>579</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>240</v>
+        <v>580</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>1456</v>
+        <v>581</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1492</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>242</v>
+        <v>12</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>243</v>
+        <v>582</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1387</v>
+        <v>1362</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>302</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>245</v>
+        <v>303</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>246</v>
+        <v>304</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1457</v>
+        <v>1442</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>248</v>
+        <v>306</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1387</v>
+        <v>1364</v>
       </c>
       <c r="B53" t="s">
-        <v>249</v>
+        <v>506</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>250</v>
+        <v>507</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>1435</v>
+        <v>508</v>
+      </c>
+      <c r="E53" t="s">
+        <v>1477</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>1667</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1666</v>
+        <v>509</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1387</v>
+        <v>1363</v>
       </c>
       <c r="B54" t="s">
-        <v>252</v>
+        <v>401</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>253</v>
+        <v>402</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>254</v>
+        <v>403</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1463</v>
+        <v>1456</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>255</v>
+        <v>404</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1668</v>
+        <v>405</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1387</v>
+        <v>1374</v>
       </c>
       <c r="B55" t="s">
-        <v>256</v>
+        <v>1704</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>257</v>
+        <v>1268</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>1464</v>
+        <v>1269</v>
+      </c>
+      <c r="E55" t="s">
+        <v>1495</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>259</v>
+        <v>1270</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>260</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1388</v>
+        <v>1362</v>
       </c>
       <c r="B56" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1458</v>
+        <v>1436</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1388</v>
+        <v>1370</v>
       </c>
       <c r="B57" t="s">
-        <v>266</v>
+        <v>1165</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>267</v>
+        <v>1166</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>1459</v>
+        <v>1167</v>
+      </c>
+      <c r="E57" t="s">
+        <v>1588</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>269</v>
+        <v>1168</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>270</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1388</v>
+        <v>1366</v>
       </c>
       <c r="B58" t="s">
-        <v>271</v>
+        <v>978</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>272</v>
+        <v>979</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>1460</v>
+        <v>980</v>
+      </c>
+      <c r="E58" t="s">
+        <v>1440</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>274</v>
+        <v>981</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>275</v>
+        <v>982</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1388</v>
+        <v>1366</v>
       </c>
       <c r="B59" t="s">
-        <v>276</v>
+        <v>1003</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>277</v>
+        <v>1004</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>1461</v>
+        <v>1005</v>
+      </c>
+      <c r="E59" t="s">
+        <v>1556</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>279</v>
+        <v>1006</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>280</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1388</v>
+        <v>1373</v>
       </c>
       <c r="B60" t="s">
-        <v>281</v>
+        <v>1230</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>282</v>
+        <v>1231</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>1462</v>
+        <v>1232</v>
+      </c>
+      <c r="E60" t="s">
+        <v>1602</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>284</v>
+        <v>1233</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>285</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1388</v>
+        <v>1364</v>
       </c>
       <c r="B61" t="s">
-        <v>286</v>
+        <v>492</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>287</v>
+        <v>493</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>1465</v>
+        <v>494</v>
+      </c>
+      <c r="E61" t="s">
+        <v>1474</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>289</v>
+        <v>495</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>290</v>
+        <v>496</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1388</v>
+        <v>1362</v>
       </c>
       <c r="B62" t="s">
-        <v>291</v>
+        <v>355</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>292</v>
+        <v>356</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>293</v>
+        <v>357</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1466</v>
+        <v>1449</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>295</v>
+        <v>359</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1388</v>
+        <v>1361</v>
       </c>
       <c r="B63" t="s">
-        <v>296</v>
+        <v>166</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>297</v>
+        <v>167</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1486</v>
+        <v>10</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1466</v>
+        <v>1416</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>298</v>
+        <v>168</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>299</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1388</v>
+        <v>1365</v>
       </c>
       <c r="B64" t="s">
-        <v>300</v>
+        <v>834</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>301</v>
+        <v>835</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>1467</v>
+        <v>836</v>
+      </c>
+      <c r="E64" t="s">
+        <v>1530</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>2</v>
+        <v>837</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>303</v>
+        <v>838</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1388</v>
+        <v>1364</v>
       </c>
       <c r="B65" t="s">
-        <v>304</v>
+        <v>545</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>305</v>
+        <v>546</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>1468</v>
+        <v>547</v>
+      </c>
+      <c r="E65" t="s">
+        <v>1432</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>307</v>
+        <v>548</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>308</v>
+        <v>549</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1388</v>
+        <v>1364</v>
       </c>
       <c r="B66" t="s">
-        <v>309</v>
+        <v>569</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>310</v>
+        <v>570</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>1487</v>
+        <v>571</v>
+      </c>
+      <c r="E66" t="s">
+        <v>1490</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>312</v>
+        <v>572</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>313</v>
+        <v>573</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1388</v>
+        <v>1373</v>
       </c>
       <c r="B67" t="s">
-        <v>314</v>
+        <v>1235</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>315</v>
+        <v>1236</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>1469</v>
+        <v>1237</v>
+      </c>
+      <c r="E67" t="s">
+        <v>1603</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>317</v>
+        <v>1238</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>318</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1388</v>
+        <v>1364</v>
       </c>
       <c r="B68" t="s">
-        <v>319</v>
+        <v>564</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>320</v>
+        <v>565</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>1462</v>
+        <v>566</v>
+      </c>
+      <c r="E68" t="s">
+        <v>1489</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>322</v>
+        <v>567</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1669</v>
+        <v>568</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1388</v>
+        <v>1366</v>
       </c>
       <c r="B69" t="s">
-        <v>323</v>
+        <v>1056</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>324</v>
+        <v>1057</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>1461</v>
+        <v>1058</v>
+      </c>
+      <c r="E69" t="s">
+        <v>1570</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>326</v>
+        <v>480</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>327</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1388</v>
+        <v>1364</v>
       </c>
       <c r="B70" t="s">
-        <v>328</v>
+        <v>616</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>329</v>
+        <v>617</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>1470</v>
+        <v>618</v>
+      </c>
+      <c r="E70" t="s">
+        <v>1496</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>331</v>
+        <v>619</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>332</v>
+        <v>620</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1388</v>
+        <v>1363</v>
       </c>
       <c r="B71" t="s">
-        <v>333</v>
+        <v>669</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>334</v>
+        <v>670</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>1655</v>
+        <v>671</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1503</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>336</v>
+        <v>672</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>1388</v>
+        <v>1367</v>
       </c>
       <c r="B72" t="s">
-        <v>338</v>
+        <v>1720</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>339</v>
+        <v>1332</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>1471</v>
+        <v>1333</v>
+      </c>
+      <c r="E72" t="s">
+        <v>1618</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>341</v>
+        <v>1334</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>342</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1388</v>
+        <v>1365</v>
       </c>
       <c r="B73" t="s">
-        <v>343</v>
+        <v>820</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>344</v>
+        <v>821</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>1472</v>
+        <v>822</v>
+      </c>
+      <c r="E73" t="s">
+        <v>1527</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>346</v>
+        <v>823</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>347</v>
+        <v>824</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1388</v>
+        <v>1364</v>
       </c>
       <c r="B74" t="s">
-        <v>348</v>
+        <v>1084</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>349</v>
+        <v>1085</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>1473</v>
+        <v>1086</v>
+      </c>
+      <c r="E74" t="s">
+        <v>1576</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>351</v>
+        <v>730</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>352</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1388</v>
+        <v>1362</v>
       </c>
       <c r="B75" t="s">
-        <v>353</v>
+        <v>312</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1474</v>
+        <v>1443</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1684</v>
+        <v>316</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1388</v>
+        <v>1361</v>
       </c>
       <c r="B76" t="s">
-        <v>357</v>
+        <v>209</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>358</v>
+        <v>210</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>359</v>
+        <v>211</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1475</v>
+        <v>1627</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>360</v>
+        <v>212</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>361</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>1388</v>
-      </c>
-      <c r="B77" t="s">
-        <v>362</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>1476</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>366</v>
+      <c r="A77" s="5" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>1164</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1388</v>
+        <v>1367</v>
       </c>
       <c r="B78" t="s">
-        <v>367</v>
+        <v>727</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>368</v>
+        <v>728</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>1460</v>
+        <v>729</v>
+      </c>
+      <c r="E78" t="s">
+        <v>1511</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>370</v>
+        <v>730</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>371</v>
+        <v>731</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1388</v>
+        <v>1365</v>
       </c>
       <c r="B79" t="s">
-        <v>372</v>
+        <v>874</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1685</v>
+        <v>875</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>1477</v>
+        <v>876</v>
+      </c>
+      <c r="E79" t="s">
+        <v>1538</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>374</v>
+        <v>877</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1686</v>
+        <v>878</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1388</v>
+        <v>1364</v>
       </c>
       <c r="B80" t="s">
-        <v>375</v>
+        <v>488</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>376</v>
+        <v>489</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>1478</v>
+        <v>490</v>
+      </c>
+      <c r="E80" t="s">
+        <v>1473</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>378</v>
+        <v>491</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>379</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1388</v>
+        <v>1364</v>
       </c>
       <c r="B81" t="s">
-        <v>380</v>
+        <v>555</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>381</v>
+        <v>556</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>1479</v>
+        <v>557</v>
+      </c>
+      <c r="E81" t="s">
+        <v>1487</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>383</v>
+        <v>9</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1687</v>
+        <v>558</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1388</v>
+        <v>1364</v>
       </c>
       <c r="B82" t="s">
-        <v>384</v>
+        <v>483</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>385</v>
+        <v>484</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>1458</v>
+        <v>485</v>
+      </c>
+      <c r="E82" t="s">
+        <v>1472</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>387</v>
+        <v>486</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>388</v>
+        <v>487</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1388</v>
+        <v>1365</v>
       </c>
       <c r="B83" t="s">
-        <v>389</v>
+        <v>943</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>390</v>
+        <v>944</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>1461</v>
+        <v>945</v>
+      </c>
+      <c r="E83" t="s">
+        <v>1551</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>392</v>
+        <v>946</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>393</v>
+        <v>947</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1388</v>
+        <v>1365</v>
       </c>
       <c r="B84" t="s">
-        <v>394</v>
+        <v>1702</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>395</v>
+        <v>1272</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>1480</v>
+        <v>1273</v>
+      </c>
+      <c r="E84" t="s">
+        <v>1609</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>1</v>
+        <v>1274</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>397</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1389</v>
+        <v>1361</v>
       </c>
       <c r="B85" t="s">
-        <v>398</v>
+        <v>147</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>399</v>
+        <v>148</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>400</v>
+        <v>149</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1481</v>
+        <v>1412</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>401</v>
+        <v>150</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>402</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1389</v>
+        <v>1362</v>
       </c>
       <c r="B86" t="s">
-        <v>403</v>
+        <v>360</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>404</v>
+        <v>361</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>405</v>
+        <v>362</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1482</v>
+        <v>1450</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>406</v>
+        <v>363</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>407</v>
+        <v>364</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1389</v>
+        <v>1361</v>
       </c>
       <c r="B87" t="s">
-        <v>408</v>
+        <v>1697</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>409</v>
+        <v>1649</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>410</v>
+        <v>41</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1483</v>
+        <v>1390</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>411</v>
+        <v>42</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>412</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1389</v>
+        <v>1361</v>
       </c>
       <c r="B88" t="s">
-        <v>413</v>
+        <v>122</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>414</v>
+        <v>123</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>415</v>
+        <v>124</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1656</v>
+        <v>1404</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>416</v>
+        <v>125</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1688</v>
+        <v>126</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1389</v>
+        <v>1365</v>
       </c>
       <c r="B89" t="s">
-        <v>417</v>
+        <v>889</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>418</v>
+        <v>890</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>1657</v>
+        <v>891</v>
+      </c>
+      <c r="E89" t="s">
+        <v>1541</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>420</v>
+        <v>892</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>421</v>
+        <v>893</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1389</v>
+        <v>1369</v>
       </c>
       <c r="B90" t="s">
-        <v>422</v>
+        <v>1124</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>423</v>
+        <v>1125</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>1485</v>
+        <v>1126</v>
+      </c>
+      <c r="E90" t="s">
+        <v>1480</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>425</v>
+        <v>1127</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>426</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1389</v>
+        <v>1362</v>
       </c>
       <c r="B91" t="s">
-        <v>427</v>
+        <v>307</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>428</v>
+        <v>308</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>429</v>
+        <v>309</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1485</v>
+        <v>1461</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>430</v>
+        <v>310</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1689</v>
+        <v>311</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1389</v>
+        <v>1365</v>
       </c>
       <c r="B92" t="s">
-        <v>431</v>
+        <v>776</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>432</v>
+        <v>777</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>1485</v>
+        <v>778</v>
+      </c>
+      <c r="E92" t="s">
+        <v>1518</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>434</v>
+        <v>779</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>435</v>
+        <v>780</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1389</v>
+        <v>1361</v>
       </c>
       <c r="B93" t="s">
-        <v>436</v>
+        <v>204</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>437</v>
+        <v>205</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E93" t="s">
-        <v>1489</v>
+        <v>206</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>1425</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>439</v>
+        <v>207</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>440</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1389</v>
+        <v>1365</v>
       </c>
       <c r="B94" t="s">
-        <v>441</v>
+        <v>923</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>442</v>
+        <v>924</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>443</v>
+        <v>925</v>
       </c>
       <c r="E94" t="s">
-        <v>1484</v>
+        <v>1548</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>444</v>
+        <v>926</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>445</v>
+        <v>927</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1389</v>
+        <v>1362</v>
       </c>
       <c r="B95" t="s">
-        <v>446</v>
+        <v>326</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>447</v>
+        <v>327</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E95" t="s">
-        <v>1490</v>
+        <v>328</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>1444</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>449</v>
+        <v>329</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1389</v>
+        <v>1375</v>
       </c>
       <c r="B96" t="s">
-        <v>451</v>
+        <v>1703</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>452</v>
+        <v>1280</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>453</v>
+        <v>1281</v>
       </c>
       <c r="E96" t="s">
-        <v>1491</v>
+        <v>1611</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>454</v>
+        <v>1282</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>455</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1389</v>
+        <v>1361</v>
       </c>
       <c r="B97" t="s">
-        <v>456</v>
+        <v>223</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>457</v>
+        <v>224</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="E97" t="s">
-        <v>1492</v>
+        <v>225</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>1427</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>459</v>
+        <v>226</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>460</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1389</v>
+        <v>1365</v>
       </c>
       <c r="B98" t="s">
-        <v>461</v>
+        <v>761</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>462</v>
+        <v>762</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>463</v>
+        <v>763</v>
       </c>
       <c r="E98" t="s">
-        <v>1493</v>
+        <v>1515</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>464</v>
+        <v>764</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>465</v>
+        <v>765</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1389</v>
+        <v>1365</v>
       </c>
       <c r="B99" t="s">
-        <v>466</v>
+        <v>1711</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>467</v>
+        <v>1302</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>468</v>
+        <v>1303</v>
       </c>
       <c r="E99" t="s">
-        <v>1494</v>
+        <v>1454</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>469</v>
+        <v>1304</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>470</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B100" t="s">
-        <v>503</v>
+        <v>756</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>504</v>
+        <v>757</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>505</v>
+        <v>758</v>
       </c>
       <c r="E100" t="s">
-        <v>1502</v>
+        <v>1514</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>506</v>
+        <v>759</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>507</v>
+        <v>760</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B101" t="s">
-        <v>471</v>
+        <v>958</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>472</v>
+        <v>959</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>473</v>
+        <v>960</v>
       </c>
       <c r="E101" t="s">
-        <v>1495</v>
+        <v>1553</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>474</v>
+        <v>961</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>475</v>
+        <v>962</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1390</v>
+        <v>1364</v>
       </c>
       <c r="B102" t="s">
-        <v>476</v>
+        <v>1074</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>477</v>
+        <v>1075</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>478</v>
+        <v>1076</v>
       </c>
       <c r="E102" t="s">
-        <v>1496</v>
+        <v>1574</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>479</v>
+        <v>1077</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1690</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1390</v>
+        <v>1362</v>
       </c>
       <c r="B103" t="s">
-        <v>480</v>
+        <v>317</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>481</v>
+        <v>318</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="E103" t="s">
-        <v>1497</v>
+        <v>319</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>1436</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>483</v>
+        <v>320</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>484</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1390</v>
+        <v>1362</v>
       </c>
       <c r="B104" t="s">
-        <v>485</v>
+        <v>269</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>486</v>
+        <v>270</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="E104" t="s">
-        <v>1498</v>
+        <v>271</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>1434</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>488</v>
+        <v>272</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>489</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B105" t="s">
-        <v>490</v>
+        <v>830</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>491</v>
+        <v>831</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>492</v>
+        <v>832</v>
       </c>
       <c r="E105" t="s">
-        <v>1499</v>
+        <v>1529</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>493</v>
+        <v>833</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1390</v>
+        <v>1361</v>
       </c>
       <c r="B106" t="s">
-        <v>494</v>
+        <v>179</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>495</v>
+        <v>180</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="E106" t="s">
-        <v>1500</v>
+        <v>181</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>1419</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>497</v>
+        <v>182</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>498</v>
+        <v>183</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B107" t="s">
-        <v>499</v>
+        <v>786</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>500</v>
+        <v>787</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>501</v>
+        <v>788</v>
       </c>
       <c r="E107" t="s">
-        <v>1501</v>
+        <v>1520</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>502</v>
+        <v>789</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1692</v>
+        <v>790</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1390</v>
+        <v>1368</v>
       </c>
       <c r="B108" t="s">
-        <v>508</v>
+        <v>1114</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>509</v>
+        <v>1115</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>510</v>
+        <v>1116</v>
       </c>
       <c r="E108" t="s">
-        <v>1503</v>
+        <v>1582</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>1693</v>
+        <v>1117</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>511</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1390</v>
+        <v>1362</v>
       </c>
       <c r="B109" t="s">
-        <v>512</v>
+        <v>382</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="E109" t="s">
-        <v>1504</v>
+        <v>384</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>1432</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>515</v>
+        <v>385</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>516</v>
+        <v>386</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B110" t="s">
-        <v>517</v>
+        <v>844</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>518</v>
+        <v>845</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>519</v>
+        <v>846</v>
       </c>
       <c r="E110" t="s">
-        <v>1505</v>
+        <v>1532</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>13</v>
+        <v>847</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>520</v>
+        <v>848</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B111" t="s">
-        <v>521</v>
+        <v>1708</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>522</v>
+        <v>1291</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>523</v>
+        <v>1292</v>
       </c>
       <c r="E111" t="s">
-        <v>1506</v>
+        <v>1462</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>524</v>
+        <v>1293</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>525</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1390</v>
+        <v>1364</v>
       </c>
       <c r="B112" t="s">
-        <v>526</v>
+        <v>587</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>527</v>
+        <v>588</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>528</v>
+        <v>589</v>
       </c>
       <c r="E112" t="s">
-        <v>1507</v>
+        <v>1434</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>529</v>
+        <v>590</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>530</v>
+        <v>591</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1390</v>
+        <v>1366</v>
       </c>
       <c r="B113" t="s">
-        <v>531</v>
+        <v>1041</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>532</v>
+        <v>1042</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>533</v>
+        <v>1043</v>
       </c>
       <c r="E113" t="s">
-        <v>1508</v>
+        <v>1567</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>534</v>
+        <v>1044</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>535</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1390</v>
+        <v>1370</v>
       </c>
       <c r="B114" t="s">
-        <v>536</v>
+        <v>1148</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>537</v>
+        <v>1149</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>538</v>
+        <v>1150</v>
       </c>
       <c r="E114" t="s">
-        <v>1509</v>
+        <v>1456</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>14</v>
+        <v>1151</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>539</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B115" t="s">
-        <v>540</v>
+        <v>815</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>541</v>
+        <v>816</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>542</v>
+        <v>817</v>
       </c>
       <c r="E115" t="s">
-        <v>1510</v>
+        <v>1526</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1694</v>
+        <v>818</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1695</v>
+        <v>819</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1390</v>
+        <v>1369</v>
       </c>
       <c r="B116" t="s">
-        <v>543</v>
+        <v>1134</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>544</v>
+        <v>1135</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>545</v>
+        <v>1136</v>
       </c>
       <c r="E116" t="s">
-        <v>1511</v>
+        <v>1584</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>283</v>
+        <v>1137</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>546</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1390</v>
+        <v>1367</v>
       </c>
       <c r="B117" t="s">
-        <v>547</v>
+        <v>1707</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>548</v>
+        <v>1284</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>549</v>
+        <v>1285</v>
       </c>
       <c r="E117" t="s">
-        <v>1458</v>
+        <v>1612</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>550</v>
+        <v>1286</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>551</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1390</v>
+        <v>1364</v>
       </c>
       <c r="B118" t="s">
-        <v>552</v>
+        <v>646</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>553</v>
+        <v>647</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>554</v>
+        <v>648</v>
       </c>
       <c r="E118" t="s">
-        <v>1512</v>
+        <v>1475</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>555</v>
+        <v>649</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>556</v>
+        <v>650</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B119" t="s">
-        <v>557</v>
+        <v>766</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>558</v>
+        <v>767</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>559</v>
+        <v>768</v>
       </c>
       <c r="E119" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>9</v>
+        <v>769</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>560</v>
+        <v>770</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1390</v>
+        <v>1361</v>
       </c>
       <c r="B120" t="s">
-        <v>561</v>
+        <v>65</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>562</v>
+        <v>66</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="E120" t="s">
-        <v>1514</v>
+        <v>67</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>1397</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>564</v>
+        <v>68</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>565</v>
+        <v>69</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1390</v>
+        <v>1364</v>
       </c>
       <c r="B121" t="s">
-        <v>566</v>
+        <v>602</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>567</v>
+        <v>603</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>568</v>
+        <v>604</v>
       </c>
       <c r="E121" t="s">
-        <v>1515</v>
+        <v>1470</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>569</v>
+        <v>605</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>570</v>
+        <v>606</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B122" t="s">
-        <v>571</v>
+        <v>879</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>572</v>
+        <v>880</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>573</v>
+        <v>881</v>
       </c>
       <c r="E122" t="s">
-        <v>1516</v>
+        <v>1539</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>574</v>
+        <v>882</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>575</v>
+        <v>883</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1390</v>
+        <v>1366</v>
       </c>
       <c r="B123" t="s">
-        <v>576</v>
+        <v>1022</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>577</v>
+        <v>1023</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>578</v>
+        <v>1024</v>
       </c>
       <c r="E123" t="s">
-        <v>1517</v>
+        <v>1563</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>579</v>
+        <v>11</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>580</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1390</v>
+        <v>1361</v>
       </c>
       <c r="B124" t="s">
-        <v>581</v>
+        <v>54</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>582</v>
+        <v>1650</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="E124" t="s">
-        <v>1518</v>
+        <v>55</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>1394</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>584</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1390</v>
+        <v>1371</v>
       </c>
       <c r="B125" t="s">
-        <v>585</v>
+        <v>1203</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>586</v>
+        <v>1204</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>587</v>
+        <v>1205</v>
       </c>
       <c r="E125" t="s">
-        <v>1519</v>
+        <v>1596</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>588</v>
+        <v>1206</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1696</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>1390</v>
+        <v>1371</v>
       </c>
       <c r="B126" t="s">
-        <v>589</v>
+        <v>1203</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>590</v>
+        <v>1356</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>591</v>
+        <v>1357</v>
       </c>
       <c r="E126" t="s">
-        <v>1460</v>
+        <v>1622</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>592</v>
+        <v>1358</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>593</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1390</v>
+        <v>1361</v>
       </c>
       <c r="B127" t="s">
-        <v>594</v>
+        <v>95</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>595</v>
+        <v>96</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="E127" t="s">
-        <v>1520</v>
+        <v>97</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>1403</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>597</v>
+        <v>98</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>598</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B128" t="s">
-        <v>599</v>
+        <v>806</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>600</v>
+        <v>807</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>601</v>
+        <v>808</v>
       </c>
       <c r="E128" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>602</v>
+        <v>809</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>603</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1390</v>
+        <v>1363</v>
       </c>
       <c r="B129" t="s">
-        <v>604</v>
+        <v>425</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>605</v>
+        <v>426</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="E129" t="s">
-        <v>1496</v>
+        <v>427</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>1459</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>607</v>
+        <v>428</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>1390</v>
+        <v>1369</v>
       </c>
       <c r="B130" t="s">
-        <v>609</v>
+        <v>1344</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>610</v>
+        <v>1682</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>611</v>
+        <v>1345</v>
       </c>
       <c r="E130" t="s">
-        <v>1661</v>
+        <v>1474</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>612</v>
+        <v>1346</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>613</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1390</v>
+        <v>1366</v>
       </c>
       <c r="B131" t="s">
-        <v>614</v>
+        <v>1036</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>615</v>
+        <v>1037</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>616</v>
+        <v>1038</v>
       </c>
       <c r="E131" t="s">
-        <v>1662</v>
+        <v>1566</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>293</v>
+        <v>1039</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>617</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1390</v>
+        <v>1361</v>
       </c>
       <c r="B132" t="s">
-        <v>618</v>
+        <v>21</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>619</v>
+        <v>22</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="E132" t="s">
-        <v>1522</v>
+        <v>23</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>1385</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>621</v>
+        <v>24</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>622</v>
+        <v>25</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1390</v>
+        <v>1366</v>
       </c>
       <c r="B133" t="s">
-        <v>623</v>
+        <v>993</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>624</v>
+        <v>994</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>625</v>
+        <v>995</v>
       </c>
       <c r="E133" t="s">
-        <v>1523</v>
+        <v>1559</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>626</v>
+        <v>996</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>627</v>
+        <v>997</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1390</v>
+        <v>1361</v>
       </c>
       <c r="B134" t="s">
-        <v>628</v>
+        <v>70</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>629</v>
+        <v>71</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="E134" t="s">
-        <v>1521</v>
+        <v>72</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>1398</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>631</v>
+        <v>73</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>632</v>
+        <v>74</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1390</v>
+        <v>1361</v>
       </c>
       <c r="B135" t="s">
-        <v>633</v>
+        <v>112</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>634</v>
+        <v>113</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="E135" t="s">
-        <v>1524</v>
+        <v>114</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>1406</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>636</v>
+        <v>115</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>637</v>
+        <v>116</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1390</v>
+        <v>1366</v>
       </c>
       <c r="B136" t="s">
-        <v>638</v>
+        <v>1709</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>639</v>
+        <v>1295</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>640</v>
+        <v>1296</v>
       </c>
       <c r="E136" t="s">
-        <v>1479</v>
+        <v>1560</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>641</v>
+        <v>1297</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>642</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B137" t="s">
-        <v>643</v>
+        <v>899</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>644</v>
+        <v>900</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>645</v>
+        <v>901</v>
       </c>
       <c r="E137" t="s">
-        <v>1525</v>
+        <v>1543</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>646</v>
+        <v>115</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>647</v>
+        <v>902</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>1390</v>
-      </c>
       <c r="B138" t="s">
-        <v>648</v>
+        <v>1710</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>649</v>
+        <v>1299</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>650</v>
+        <v>1300</v>
       </c>
       <c r="E138" t="s">
-        <v>1501</v>
+        <v>1614</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>651</v>
+        <v>1255</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>652</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B139" t="s">
-        <v>653</v>
+        <v>825</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>654</v>
+        <v>826</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>655</v>
+        <v>827</v>
       </c>
       <c r="E139" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>656</v>
+        <v>828</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>657</v>
+        <v>829</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1389</v>
+        <v>1361</v>
       </c>
       <c r="B140" t="s">
-        <v>658</v>
+        <v>30</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>659</v>
+        <v>31</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="E140" t="s">
-        <v>1527</v>
+        <v>32</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>1387</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>661</v>
+        <v>1654</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1697</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1389</v>
+        <v>1363</v>
       </c>
       <c r="B141" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="E141" t="s">
-        <v>1528</v>
+        <v>1505</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1389</v>
+        <v>1363</v>
       </c>
       <c r="B142" t="s">
-        <v>667</v>
+        <v>709</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>668</v>
+        <v>710</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>669</v>
+        <v>711</v>
       </c>
       <c r="E142" t="s">
-        <v>1490</v>
+        <v>1632</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>670</v>
+        <v>712</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1698</v>
+        <v>713</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1389</v>
+        <v>1364</v>
       </c>
       <c r="B143" t="s">
-        <v>671</v>
+        <v>636</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>672</v>
+        <v>637</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>673</v>
+        <v>638</v>
       </c>
       <c r="E143" t="s">
-        <v>1529</v>
+        <v>1453</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>674</v>
+        <v>639</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1699</v>
+        <v>640</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1389</v>
+        <v>1364</v>
       </c>
       <c r="B144" t="s">
-        <v>675</v>
+        <v>631</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>676</v>
+        <v>632</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>677</v>
+        <v>633</v>
       </c>
       <c r="E144" t="s">
-        <v>1530</v>
+        <v>1498</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>678</v>
+        <v>634</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>679</v>
+        <v>635</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1389</v>
+        <v>1363</v>
       </c>
       <c r="B145" t="s">
-        <v>680</v>
+        <v>420</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>681</v>
+        <v>421</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="E145" t="s">
-        <v>1531</v>
+        <v>422</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>1459</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>683</v>
+        <v>423</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>684</v>
+        <v>424</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1389</v>
+        <v>1364</v>
       </c>
       <c r="B146" t="s">
-        <v>685</v>
+        <v>607</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>686</v>
+        <v>608</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>687</v>
+        <v>609</v>
       </c>
       <c r="E146" t="s">
-        <v>1532</v>
+        <v>1635</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>688</v>
+        <v>610</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>689</v>
+        <v>611</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1389</v>
+        <v>1373</v>
       </c>
       <c r="B147" t="s">
-        <v>690</v>
+        <v>1245</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>691</v>
+        <v>1246</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>692</v>
+        <v>1247</v>
       </c>
       <c r="E147" t="s">
-        <v>1533</v>
+        <v>1605</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>693</v>
+        <v>1248</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>694</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1389</v>
+        <v>1363</v>
       </c>
       <c r="B148" t="s">
-        <v>695</v>
+        <v>411</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>696</v>
+        <v>412</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="E148" t="s">
-        <v>1534</v>
+        <v>413</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>1630</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>1700</v>
+        <v>414</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1701</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1389</v>
+        <v>1365</v>
       </c>
       <c r="B149" t="s">
-        <v>698</v>
+        <v>849</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>699</v>
+        <v>850</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>274</v>
+        <v>851</v>
       </c>
       <c r="E149" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>700</v>
+        <v>852</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>701</v>
+        <v>853</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1389</v>
+        <v>1370</v>
       </c>
       <c r="B150" t="s">
-        <v>702</v>
+        <v>1179</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>703</v>
+        <v>1180</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>704</v>
+        <v>1181</v>
       </c>
       <c r="E150" t="s">
-        <v>1534</v>
+        <v>1591</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1389</v>
+        <v>1368</v>
       </c>
       <c r="B151" t="s">
-        <v>706</v>
+        <v>1112</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>707</v>
+        <v>1341</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>708</v>
+        <v>1113</v>
       </c>
       <c r="E151" t="s">
-        <v>1534</v>
+        <v>1620</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>709</v>
+        <v>1342</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>710</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1389</v>
+        <v>1365</v>
       </c>
       <c r="B152" t="s">
-        <v>711</v>
+        <v>781</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>712</v>
+        <v>782</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>713</v>
+        <v>783</v>
       </c>
       <c r="E152" t="s">
-        <v>1658</v>
+        <v>1519</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>714</v>
+        <v>784</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1393</v>
+        <v>1365</v>
       </c>
       <c r="B153" t="s">
-        <v>716</v>
+        <v>1712</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>717</v>
+        <v>1306</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>718</v>
+        <v>1307</v>
       </c>
       <c r="E153" t="s">
-        <v>1659</v>
+        <v>1454</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>719</v>
+        <v>1308</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>720</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1393</v>
+        <v>1361</v>
       </c>
       <c r="B154" t="s">
-        <v>721</v>
+        <v>80</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>722</v>
+        <v>81</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="E154" t="s">
-        <v>1535</v>
+        <v>82</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>1400</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>724</v>
+        <v>83</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>1702</v>
+        <v>84</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1393</v>
+        <v>1362</v>
       </c>
       <c r="B155" t="s">
-        <v>725</v>
+        <v>370</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>726</v>
+        <v>1659</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="E155" t="s">
-        <v>1536</v>
+        <v>371</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>1451</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>728</v>
+        <v>372</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>1703</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1393</v>
+        <v>1366</v>
       </c>
       <c r="B156" t="s">
-        <v>729</v>
+        <v>1051</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>730</v>
+        <v>1052</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>731</v>
+        <v>1053</v>
       </c>
       <c r="E156" t="s">
-        <v>1537</v>
+        <v>1569</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>732</v>
+        <v>1054</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>733</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1393</v>
+        <v>1362</v>
       </c>
       <c r="B157" t="s">
-        <v>734</v>
+        <v>298</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>735</v>
+        <v>299</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="E157" t="s">
-        <v>1538</v>
+        <v>300</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>1441</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>737</v>
+        <v>2</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>738</v>
+        <v>301</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1393</v>
+        <v>1365</v>
       </c>
       <c r="B158" t="s">
-        <v>739</v>
+        <v>953</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>740</v>
+        <v>954</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>741</v>
+        <v>955</v>
       </c>
       <c r="E158" t="s">
-        <v>1511</v>
+        <v>1552</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>742</v>
+        <v>956</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>743</v>
+        <v>957</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1393</v>
+        <v>1365</v>
       </c>
       <c r="B159" t="s">
-        <v>744</v>
+        <v>859</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>745</v>
+        <v>860</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>746</v>
+        <v>861</v>
       </c>
       <c r="E159" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>747</v>
+        <v>862</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>748</v>
+        <v>863</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1393</v>
+        <v>1361</v>
       </c>
       <c r="B160" t="s">
-        <v>749</v>
+        <v>175</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>750</v>
+        <v>176</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="E160" t="s">
-        <v>1660</v>
+        <v>177</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>1418</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>752</v>
+        <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>753</v>
+        <v>178</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1391</v>
+        <v>1365</v>
       </c>
       <c r="B161" t="s">
-        <v>754</v>
+        <v>908</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>755</v>
+        <v>909</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>756</v>
+        <v>910</v>
       </c>
       <c r="E161" t="s">
-        <v>1539</v>
+        <v>1545</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>757</v>
+        <v>911</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>758</v>
+        <v>912</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1391</v>
+        <v>1365</v>
       </c>
       <c r="B162" t="s">
-        <v>759</v>
+        <v>928</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>760</v>
+        <v>929</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>761</v>
+        <v>930</v>
       </c>
       <c r="E162" t="s">
-        <v>1540</v>
+        <v>1518</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>762</v>
+        <v>931</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>763</v>
+        <v>932</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1391</v>
+        <v>1370</v>
       </c>
       <c r="B163" t="s">
-        <v>764</v>
+        <v>1157</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>765</v>
+        <v>1158</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>766</v>
+        <v>1159</v>
       </c>
       <c r="E163" t="s">
-        <v>1541</v>
+        <v>1623</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>767</v>
+        <v>1679</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>768</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1391</v>
+        <v>1366</v>
       </c>
       <c r="B164" t="s">
-        <v>769</v>
+        <v>1008</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>770</v>
+        <v>1009</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>771</v>
+        <v>1010</v>
       </c>
       <c r="E164" t="s">
-        <v>1542</v>
+        <v>1561</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>772</v>
+        <v>1011</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>773</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1391</v>
+        <v>1365</v>
       </c>
       <c r="B165" t="s">
-        <v>774</v>
+        <v>963</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>775</v>
+        <v>964</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>776</v>
+        <v>965</v>
       </c>
       <c r="E165" t="s">
-        <v>1543</v>
+        <v>1554</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>777</v>
+        <v>966</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>778</v>
+        <v>967</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1391</v>
+        <v>1364</v>
       </c>
       <c r="B166" t="s">
-        <v>779</v>
+        <v>612</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>780</v>
+        <v>613</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>781</v>
+        <v>614</v>
       </c>
       <c r="E166" t="s">
-        <v>1544</v>
+        <v>1636</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>782</v>
+        <v>291</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>783</v>
+        <v>615</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1391</v>
+        <v>1367</v>
       </c>
       <c r="B167" t="s">
-        <v>784</v>
+        <v>719</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>785</v>
+        <v>720</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>786</v>
+        <v>721</v>
       </c>
       <c r="E167" t="s">
-        <v>1545</v>
+        <v>1509</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>787</v>
+        <v>722</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>788</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1391</v>
+        <v>1367</v>
       </c>
       <c r="B168" t="s">
-        <v>789</v>
+        <v>1706</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>790</v>
+        <v>1287</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>791</v>
+        <v>1288</v>
       </c>
       <c r="E168" t="s">
-        <v>1546</v>
+        <v>1613</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>792</v>
+        <v>1289</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>793</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1391</v>
+        <v>1373</v>
       </c>
       <c r="B169" t="s">
-        <v>794</v>
+        <v>1216</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>795</v>
+        <v>1217</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>796</v>
+        <v>1218</v>
       </c>
       <c r="E169" t="s">
-        <v>1547</v>
+        <v>1599</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>797</v>
+        <v>1099</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>798</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1391</v>
+        <v>1361</v>
       </c>
       <c r="B170" t="s">
-        <v>799</v>
+        <v>218</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>800</v>
+        <v>219</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="E170" t="s">
-        <v>1548</v>
+        <v>220</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>1628</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>802</v>
+        <v>221</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>803</v>
+        <v>222</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1391</v>
+        <v>1361</v>
       </c>
       <c r="B171" t="s">
-        <v>804</v>
+        <v>117</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>805</v>
+        <v>118</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="E171" t="s">
-        <v>1549</v>
+        <v>119</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>1407</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>807</v>
+        <v>120</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>808</v>
+        <v>121</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1391</v>
+        <v>1361</v>
       </c>
       <c r="B172" t="s">
-        <v>809</v>
+        <v>85</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>810</v>
+        <v>86</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="E172" t="s">
-        <v>1550</v>
+        <v>87</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>1401</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>812</v>
+        <v>88</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>1719</v>
+        <v>89</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1391</v>
+        <v>1369</v>
       </c>
       <c r="B173" t="s">
-        <v>813</v>
+        <v>1119</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>814</v>
+        <v>1120</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>815</v>
+        <v>1121</v>
       </c>
       <c r="E173" t="s">
-        <v>1551</v>
+        <v>1583</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>816</v>
+        <v>1122</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>817</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1391</v>
+        <v>1365</v>
       </c>
       <c r="B174" t="s">
-        <v>818</v>
+        <v>791</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>819</v>
+        <v>792</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>820</v>
+        <v>793</v>
       </c>
       <c r="E174" t="s">
-        <v>1552</v>
+        <v>1521</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>821</v>
+        <v>794</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>822</v>
+        <v>795</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1391</v>
+        <v>1361</v>
       </c>
       <c r="B175" t="s">
-        <v>823</v>
+        <v>213</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>824</v>
+        <v>214</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="E175" t="s">
-        <v>1553</v>
+        <v>215</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>1426</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>826</v>
+        <v>216</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>827</v>
+        <v>217</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1391</v>
+        <v>1362</v>
       </c>
       <c r="B176" t="s">
-        <v>828</v>
+        <v>392</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>829</v>
+        <v>393</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="E176" t="s">
-        <v>1554</v>
+        <v>394</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>1454</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>831</v>
+        <v>1</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>832</v>
+        <v>395</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1391</v>
+        <v>1361</v>
       </c>
       <c r="B177" t="s">
-        <v>833</v>
+        <v>107</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>834</v>
+        <v>108</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="E177" t="s">
-        <v>1555</v>
+        <v>109</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>1405</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>836</v>
+        <v>110</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>1720</v>
+        <v>111</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1391</v>
+        <v>1364</v>
       </c>
       <c r="B178" t="s">
-        <v>837</v>
+        <v>524</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>838</v>
+        <v>525</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>839</v>
+        <v>526</v>
       </c>
       <c r="E178" t="s">
-        <v>1556</v>
+        <v>1481</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>840</v>
+        <v>527</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>841</v>
+        <v>528</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1391</v>
+        <v>1375</v>
       </c>
       <c r="B179" t="s">
-        <v>842</v>
+        <v>1705</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>843</v>
+        <v>1276</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>844</v>
+        <v>1277</v>
       </c>
       <c r="E179" t="s">
-        <v>1557</v>
+        <v>1610</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>845</v>
+        <v>1278</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>846</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1391</v>
+        <v>1364</v>
       </c>
       <c r="B180" t="s">
-        <v>847</v>
+        <v>550</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>848</v>
+        <v>551</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>849</v>
+        <v>552</v>
       </c>
       <c r="E180" t="s">
-        <v>1558</v>
+        <v>1486</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>850</v>
+        <v>553</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>851</v>
+        <v>554</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1391</v>
+        <v>1364</v>
       </c>
       <c r="B181" t="s">
-        <v>852</v>
+        <v>626</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>853</v>
+        <v>627</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>854</v>
+        <v>628</v>
       </c>
       <c r="E181" t="s">
-        <v>1559</v>
+        <v>1495</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>855</v>
+        <v>629</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>856</v>
+        <v>630</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1391</v>
+        <v>1362</v>
       </c>
       <c r="B182" t="s">
-        <v>857</v>
+        <v>336</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>858</v>
+        <v>337</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="E182" t="s">
-        <v>1560</v>
+        <v>338</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>1445</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>860</v>
+        <v>339</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>861</v>
+        <v>340</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1391</v>
+        <v>1361</v>
       </c>
       <c r="B183" t="s">
-        <v>862</v>
+        <v>237</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>863</v>
+        <v>238</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="E183" t="s">
-        <v>1561</v>
+        <v>239</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>1430</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>865</v>
+        <v>240</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>866</v>
+        <v>241</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1391</v>
+        <v>1367</v>
       </c>
       <c r="B184" t="s">
-        <v>867</v>
+        <v>714</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>868</v>
+        <v>715</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>869</v>
+        <v>716</v>
       </c>
       <c r="E184" t="s">
-        <v>1562</v>
+        <v>1633</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>870</v>
+        <v>717</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>871</v>
+        <v>718</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1391</v>
+        <v>1366</v>
       </c>
       <c r="B185" t="s">
-        <v>872</v>
+        <v>1065</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>873</v>
+        <v>1066</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>874</v>
+        <v>1067</v>
       </c>
       <c r="E185" t="s">
-        <v>1563</v>
+        <v>1572</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>875</v>
+        <v>1068</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>876</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1391</v>
+        <v>1366</v>
       </c>
       <c r="B186" t="s">
-        <v>877</v>
+        <v>988</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>878</v>
+        <v>989</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>879</v>
+        <v>990</v>
       </c>
       <c r="E186" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>880</v>
+        <v>991</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>881</v>
+        <v>992</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1391</v>
+        <v>1362</v>
       </c>
       <c r="B187" t="s">
-        <v>882</v>
+        <v>365</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>883</v>
+        <v>366</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="E187" t="s">
-        <v>1565</v>
+        <v>367</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>1434</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>885</v>
+        <v>368</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>886</v>
+        <v>369</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1391</v>
+        <v>1371</v>
       </c>
       <c r="B188" t="s">
-        <v>887</v>
+        <v>1198</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>888</v>
+        <v>1199</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>889</v>
+        <v>1200</v>
       </c>
       <c r="E188" t="s">
-        <v>1566</v>
+        <v>1595</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>890</v>
+        <v>1201</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>1391</v>
+        <v>1363</v>
       </c>
       <c r="B189" t="s">
-        <v>892</v>
+        <v>1719</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>893</v>
+        <v>1321</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>894</v>
+        <v>1322</v>
       </c>
       <c r="E189" t="s">
-        <v>1567</v>
+        <v>1490</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>895</v>
+        <v>1323</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>896</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1391</v>
+        <v>1364</v>
       </c>
       <c r="B190" t="s">
-        <v>897</v>
+        <v>592</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>898</v>
+        <v>593</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>899</v>
+        <v>594</v>
       </c>
       <c r="E190" t="s">
-        <v>1568</v>
+        <v>1494</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>900</v>
+        <v>595</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>901</v>
+        <v>596</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1391</v>
+        <v>1362</v>
       </c>
       <c r="B191" t="s">
-        <v>902</v>
+        <v>294</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>903</v>
+        <v>295</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="E191" t="s">
-        <v>1569</v>
+        <v>1460</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>1440</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>116</v>
+        <v>296</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>905</v>
+        <v>297</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1391</v>
+        <v>1366</v>
       </c>
       <c r="B192" t="s">
-        <v>906</v>
+        <v>1060</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>907</v>
+        <v>1061</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>908</v>
+        <v>1062</v>
       </c>
       <c r="E192" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>909</v>
+        <v>1063</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>910</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1391</v>
+        <v>1362</v>
       </c>
       <c r="B193" t="s">
-        <v>911</v>
+        <v>321</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>912</v>
+        <v>322</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="E193" t="s">
-        <v>1571</v>
+        <v>323</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>1435</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>914</v>
+        <v>324</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>915</v>
+        <v>325</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1391</v>
+        <v>1364</v>
       </c>
       <c r="B194" t="s">
-        <v>916</v>
+        <v>501</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>917</v>
+        <v>502</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>918</v>
+        <v>503</v>
       </c>
       <c r="E194" t="s">
-        <v>1572</v>
+        <v>1476</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>919</v>
+        <v>504</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>920</v>
+        <v>505</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1391</v>
+        <v>1364</v>
       </c>
       <c r="B195" t="s">
-        <v>921</v>
+        <v>621</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>922</v>
+        <v>622</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>923</v>
+        <v>623</v>
       </c>
       <c r="E195" t="s">
-        <v>1573</v>
+        <v>1497</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>924</v>
+        <v>624</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>925</v>
+        <v>625</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1391</v>
+        <v>1364</v>
       </c>
       <c r="B196" t="s">
-        <v>926</v>
+        <v>497</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>927</v>
+        <v>498</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>928</v>
+        <v>499</v>
       </c>
       <c r="E196" t="s">
-        <v>1574</v>
+        <v>1475</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>929</v>
+        <v>500</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>930</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1391</v>
+        <v>1365</v>
       </c>
       <c r="B197" t="s">
-        <v>931</v>
+        <v>854</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>932</v>
+        <v>855</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>933</v>
+        <v>856</v>
       </c>
       <c r="E197" t="s">
-        <v>1544</v>
+        <v>1534</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>934</v>
+        <v>857</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>935</v>
+        <v>858</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1391</v>
+        <v>1363</v>
       </c>
       <c r="B198" t="s">
-        <v>936</v>
+        <v>449</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>937</v>
+        <v>450</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>938</v>
+        <v>451</v>
       </c>
       <c r="E198" t="s">
-        <v>1575</v>
+        <v>1465</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>939</v>
+        <v>452</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>940</v>
+        <v>453</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1391</v>
+        <v>1363</v>
       </c>
       <c r="B199" t="s">
-        <v>941</v>
+        <v>464</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>942</v>
+        <v>465</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>943</v>
+        <v>466</v>
       </c>
       <c r="E199" t="s">
-        <v>1576</v>
+        <v>1468</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>944</v>
+        <v>467</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>945</v>
+        <v>468</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1391</v>
+        <v>1362</v>
       </c>
       <c r="B200" t="s">
-        <v>946</v>
+        <v>289</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>947</v>
+        <v>290</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>948</v>
-      </c>
-      <c r="E200" t="s">
-        <v>1577</v>
+        <v>291</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>1440</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>949</v>
+        <v>292</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>950</v>
+        <v>293</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1391</v>
+        <v>1363</v>
       </c>
       <c r="B201" t="s">
-        <v>951</v>
+        <v>444</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>952</v>
+        <v>445</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>953</v>
+        <v>446</v>
       </c>
       <c r="E201" t="s">
-        <v>1552</v>
+        <v>1464</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>954</v>
+        <v>447</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>955</v>
+        <v>448</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1391</v>
+        <v>1364</v>
       </c>
       <c r="B202" t="s">
-        <v>956</v>
+        <v>597</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>957</v>
+        <v>598</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>958</v>
+        <v>599</v>
       </c>
       <c r="E202" t="s">
-        <v>1578</v>
+        <v>1495</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>959</v>
+        <v>600</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>960</v>
+        <v>601</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1391</v>
+        <v>1364</v>
       </c>
       <c r="B203" t="s">
-        <v>961</v>
+        <v>515</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>962</v>
+        <v>516</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>963</v>
+        <v>517</v>
       </c>
       <c r="E203" t="s">
-        <v>1579</v>
+        <v>1479</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>964</v>
+        <v>13</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>965</v>
+        <v>518</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1391</v>
+        <v>1365</v>
       </c>
       <c r="B204" t="s">
-        <v>966</v>
+        <v>801</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>967</v>
+        <v>802</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>968</v>
+        <v>803</v>
       </c>
       <c r="E204" t="s">
-        <v>1580</v>
+        <v>1523</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>969</v>
+        <v>804</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>970</v>
+        <v>805</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1392</v>
+        <v>1365</v>
       </c>
       <c r="B205" t="s">
-        <v>971</v>
+        <v>903</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>972</v>
+        <v>904</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>973</v>
+        <v>905</v>
       </c>
       <c r="E205" t="s">
-        <v>1581</v>
+        <v>1544</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>974</v>
+        <v>906</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>975</v>
+        <v>907</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1392</v>
+        <v>1364</v>
       </c>
       <c r="B206" t="s">
-        <v>976</v>
+        <v>478</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>977</v>
+        <v>479</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>978</v>
+        <v>480</v>
       </c>
       <c r="E206" t="s">
-        <v>1582</v>
+        <v>1471</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>979</v>
+        <v>481</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>1392</v>
+        <v>1367</v>
       </c>
       <c r="B207" t="s">
-        <v>981</v>
+        <v>1718</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>982</v>
+        <v>1310</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>983</v>
+        <v>1311</v>
       </c>
       <c r="E207" t="s">
-        <v>1466</v>
+        <v>1615</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>984</v>
+        <v>1312</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>985</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1392</v>
+        <v>1370</v>
       </c>
       <c r="B208" t="s">
-        <v>986</v>
+        <v>1193</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>987</v>
+        <v>1194</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>988</v>
+        <v>1195</v>
       </c>
       <c r="E208" t="s">
-        <v>1583</v>
+        <v>1594</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>989</v>
+        <v>1196</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>1392</v>
+        <v>1363</v>
       </c>
       <c r="B209" t="s">
-        <v>991</v>
+        <v>1717</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>992</v>
+        <v>1314</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>993</v>
+        <v>1315</v>
       </c>
       <c r="E209" t="s">
-        <v>1584</v>
+        <v>1467</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>994</v>
+        <v>1316</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>995</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1392</v>
+        <v>1362</v>
       </c>
       <c r="B210" t="s">
-        <v>996</v>
+        <v>351</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>997</v>
+        <v>352</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>998</v>
-      </c>
-      <c r="E210" t="s">
-        <v>1585</v>
+        <v>353</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>1448</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>999</v>
+        <v>354</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>1000</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1392</v>
+        <v>1363</v>
       </c>
       <c r="B211" t="s">
-        <v>1001</v>
+        <v>1716</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1002</v>
+        <v>1318</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1003</v>
+        <v>1319</v>
       </c>
       <c r="E211" t="s">
-        <v>1586</v>
+        <v>1452</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>1004</v>
+        <v>1320</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>1005</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1392</v>
+        <v>1369</v>
       </c>
       <c r="B212" t="s">
-        <v>1006</v>
+        <v>1129</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>1007</v>
+        <v>1130</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1008</v>
+        <v>1131</v>
       </c>
       <c r="E212" t="s">
-        <v>1582</v>
+        <v>1488</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>1009</v>
+        <v>1132</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1010</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1392</v>
+        <v>1373</v>
       </c>
       <c r="B213" t="s">
-        <v>1011</v>
+        <v>1220</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>1012</v>
+        <v>1221</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1013</v>
+        <v>1222</v>
       </c>
       <c r="E213" t="s">
-        <v>1587</v>
+        <v>1600</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>1014</v>
+        <v>1223</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>1015</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1392</v>
+        <v>1363</v>
       </c>
       <c r="B214" t="s">
-        <v>1016</v>
+        <v>454</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>1017</v>
+        <v>455</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>1018</v>
+        <v>456</v>
       </c>
       <c r="E214" t="s">
-        <v>1588</v>
+        <v>1466</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>1019</v>
+        <v>457</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1721</v>
+        <v>458</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1392</v>
+        <v>1366</v>
       </c>
       <c r="B215" t="s">
-        <v>1020</v>
+        <v>998</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>1021</v>
+        <v>999</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1022</v>
+        <v>1000</v>
       </c>
       <c r="E215" t="s">
-        <v>1514</v>
+        <v>1560</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>1023</v>
+        <v>1001</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1024</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1392</v>
+        <v>1361</v>
       </c>
       <c r="B216" t="s">
-        <v>1025</v>
+        <v>127</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>1026</v>
+        <v>128</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="E216" t="s">
-        <v>1589</v>
+        <v>129</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>1408</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>11</v>
+        <v>130</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1028</v>
+        <v>131</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1392</v>
+        <v>1364</v>
       </c>
       <c r="B217" t="s">
-        <v>1029</v>
+        <v>651</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>1030</v>
+        <v>652</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>1031</v>
+        <v>653</v>
       </c>
       <c r="E217" t="s">
-        <v>1590</v>
+        <v>1500</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>1032</v>
+        <v>654</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>1033</v>
+        <v>655</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1392</v>
+        <v>1367</v>
       </c>
       <c r="B218" t="s">
-        <v>1034</v>
+        <v>1097</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>1035</v>
+        <v>1098</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>1036</v>
+        <v>1099</v>
       </c>
       <c r="E218" t="s">
-        <v>1591</v>
+        <v>1579</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>1037</v>
+        <v>1100</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>1038</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1392</v>
+        <v>1361</v>
       </c>
       <c r="B219" t="s">
-        <v>1039</v>
+        <v>33</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>1040</v>
+        <v>34</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E219" t="s">
-        <v>1592</v>
+        <v>35</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>1388</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>1042</v>
+        <v>36</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>1043</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1392</v>
+        <v>1365</v>
       </c>
       <c r="B220" t="s">
-        <v>1044</v>
+        <v>1700</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>1045</v>
+        <v>1266</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>1046</v>
+        <v>1238</v>
       </c>
       <c r="E220" t="s">
-        <v>1593</v>
+        <v>1608</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>1047</v>
+        <v>4</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>1048</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1392</v>
+        <v>1371</v>
       </c>
       <c r="B221" t="s">
-        <v>1049</v>
+        <v>1208</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>1050</v>
+        <v>1209</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>1051</v>
+        <v>1210</v>
       </c>
       <c r="E221" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>1052</v>
+        <v>7</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>1053</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1392</v>
+        <v>1365</v>
       </c>
       <c r="B222" t="s">
-        <v>1054</v>
+        <v>771</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>1055</v>
+        <v>772</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>1056</v>
+        <v>773</v>
       </c>
       <c r="E222" t="s">
-        <v>1595</v>
+        <v>1517</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>1057</v>
+        <v>774</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>1058</v>
+        <v>775</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1392</v>
+        <v>1363</v>
       </c>
       <c r="B223" t="s">
-        <v>1059</v>
+        <v>656</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>1060</v>
+        <v>657</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>1061</v>
+        <v>658</v>
       </c>
       <c r="E223" t="s">
-        <v>1596</v>
+        <v>1501</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>482</v>
+        <v>659</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1062</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1392</v>
+        <v>1363</v>
       </c>
       <c r="B224" t="s">
-        <v>1063</v>
+        <v>439</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>1064</v>
+        <v>440</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>1065</v>
+        <v>441</v>
       </c>
       <c r="E224" t="s">
-        <v>1597</v>
+        <v>1458</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>1066</v>
+        <v>442</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>1067</v>
+        <v>443</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1392</v>
+        <v>1364</v>
       </c>
       <c r="B225" t="s">
-        <v>1068</v>
+        <v>1079</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>1069</v>
+        <v>1080</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>1070</v>
+        <v>1081</v>
       </c>
       <c r="E225" t="s">
-        <v>1598</v>
+        <v>1575</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>1072</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1392</v>
+        <v>1361</v>
       </c>
       <c r="B226" t="s">
-        <v>1073</v>
+        <v>184</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>1074</v>
+        <v>185</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E226" t="s">
-        <v>1599</v>
+        <v>186</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>1421</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>1075</v>
+        <v>187</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>1076</v>
+        <v>188</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1390</v>
+        <v>1365</v>
       </c>
       <c r="B227" t="s">
-        <v>1077</v>
+        <v>839</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>1078</v>
+        <v>840</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>1079</v>
+        <v>841</v>
       </c>
       <c r="E227" t="s">
-        <v>1600</v>
+        <v>1531</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>1080</v>
+        <v>842</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>1081</v>
+        <v>843</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1390</v>
+        <v>1364</v>
       </c>
       <c r="B228" t="s">
-        <v>1082</v>
+        <v>538</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>1083</v>
+        <v>539</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>1084</v>
+        <v>540</v>
       </c>
       <c r="E228" t="s">
-        <v>1601</v>
+        <v>1484</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>1085</v>
+        <v>1668</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>1086</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1390</v>
+        <v>1361</v>
       </c>
       <c r="B229" t="s">
-        <v>1087</v>
+        <v>104</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1088</v>
+        <v>1647</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E229" t="s">
-        <v>1602</v>
+        <v>105</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>1404</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>732</v>
+        <v>106</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1716</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1390</v>
+        <v>1361</v>
       </c>
       <c r="B230" t="s">
-        <v>1090</v>
+        <v>242</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>1091</v>
+        <v>243</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="E230" t="s">
-        <v>1603</v>
+        <v>244</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>1431</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>1093</v>
+        <v>245</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>1094</v>
+        <v>246</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1390</v>
+        <v>1367</v>
       </c>
       <c r="B231" t="s">
-        <v>1095</v>
+        <v>732</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>1096</v>
+        <v>733</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>1097</v>
+        <v>734</v>
       </c>
       <c r="E231" t="s">
-        <v>1604</v>
+        <v>1512</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>1098</v>
+        <v>735</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>1099</v>
+        <v>736</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B232" t="s">
+        <v>529</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="E232" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1393</v>
+        <v>1370</v>
       </c>
       <c r="B233" t="s">
-        <v>1100</v>
+        <v>1143</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>1101</v>
+        <v>1144</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>1102</v>
+        <v>1145</v>
       </c>
       <c r="E233" t="s">
-        <v>1605</v>
+        <v>1586</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>1103</v>
+        <v>1146</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>1104</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1394</v>
+        <v>1365</v>
       </c>
       <c r="B234" t="s">
-        <v>1105</v>
+        <v>751</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>1106</v>
+        <v>752</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>1107</v>
+        <v>753</v>
       </c>
       <c r="E234" t="s">
-        <v>1606</v>
+        <v>1513</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>1108</v>
+        <v>754</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>1109</v>
+        <v>755</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1394</v>
+        <v>1365</v>
       </c>
       <c r="B235" t="s">
-        <v>1110</v>
+        <v>864</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>1111</v>
+        <v>865</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>1112</v>
+        <v>866</v>
       </c>
       <c r="E235" t="s">
-        <v>1607</v>
+        <v>1536</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>1113</v>
+        <v>867</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>1114</v>
+        <v>868</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1394</v>
+        <v>1361</v>
       </c>
       <c r="B236" t="s">
-        <v>1117</v>
+        <v>137</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>1118</v>
+        <v>138</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E236" t="s">
-        <v>1608</v>
+        <v>139</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>1410</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>1120</v>
+        <v>140</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>1121</v>
+        <v>141</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1395</v>
+        <v>1370</v>
       </c>
       <c r="B237" t="s">
-        <v>1122</v>
+        <v>1170</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1123</v>
+        <v>1171</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>1124</v>
+        <v>1172</v>
       </c>
       <c r="E237" t="s">
-        <v>1609</v>
+        <v>1589</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>1125</v>
+        <v>1173</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>1126</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1395</v>
+        <v>1364</v>
       </c>
       <c r="B238" t="s">
-        <v>1127</v>
+        <v>541</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>1128</v>
+        <v>542</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>1129</v>
+        <v>543</v>
       </c>
       <c r="E238" t="s">
-        <v>1506</v>
+        <v>1485</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>1130</v>
+        <v>281</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>1131</v>
+        <v>544</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1395</v>
+        <v>1367</v>
       </c>
       <c r="B239" t="s">
-        <v>1132</v>
+        <v>1701</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>1133</v>
+        <v>1262</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>1134</v>
+        <v>1263</v>
       </c>
       <c r="E239" t="s">
-        <v>1514</v>
+        <v>1625</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>1135</v>
+        <v>1264</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>1136</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1395</v>
+        <v>1367</v>
       </c>
       <c r="B240" t="s">
-        <v>1137</v>
+        <v>741</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>1138</v>
+        <v>742</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>1139</v>
+        <v>743</v>
       </c>
       <c r="E240" t="s">
-        <v>1610</v>
+        <v>1513</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>1140</v>
+        <v>744</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>1141</v>
+        <v>745</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1395</v>
+        <v>1366</v>
       </c>
       <c r="B241" t="s">
-        <v>1142</v>
+        <v>1070</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1143</v>
+        <v>1071</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E241" t="s">
-        <v>1611</v>
+        <v>1573</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>1144</v>
+        <v>1072</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>1145</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1396</v>
+        <v>1373</v>
       </c>
       <c r="B242" t="s">
-        <v>1168</v>
+        <v>1250</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>1169</v>
+        <v>1251</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>1170</v>
+        <v>1252</v>
       </c>
       <c r="E242" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>1171</v>
+        <v>1253</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>1172</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1396</v>
+        <v>1362</v>
       </c>
       <c r="B243" t="s">
-        <v>1173</v>
+        <v>378</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>1174</v>
+        <v>379</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E243" t="s">
-        <v>1615</v>
+        <v>380</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>1453</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>1176</v>
+        <v>381</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>1177</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1396</v>
+        <v>1362</v>
       </c>
       <c r="B244" t="s">
-        <v>1178</v>
+        <v>284</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>1179</v>
+        <v>285</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="E244" t="s">
-        <v>1616</v>
+        <v>286</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>1439</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>1180</v>
+        <v>287</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1181</v>
+        <v>288</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1396</v>
+        <v>1362</v>
       </c>
       <c r="B245" t="s">
-        <v>1182</v>
+        <v>259</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>1183</v>
+        <v>260</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>1184</v>
-      </c>
-      <c r="E245" t="s">
-        <v>1617</v>
+        <v>261</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>1432</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>6</v>
+        <v>262</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1185</v>
+        <v>263</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1396</v>
+        <v>1364</v>
       </c>
       <c r="B246" t="s">
-        <v>1186</v>
+        <v>583</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>1187</v>
+        <v>584</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>1188</v>
+        <v>585</v>
       </c>
       <c r="E246" t="s">
-        <v>1618</v>
+        <v>1493</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>1189</v>
+        <v>586</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1190</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1396</v>
+        <v>1366</v>
       </c>
       <c r="B247" t="s">
-        <v>1191</v>
+        <v>1013</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1192</v>
+        <v>1014</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1193</v>
+        <v>1015</v>
       </c>
       <c r="E247" t="s">
-        <v>1619</v>
+        <v>1562</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>1194</v>
+        <v>1016</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1195</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1396</v>
+        <v>1367</v>
       </c>
       <c r="B248" t="s">
-        <v>1196</v>
+        <v>746</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>1197</v>
+        <v>747</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>1198</v>
+        <v>748</v>
       </c>
       <c r="E248" t="s">
-        <v>1620</v>
+        <v>1634</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>1199</v>
+        <v>749</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>1200</v>
+        <v>750</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1397</v>
+        <v>1362</v>
       </c>
       <c r="B249" t="s">
-        <v>1201</v>
+        <v>264</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>1202</v>
+        <v>265</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E249" t="s">
-        <v>1621</v>
+        <v>266</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>1433</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>1204</v>
+        <v>267</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1205</v>
+        <v>268</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1397</v>
+        <v>1373</v>
       </c>
       <c r="B250" t="s">
-        <v>1206</v>
+        <v>1225</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>1207</v>
+        <v>1226</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>1208</v>
+        <v>1227</v>
       </c>
       <c r="E250" t="s">
-        <v>1622</v>
+        <v>1601</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>1209</v>
+        <v>1228</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1210</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1397</v>
+        <v>1361</v>
       </c>
       <c r="B251" t="s">
-        <v>1211</v>
+        <v>26</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1212</v>
+        <v>27</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>1213</v>
-      </c>
-      <c r="E251" t="s">
-        <v>1623</v>
+        <v>28</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>1386</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1214</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1398</v>
+        <v>1361</v>
       </c>
       <c r="B252" t="s">
-        <v>1215</v>
+        <v>247</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>1216</v>
+        <v>248</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E252" t="s">
-        <v>1624</v>
+        <v>249</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>1409</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>1217</v>
+        <v>1641</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>1218</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1399</v>
+        <v>1363</v>
       </c>
       <c r="B253" t="s">
-        <v>1219</v>
+        <v>700</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>1220</v>
+        <v>701</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>1221</v>
+        <v>702</v>
       </c>
       <c r="E253" t="s">
-        <v>1625</v>
+        <v>1508</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>1102</v>
+        <v>4</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>1222</v>
+        <v>703</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1399</v>
+        <v>1365</v>
       </c>
       <c r="B254" t="s">
-        <v>1223</v>
+        <v>1347</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>1224</v>
+        <v>1348</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>1225</v>
+        <v>1349</v>
       </c>
       <c r="E254" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>1226</v>
+        <v>1350</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1227</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1399</v>
+        <v>1364</v>
       </c>
       <c r="B255" t="s">
-        <v>1228</v>
+        <v>641</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>1229</v>
+        <v>642</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>1230</v>
+        <v>643</v>
       </c>
       <c r="E255" t="s">
-        <v>1627</v>
+        <v>1499</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>1231</v>
+        <v>644</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1232</v>
+        <v>645</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1399</v>
+        <v>1363</v>
       </c>
       <c r="B256" t="s">
-        <v>1233</v>
+        <v>704</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1234</v>
+        <v>705</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>1235</v>
+        <v>706</v>
       </c>
       <c r="E256" t="s">
-        <v>1628</v>
+        <v>1508</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>1236</v>
+        <v>707</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>1237</v>
+        <v>708</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1399</v>
+        <v>1370</v>
       </c>
       <c r="B257" t="s">
-        <v>1238</v>
+        <v>1183</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1239</v>
+        <v>1184</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>1240</v>
+        <v>1185</v>
       </c>
       <c r="E257" t="s">
-        <v>1629</v>
+        <v>1592</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>1241</v>
+        <v>1186</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>1242</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1399</v>
+        <v>1361</v>
       </c>
       <c r="B258" t="s">
-        <v>1243</v>
+        <v>199</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>1244</v>
+        <v>200</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>1245</v>
-      </c>
-      <c r="E258" t="s">
-        <v>1630</v>
+        <v>201</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>1424</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>1246</v>
+        <v>202</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>1247</v>
+        <v>203</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1399</v>
+        <v>1361</v>
       </c>
       <c r="B259" t="s">
-        <v>1248</v>
+        <v>189</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1249</v>
+        <v>190</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>1250</v>
-      </c>
-      <c r="E259" t="s">
-        <v>1631</v>
+        <v>191</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>1422</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>1251</v>
+        <v>192</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>1252</v>
+        <v>193</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1399</v>
+        <v>1365</v>
       </c>
       <c r="B260" t="s">
-        <v>1253</v>
+        <v>913</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>1254</v>
+        <v>914</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>1255</v>
+        <v>915</v>
       </c>
       <c r="E260" t="s">
-        <v>1632</v>
+        <v>1546</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>1256</v>
+        <v>916</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>1257</v>
+        <v>917</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1401</v>
+        <v>1366</v>
       </c>
       <c r="B261" t="s">
-        <v>1259</v>
+        <v>973</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>1260</v>
+        <v>974</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>1261</v>
+        <v>975</v>
       </c>
       <c r="E261" t="s">
-        <v>1633</v>
+        <v>1556</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>1262</v>
+        <v>976</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>1263</v>
+        <v>977</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1393</v>
+        <v>1362</v>
       </c>
       <c r="B262" t="s">
-        <v>1264</v>
+        <v>346</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>1402</v>
+        <v>347</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>1265</v>
-      </c>
-      <c r="E262" t="s">
-        <v>1650</v>
+        <v>348</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>1447</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>1266</v>
+        <v>349</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>1403</v>
+        <v>350</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1393</v>
+        <v>1367</v>
       </c>
       <c r="B263" t="s">
-        <v>1267</v>
+        <v>1715</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>1268</v>
+        <v>737</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1269</v>
+        <v>738</v>
       </c>
       <c r="E263" t="s">
-        <v>1651</v>
+        <v>1485</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>1270</v>
+        <v>739</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>1271</v>
+        <v>740</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1391</v>
+        <v>1365</v>
       </c>
       <c r="B264" t="s">
-        <v>1272</v>
+        <v>796</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>1273</v>
+        <v>797</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>1241</v>
+        <v>798</v>
       </c>
       <c r="E264" t="s">
-        <v>1634</v>
+        <v>1522</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>4</v>
+        <v>799</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1274</v>
+        <v>800</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1400</v>
+        <v>1363</v>
       </c>
       <c r="B265" t="s">
-        <v>1275</v>
+        <v>396</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1276</v>
+        <v>397</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1277</v>
-      </c>
-      <c r="E265" t="s">
-        <v>1521</v>
+        <v>398</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>1455</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>1278</v>
+        <v>399</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1279</v>
+        <v>400</v>
+      </c>
+      <c r="L265" t="s">
+        <v>1360</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1391</v>
+        <v>1364</v>
       </c>
       <c r="B266" t="s">
-        <v>1280</v>
+        <v>559</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>1281</v>
+        <v>560</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>1282</v>
+        <v>561</v>
       </c>
       <c r="E266" t="s">
-        <v>1635</v>
+        <v>1488</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>1283</v>
+        <v>562</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1284</v>
-      </c>
-      <c r="L266" t="s">
-        <v>1386</v>
+        <v>563</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1401</v>
+        <v>1373</v>
       </c>
       <c r="B267" t="s">
-        <v>1285</v>
+        <v>1714</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>1286</v>
+        <v>1325</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1287</v>
+        <v>1326</v>
       </c>
       <c r="E267" t="s">
-        <v>1636</v>
+        <v>1616</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>1288</v>
+        <v>1327</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1289</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1401</v>
+        <v>1369</v>
       </c>
       <c r="B268" t="s">
-        <v>1290</v>
+        <v>1139</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>1291</v>
+        <v>1140</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1292</v>
+        <v>8</v>
       </c>
       <c r="E268" t="s">
-        <v>1637</v>
+        <v>1585</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>1293</v>
+        <v>1141</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1294</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1393</v>
+        <v>1368</v>
       </c>
       <c r="B269" t="s">
-        <v>1295</v>
+        <v>1102</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>1296</v>
+        <v>1103</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1297</v>
+        <v>1104</v>
       </c>
       <c r="E269" t="s">
-        <v>1638</v>
+        <v>1580</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>1298</v>
+        <v>1105</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1711</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1393</v>
+        <v>1361</v>
       </c>
       <c r="B270" t="s">
-        <v>1299</v>
+        <v>16</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>1300</v>
+        <v>17</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1301</v>
-      </c>
-      <c r="E270" t="s">
-        <v>1639</v>
+        <v>18</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>1384</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>1302</v>
+        <v>19</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1303</v>
+        <v>20</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1391</v>
+        <v>1362</v>
       </c>
       <c r="B271" t="s">
-        <v>1304</v>
+        <v>331</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>1305</v>
+        <v>332</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E271" t="s">
-        <v>1488</v>
+        <v>333</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>1629</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>1307</v>
+        <v>334</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1308</v>
+        <v>335</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1392</v>
+        <v>1364</v>
       </c>
       <c r="B272" t="s">
-        <v>1309</v>
+        <v>474</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>1310</v>
+        <v>475</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>1311</v>
+        <v>476</v>
       </c>
       <c r="E272" t="s">
-        <v>1586</v>
+        <v>1470</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>1312</v>
+        <v>477</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1313</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>1361</v>
+      </c>
       <c r="B273" t="s">
-        <v>1314</v>
+        <v>250</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>1315</v>
+        <v>251</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>1316</v>
-      </c>
-      <c r="E273" t="s">
-        <v>1640</v>
+        <v>252</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>1437</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>1258</v>
+        <v>253</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1317</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1391</v>
+        <v>1361</v>
       </c>
       <c r="B274" t="s">
-        <v>1318</v>
+        <v>57</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>1319</v>
+        <v>58</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>1320</v>
-      </c>
-      <c r="E274" t="s">
-        <v>1480</v>
+        <v>59</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>1395</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>1321</v>
+        <v>1652</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1322</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="275" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1391</v>
+        <v>1374</v>
       </c>
       <c r="B275" t="s">
-        <v>1323</v>
+        <v>1336</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>1324</v>
+        <v>1337</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>1325</v>
+        <v>1338</v>
       </c>
       <c r="E275" t="s">
-        <v>1480</v>
+        <v>1619</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>1393</v>
+        <v>1361</v>
       </c>
       <c r="B276" t="s">
-        <v>1328</v>
+        <v>46</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>1329</v>
+        <v>47</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1330</v>
-      </c>
-      <c r="E276" t="s">
-        <v>1641</v>
+        <v>48</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>1392</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>1331</v>
+        <v>49</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>1389</v>
+        <v>1361</v>
       </c>
       <c r="B277" t="s">
-        <v>1333</v>
+        <v>142</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>1334</v>
+        <v>143</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>1335</v>
-      </c>
-      <c r="E277" t="s">
-        <v>1493</v>
+        <v>144</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>1411</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>1336</v>
+        <v>145</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1337</v>
+        <v>146</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1389</v>
+        <v>1363</v>
       </c>
       <c r="B278" t="s">
-        <v>1338</v>
+        <v>415</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>1339</v>
+        <v>416</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>1340</v>
-      </c>
-      <c r="E278" t="s">
-        <v>1478</v>
+        <v>417</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>1631</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>1341</v>
+        <v>418</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>1389</v>
+        <v>1363</v>
       </c>
       <c r="B279" t="s">
-        <v>1342</v>
+        <v>459</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>1343</v>
+        <v>460</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1344</v>
+        <v>461</v>
       </c>
       <c r="E279" t="s">
-        <v>1516</v>
+        <v>1467</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>1345</v>
+        <v>462</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1346</v>
+        <v>463</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>1399</v>
+        <v>1362</v>
       </c>
       <c r="B280" t="s">
-        <v>1347</v>
+        <v>373</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>1348</v>
+        <v>374</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>1349</v>
-      </c>
-      <c r="E280" t="s">
-        <v>1642</v>
+        <v>375</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>1452</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>1350</v>
+        <v>376</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>1395</v>
+        <v>1365</v>
       </c>
       <c r="B281" t="s">
-        <v>1352</v>
+        <v>869</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>1353</v>
+        <v>870</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>1354</v>
+        <v>871</v>
       </c>
       <c r="E281" t="s">
-        <v>1643</v>
+        <v>1537</v>
       </c>
       <c r="F281" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="G281" s="1" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B282" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E282" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F282" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G282" s="1" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B283" t="s">
+        <v>151</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F283" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G281" s="1" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B282" t="s">
-        <v>1356</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>1357</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>1358</v>
-      </c>
-      <c r="E282" t="s">
-        <v>1644</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>1359</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A283" t="s">
-        <v>1400</v>
-      </c>
-      <c r="B283" t="s">
-        <v>1361</v>
-      </c>
-      <c r="C283" s="1" t="s">
-        <v>1362</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>1363</v>
-      </c>
-      <c r="E283" t="s">
-        <v>1645</v>
-      </c>
-      <c r="F283" s="2" t="s">
+      <c r="G283" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
         <v>1364</v>
       </c>
-      <c r="G283" s="1" t="s">
+      <c r="B284" t="s">
+        <v>519</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="E284" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F284" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="G284" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
         <v>1365</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A284" t="s">
-        <v>1394</v>
-      </c>
-      <c r="B284" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C284" s="1" t="s">
-        <v>1366</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E284" t="s">
-        <v>1646</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>1367</v>
-      </c>
-      <c r="G284" s="1" t="s">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A285" t="s">
-        <v>1395</v>
-      </c>
       <c r="B285" t="s">
-        <v>1369</v>
+        <v>948</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>1708</v>
+        <v>949</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>1370</v>
+        <v>950</v>
       </c>
       <c r="E285" t="s">
-        <v>1500</v>
+        <v>1526</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>1371</v>
+        <v>951</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1709</v>
+        <v>952</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>1391</v>
+        <v>1362</v>
       </c>
       <c r="B286" t="s">
-        <v>1372</v>
+        <v>274</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>1373</v>
+        <v>275</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>1374</v>
-      </c>
-      <c r="E286" t="s">
-        <v>1647</v>
+        <v>276</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>1435</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>1375</v>
+        <v>277</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>1393</v>
+        <v>1362</v>
       </c>
       <c r="B287" t="s">
-        <v>1377</v>
+        <v>387</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>1378</v>
+        <v>388</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1379</v>
-      </c>
-      <c r="E287" t="s">
-        <v>1521</v>
+        <v>389</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>1435</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>1380</v>
+        <v>390</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1381</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>1397</v>
+        <v>1366</v>
       </c>
       <c r="B288" t="s">
-        <v>1206</v>
+        <v>983</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>1382</v>
+        <v>984</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>1383</v>
+        <v>985</v>
       </c>
       <c r="E288" t="s">
-        <v>1648</v>
+        <v>1557</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>1384</v>
+        <v>986</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1385</v>
+        <v>987</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1396</v>
+        <v>1368</v>
       </c>
       <c r="B289" t="s">
-        <v>1146</v>
+        <v>1107</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>1147</v>
+        <v>1108</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1148</v>
+        <v>1109</v>
       </c>
       <c r="E289" t="s">
-        <v>1612</v>
+        <v>1581</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>1149</v>
+        <v>1110</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A290" s="5" t="s">
-        <v>1396</v>
-      </c>
-      <c r="B290" s="6" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C290" s="7" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D290" s="7" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E290" s="6" t="s">
-        <v>1613</v>
-      </c>
-      <c r="F290" s="8" t="s">
-        <v>1166</v>
-      </c>
-      <c r="G290" s="7" t="s">
-        <v>1167</v>
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B290" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E290" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F290" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G290" s="1" t="s">
+        <v>1331</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>1396</v>
+        <v>1363</v>
       </c>
       <c r="B291" t="s">
-        <v>1151</v>
+        <v>660</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>1152</v>
+        <v>661</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>1153</v>
+        <v>662</v>
       </c>
       <c r="E291" t="s">
-        <v>1482</v>
+        <v>1502</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>1154</v>
+        <v>663</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>1707</v>
+        <v>664</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>1396</v>
+        <v>1361</v>
       </c>
       <c r="B292" t="s">
-        <v>1155</v>
+        <v>44</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>1156</v>
+        <v>1645</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E292" t="s">
-        <v>1634</v>
+        <v>45</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>1391</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>1158</v>
+        <v>6</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1159</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>1396</v>
+        <v>1361</v>
       </c>
       <c r="B293" t="s">
-        <v>1160</v>
+        <v>37</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>1161</v>
+        <v>38</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="E293" t="s">
-        <v>1649</v>
+        <v>39</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>1389</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>1705</v>
+        <v>40</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>1393</v>
-      </c>
-      <c r="B294" t="s">
-        <v>1712</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>1713</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>1714</v>
-      </c>
-      <c r="E294" t="s">
-        <v>1717</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>1715</v>
-      </c>
-      <c r="G294" t="s">
-        <v>1718</v>
+        <v>1644</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G293">
+    <sortCondition ref="B1:B293"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/data/Russian_Words_Cards.xlsx
+++ b/public/data/Russian_Words_Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4554F4C-F372-493B-BAE7-55468E077B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921BD1E2-3812-42F2-9863-D6610B177472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="1722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="1722">
   <si>
     <t>Topic</t>
   </si>
@@ -4792,9 +4792,6 @@
     <t>😌</t>
   </si>
   <si>
-    <t>😨</t>
-  </si>
-  <si>
     <t>🐶</t>
   </si>
   <si>
@@ -4802,9 +4799,6 @@
   </si>
   <si>
     <t>🐮</t>
-  </si>
-  <si>
-    <t>🐴</t>
   </si>
   <si>
     <t>🐷</t>
@@ -5437,6 +5431,12 @@
   </si>
   <si>
     <t>бедный</t>
+  </si>
+  <si>
+    <t>🫏</t>
+  </si>
+  <si>
+    <t>🐑</t>
   </si>
 </sst>
 </file>
@@ -5513,7 +5513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -5532,6 +5532,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5852,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1381</v>
@@ -5860,7 +5866,7 @@
       <c r="D1" s="3" t="s">
         <v>1380</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="9" t="s">
         <v>1383</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -5872,25 +5878,25 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="B2" t="s">
-        <v>894</v>
+        <v>209</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>895</v>
+        <v>210</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1542</v>
+        <v>211</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1625</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>897</v>
+        <v>212</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>898</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -5898,22 +5904,22 @@
         <v>1361</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1396</v>
+        <v>1411</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -5921,183 +5927,183 @@
         <v>1361</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1415</v>
+        <v>1425</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="B5" t="s">
-        <v>918</v>
+        <v>250</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>919</v>
+        <v>251</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>920</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1547</v>
+        <v>252</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1437</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>921</v>
+        <v>253</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>922</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="B6" t="s">
-        <v>510</v>
+        <v>179</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>511</v>
+        <v>180</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1478</v>
+        <v>181</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1419</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>513</v>
+        <v>182</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="B7" t="s">
-        <v>1721</v>
+        <v>189</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1352</v>
+        <v>190</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1353</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1495</v>
+        <v>191</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1422</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1354</v>
+        <v>192</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1355</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="B8" t="s">
-        <v>884</v>
+        <v>156</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>885</v>
+        <v>157</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1540</v>
+        <v>158</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1414</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>887</v>
+        <v>159</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>888</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="B9" t="s">
-        <v>1092</v>
+        <v>75</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1093</v>
+        <v>76</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1578</v>
+        <v>77</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1399</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1095</v>
+        <v>78</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1096</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="B10" t="s">
-        <v>1017</v>
+        <v>166</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1018</v>
+        <v>167</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1488</v>
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1416</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1020</v>
+        <v>168</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1021</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B11" t="s">
-        <v>696</v>
+        <v>161</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>697</v>
+        <v>162</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1508</v>
+        <v>163</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1415</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>698</v>
+        <v>164</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>699</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -6105,91 +6111,91 @@
         <v>1361</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1409</v>
+        <v>1396</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>135</v>
+        <v>63</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="B13" t="s">
-        <v>1026</v>
+        <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1027</v>
+        <v>1643</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1028</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1564</v>
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1391</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1029</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1030</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="B14" t="s">
-        <v>1240</v>
+        <v>90</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1241</v>
+        <v>91</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1242</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1604</v>
+        <v>92</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1402</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1243</v>
+        <v>93</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1244</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="B15" t="s">
-        <v>574</v>
+        <v>184</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>575</v>
+        <v>185</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1491</v>
+        <v>186</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1421</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>577</v>
+        <v>187</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>578</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -6197,45 +6203,45 @@
         <v>1361</v>
       </c>
       <c r="B16" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>229</v>
+        <v>171</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1428</v>
+        <v>1417</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>231</v>
+        <v>173</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>1696</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="B17" t="s">
-        <v>341</v>
+        <v>127</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>342</v>
+        <v>128</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>343</v>
+        <v>129</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1446</v>
+        <v>1408</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>344</v>
+        <v>130</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>345</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -6243,160 +6249,160 @@
         <v>1361</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>237</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>100</v>
+        <v>238</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>101</v>
+        <v>239</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1420</v>
+        <v>1430</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>102</v>
+        <v>240</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>103</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B19" t="s">
-        <v>683</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>684</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1506</v>
+        <v>18</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>1384</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>687</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="B20" t="s">
-        <v>933</v>
+        <v>218</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>934</v>
+        <v>219</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1549</v>
+        <v>220</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>1626</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>936</v>
+        <v>221</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>937</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1370</v>
+        <v>1361</v>
       </c>
       <c r="B21" t="s">
-        <v>1152</v>
+        <v>112</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1153</v>
+        <v>113</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1154</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1608</v>
+        <v>114</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>1406</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1155</v>
+        <v>115</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1156</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1370</v>
+        <v>1361</v>
       </c>
       <c r="B22" t="s">
-        <v>1175</v>
+        <v>213</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1176</v>
+        <v>214</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1590</v>
+        <v>215</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1426</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1177</v>
+        <v>216</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1178</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B23" t="s">
-        <v>406</v>
+        <v>223</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>407</v>
+        <v>224</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>408</v>
+        <v>225</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1457</v>
+        <v>1427</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>409</v>
+        <v>226</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>410</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="B24" t="s">
-        <v>534</v>
+        <v>95</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>535</v>
+        <v>96</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1483</v>
+        <v>97</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>1403</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>537</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -6404,22 +6410,22 @@
         <v>1361</v>
       </c>
       <c r="B25" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -6427,22 +6433,22 @@
         <v>1361</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -6450,45 +6456,45 @@
         <v>1361</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1417</v>
+        <v>1424</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B28" t="s">
-        <v>688</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>689</v>
+        <v>34</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1507</v>
+        <v>35</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>1388</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>691</v>
+        <v>36</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>692</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -6508,286 +6514,286 @@
         <v>1393</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="B30" t="s">
-        <v>1031</v>
+        <v>57</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1032</v>
+        <v>58</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1565</v>
+        <v>59</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>1395</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>1034</v>
+        <v>1650</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1035</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="B31" t="s">
-        <v>810</v>
+        <v>254</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>811</v>
+        <v>255</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1525</v>
+        <v>256</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>1438</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>813</v>
+        <v>257</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>814</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B32" t="s">
-        <v>665</v>
+        <v>80</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>666</v>
+        <v>81</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1464</v>
+        <v>82</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>1400</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>668</v>
+        <v>83</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1672</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B33" t="s">
-        <v>673</v>
+        <v>1695</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>674</v>
+        <v>1647</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1504</v>
+        <v>41</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>1390</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>676</v>
+        <v>42</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>677</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1372</v>
+        <v>1361</v>
       </c>
       <c r="B34" t="s">
-        <v>1212</v>
+        <v>70</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1213</v>
+        <v>71</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1598</v>
+        <v>72</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>1398</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1214</v>
+        <v>73</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>1215</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B35" t="s">
-        <v>434</v>
+        <v>232</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>435</v>
+        <v>233</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1463</v>
+        <v>234</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>1429</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>437</v>
+        <v>235</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>438</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1375</v>
+        <v>1361</v>
       </c>
       <c r="B36" t="s">
-        <v>1698</v>
+        <v>37</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1256</v>
+        <v>38</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1257</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1607</v>
+        <v>39</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>1389</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1258</v>
+        <v>40</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1259</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="B37" t="s">
-        <v>469</v>
+        <v>21</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>470</v>
+        <v>22</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1469</v>
+        <v>23</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>1385</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>472</v>
+        <v>24</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>473</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B38" t="s">
-        <v>429</v>
+        <v>175</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>430</v>
+        <v>176</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>431</v>
+        <v>177</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1459</v>
+        <v>1418</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>432</v>
+        <v>5</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>433</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="B39" t="s">
-        <v>938</v>
+        <v>132</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>939</v>
+        <v>133</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1550</v>
+        <v>134</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>1409</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>941</v>
+        <v>135</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>942</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="B40" t="s">
-        <v>1046</v>
+        <v>247</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1047</v>
+        <v>248</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E40" t="s">
-        <v>1568</v>
+        <v>249</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>1409</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>1049</v>
+        <v>1639</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1050</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="B41" t="s">
-        <v>968</v>
+        <v>117</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>969</v>
+        <v>118</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>970</v>
-      </c>
-      <c r="E41" t="s">
-        <v>1555</v>
+        <v>119</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>1407</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>971</v>
+        <v>120</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>972</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -6795,22 +6801,22 @@
         <v>1361</v>
       </c>
       <c r="B42" t="s">
-        <v>194</v>
+        <v>122</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>195</v>
+        <v>123</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>196</v>
+        <v>124</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1423</v>
+        <v>1404</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>197</v>
+        <v>125</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>198</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -6818,22 +6824,22 @@
         <v>1361</v>
       </c>
       <c r="B43" t="s">
-        <v>254</v>
+        <v>104</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>255</v>
+        <v>1645</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>256</v>
+        <v>105</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1438</v>
+        <v>1404</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>257</v>
+        <v>106</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>258</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -6841,91 +6847,91 @@
         <v>1361</v>
       </c>
       <c r="B44" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1414</v>
+        <v>1405</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1370</v>
+        <v>1361</v>
       </c>
       <c r="B45" t="s">
-        <v>1188</v>
+        <v>30</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1189</v>
+        <v>31</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="E45" t="s">
-        <v>1593</v>
+        <v>32</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>1387</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>1191</v>
+        <v>1652</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1192</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="B46" t="s">
-        <v>1699</v>
+        <v>228</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1376</v>
+        <v>229</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="E46" t="s">
-        <v>1624</v>
+        <v>230</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>1428</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>1261</v>
+        <v>231</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>1377</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="B47" t="s">
-        <v>723</v>
+        <v>147</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>724</v>
+        <v>148</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="E47" t="s">
-        <v>1510</v>
+        <v>149</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>1412</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>726</v>
+        <v>150</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1677</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -6933,183 +6939,183 @@
         <v>1361</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1402</v>
+        <v>1386</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>94</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="B49" t="s">
-        <v>1686</v>
+        <v>137</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1687</v>
+        <v>138</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1688</v>
-      </c>
-      <c r="E49" t="s">
-        <v>1691</v>
+        <v>139</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>1410</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>1689</v>
-      </c>
-      <c r="G49" t="s">
-        <v>1692</v>
+        <v>140</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B50" t="s">
-        <v>693</v>
+        <v>151</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>694</v>
+        <v>152</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="E50" t="s">
-        <v>1508</v>
+        <v>153</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>1413</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>1674</v>
+        <v>154</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1675</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="B51" t="s">
-        <v>579</v>
+        <v>65</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>580</v>
+        <v>66</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E51" t="s">
-        <v>1492</v>
+        <v>67</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>1397</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>582</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="B52" t="s">
-        <v>302</v>
+        <v>54</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>303</v>
+        <v>1648</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>304</v>
+        <v>55</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1442</v>
+        <v>1394</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>305</v>
+        <v>56</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>306</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="B53" t="s">
-        <v>506</v>
+        <v>85</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>507</v>
+        <v>86</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E53" t="s">
-        <v>1477</v>
+        <v>87</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>1401</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1667</v>
+        <v>88</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>509</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B54" t="s">
-        <v>401</v>
+        <v>99</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>402</v>
+        <v>100</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>403</v>
+        <v>101</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1456</v>
+        <v>1420</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>404</v>
+        <v>102</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>405</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1374</v>
+        <v>1361</v>
       </c>
       <c r="B55" t="s">
-        <v>1704</v>
+        <v>194</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1268</v>
+        <v>195</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="E55" t="s">
-        <v>1495</v>
+        <v>196</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>1423</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>1270</v>
+        <v>197</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>1271</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -7117,137 +7123,137 @@
         <v>1362</v>
       </c>
       <c r="B56" t="s">
-        <v>279</v>
+        <v>373</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>280</v>
+        <v>374</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>281</v>
+        <v>375</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1436</v>
+        <v>1452</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>282</v>
+        <v>376</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>283</v>
+        <v>377</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1370</v>
+        <v>1362</v>
       </c>
       <c r="B57" t="s">
-        <v>1165</v>
+        <v>336</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1166</v>
+        <v>337</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1167</v>
-      </c>
-      <c r="E57" t="s">
-        <v>1588</v>
+        <v>338</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>1445</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>1168</v>
+        <v>339</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>1169</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="B58" t="s">
-        <v>978</v>
+        <v>382</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>979</v>
+        <v>383</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>980</v>
-      </c>
-      <c r="E58" t="s">
-        <v>1440</v>
+        <v>384</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>1432</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>981</v>
+        <v>385</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>982</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="B59" t="s">
-        <v>1003</v>
+        <v>259</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1004</v>
+        <v>260</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E59" t="s">
-        <v>1556</v>
+        <v>261</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>1432</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>1006</v>
+        <v>262</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1007</v>
+        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1373</v>
+        <v>1362</v>
       </c>
       <c r="B60" t="s">
-        <v>1230</v>
+        <v>294</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1231</v>
+        <v>295</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1232</v>
-      </c>
-      <c r="E60" t="s">
-        <v>1602</v>
+        <v>1460</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>1440</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>1233</v>
+        <v>296</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>1234</v>
+        <v>297</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B61" t="s">
-        <v>492</v>
+        <v>289</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>493</v>
+        <v>290</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="E61" t="s">
-        <v>1474</v>
+        <v>291</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>1440</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>495</v>
+        <v>292</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>496</v>
+        <v>293</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -7255,298 +7261,298 @@
         <v>1362</v>
       </c>
       <c r="B62" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>359</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>392</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>167</v>
+        <v>393</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>10</v>
+        <v>394</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1416</v>
+        <v>1454</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>168</v>
+        <v>1</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>169</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="B64" t="s">
-        <v>834</v>
+        <v>360</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>835</v>
+        <v>361</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="E64" t="s">
-        <v>1530</v>
+        <v>362</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>1450</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>837</v>
+        <v>363</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>838</v>
+        <v>364</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B65" t="s">
-        <v>545</v>
+        <v>326</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>546</v>
+        <v>327</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="E65" t="s">
-        <v>1432</v>
+        <v>328</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>1444</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>548</v>
+        <v>329</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>549</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B66" t="s">
-        <v>569</v>
+        <v>321</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>570</v>
+        <v>322</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="E66" t="s">
-        <v>1490</v>
+        <v>323</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>1435</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>572</v>
+        <v>324</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>573</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1373</v>
+        <v>1362</v>
       </c>
       <c r="B67" t="s">
-        <v>1235</v>
+        <v>274</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1236</v>
+        <v>275</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1237</v>
-      </c>
-      <c r="E67" t="s">
-        <v>1603</v>
+        <v>276</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>1435</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>1238</v>
+        <v>277</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>1239</v>
+        <v>278</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B68" t="s">
-        <v>564</v>
+        <v>387</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>565</v>
+        <v>388</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E68" t="s">
-        <v>1489</v>
+        <v>389</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>1435</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>567</v>
+        <v>390</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>568</v>
+        <v>391</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="B69" t="s">
-        <v>1056</v>
+        <v>302</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1057</v>
+        <v>303</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E69" t="s">
-        <v>1570</v>
+        <v>304</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>1442</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>480</v>
+        <v>305</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>1059</v>
+        <v>306</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B70" t="s">
-        <v>616</v>
+        <v>351</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>617</v>
+        <v>352</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="E70" t="s">
-        <v>1496</v>
+        <v>353</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>1448</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>619</v>
+        <v>354</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>620</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="B71" t="s">
-        <v>669</v>
+        <v>346</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>670</v>
+        <v>347</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="E71" t="s">
-        <v>1503</v>
+        <v>348</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>1447</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>672</v>
+        <v>349</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>1673</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="B72" t="s">
-        <v>1720</v>
+        <v>355</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1332</v>
+        <v>356</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>1333</v>
-      </c>
-      <c r="E72" t="s">
-        <v>1618</v>
+        <v>357</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>1449</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>1334</v>
+        <v>358</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>1335</v>
+        <v>359</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="B73" t="s">
-        <v>820</v>
+        <v>341</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>821</v>
+        <v>342</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="E73" t="s">
-        <v>1527</v>
+        <v>343</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>1446</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>823</v>
+        <v>344</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>824</v>
+        <v>345</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B74" t="s">
-        <v>1084</v>
+        <v>279</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1085</v>
+        <v>280</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E74" t="s">
-        <v>1576</v>
+        <v>281</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>1436</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>730</v>
+        <v>282</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>1690</v>
+        <v>283</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -7554,321 +7560,321 @@
         <v>1362</v>
       </c>
       <c r="B75" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1443</v>
+        <v>1436</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>316</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B76" t="s">
-        <v>209</v>
+        <v>370</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>210</v>
+        <v>1657</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>211</v>
+        <v>371</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1627</v>
+        <v>1451</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>212</v>
+        <v>372</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1637</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="5" t="s">
-        <v>1370</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>1161</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>1162</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>1163</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>1164</v>
+      <c r="A77" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B77" t="s">
+        <v>269</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="B78" t="s">
-        <v>727</v>
+        <v>365</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>728</v>
+        <v>366</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="E78" t="s">
-        <v>1511</v>
+        <v>367</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>1434</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>730</v>
+        <v>368</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>731</v>
+        <v>369</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="B79" t="s">
-        <v>874</v>
+        <v>331</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>875</v>
+        <v>332</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="E79" t="s">
-        <v>1538</v>
+        <v>333</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>1627</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>877</v>
+        <v>334</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>878</v>
+        <v>335</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B80" t="s">
-        <v>488</v>
+        <v>307</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>489</v>
+        <v>308</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="E80" t="s">
-        <v>1473</v>
+        <v>309</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>1461</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>491</v>
+        <v>310</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1665</v>
+        <v>311</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B81" t="s">
-        <v>555</v>
+        <v>284</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>556</v>
+        <v>285</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="E81" t="s">
-        <v>1487</v>
+        <v>286</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>1439</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>9</v>
+        <v>287</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>558</v>
+        <v>288</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B82" t="s">
-        <v>483</v>
+        <v>264</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>484</v>
+        <v>265</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="E82" t="s">
-        <v>1472</v>
+        <v>266</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>1433</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>486</v>
+        <v>267</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>487</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="B83" t="s">
-        <v>943</v>
+        <v>312</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>944</v>
+        <v>313</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="E83" t="s">
-        <v>1551</v>
+        <v>314</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>1443</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>946</v>
+        <v>315</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>947</v>
+        <v>316</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="B84" t="s">
-        <v>1702</v>
+        <v>298</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>1272</v>
+        <v>299</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="E84" t="s">
-        <v>1609</v>
+        <v>300</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>1441</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>1274</v>
+        <v>2</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>1275</v>
+        <v>301</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B85" t="s">
-        <v>147</v>
+        <v>1347</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>148</v>
+        <v>1348</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>149</v>
+        <v>1349</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1412</v>
+        <v>1619</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>150</v>
+        <v>1350</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>1638</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="B86" t="s">
-        <v>360</v>
+        <v>1698</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>361</v>
+        <v>1266</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>362</v>
+        <v>1238</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1450</v>
+        <v>1606</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>363</v>
+        <v>4</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>364</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B87" t="s">
-        <v>1697</v>
+        <v>830</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1649</v>
+        <v>831</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>41</v>
+        <v>832</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1390</v>
+        <v>1527</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>42</v>
+        <v>833</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>43</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B88" t="s">
-        <v>122</v>
+        <v>889</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>123</v>
+        <v>890</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>124</v>
+        <v>891</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1404</v>
+        <v>1539</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>125</v>
+        <v>892</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>126</v>
+        <v>893</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -7876,68 +7882,68 @@
         <v>1365</v>
       </c>
       <c r="B89" t="s">
-        <v>889</v>
+        <v>913</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>890</v>
+        <v>914</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>891</v>
-      </c>
-      <c r="E89" t="s">
-        <v>1541</v>
+        <v>915</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>1544</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>892</v>
+        <v>916</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>893</v>
+        <v>917</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="B90" t="s">
-        <v>1124</v>
+        <v>874</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>1125</v>
+        <v>875</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E90" t="s">
-        <v>1480</v>
+        <v>876</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>1536</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>1127</v>
+        <v>877</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>1128</v>
+        <v>878</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="B91" t="s">
-        <v>307</v>
+        <v>786</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>308</v>
+        <v>787</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>309</v>
+        <v>788</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1461</v>
+        <v>1518</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>310</v>
+        <v>789</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>311</v>
+        <v>790</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -7945,45 +7951,45 @@
         <v>1365</v>
       </c>
       <c r="B92" t="s">
-        <v>776</v>
+        <v>849</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>777</v>
+        <v>850</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="E92" t="s">
-        <v>1518</v>
+        <v>851</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>1531</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>779</v>
+        <v>852</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>780</v>
+        <v>853</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B93" t="s">
-        <v>204</v>
+        <v>791</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>205</v>
+        <v>792</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>793</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>1425</v>
+        <v>1519</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>207</v>
+        <v>794</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>208</v>
+        <v>795</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -7991,91 +7997,91 @@
         <v>1365</v>
       </c>
       <c r="B94" t="s">
-        <v>923</v>
+        <v>943</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="E94" t="s">
-        <v>1548</v>
+        <v>945</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>1549</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>926</v>
+        <v>946</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>927</v>
+        <v>947</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="B95" t="s">
-        <v>326</v>
+        <v>839</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>327</v>
+        <v>840</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>328</v>
+        <v>841</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>1444</v>
+        <v>1529</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>329</v>
+        <v>842</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>330</v>
+        <v>843</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1375</v>
+        <v>1365</v>
       </c>
       <c r="B96" t="s">
-        <v>1703</v>
+        <v>963</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>1280</v>
+        <v>964</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>1281</v>
-      </c>
-      <c r="E96" t="s">
-        <v>1611</v>
+        <v>965</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>1552</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>1282</v>
+        <v>966</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>1283</v>
+        <v>967</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B97" t="s">
-        <v>223</v>
+        <v>899</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>224</v>
+        <v>900</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>225</v>
+        <v>901</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>1427</v>
+        <v>1541</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>226</v>
+        <v>115</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>227</v>
+        <v>902</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
@@ -8083,22 +8089,22 @@
         <v>1365</v>
       </c>
       <c r="B98" t="s">
-        <v>761</v>
+        <v>903</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>762</v>
+        <v>904</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="E98" t="s">
-        <v>1515</v>
+        <v>905</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>1542</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>764</v>
+        <v>906</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>765</v>
+        <v>907</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -8106,22 +8112,22 @@
         <v>1365</v>
       </c>
       <c r="B99" t="s">
-        <v>1711</v>
+        <v>869</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>1302</v>
+        <v>870</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>1303</v>
-      </c>
-      <c r="E99" t="s">
-        <v>1454</v>
+        <v>871</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>1535</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>1304</v>
+        <v>872</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>1305</v>
+        <v>873</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -8129,22 +8135,22 @@
         <v>1365</v>
       </c>
       <c r="B100" t="s">
-        <v>756</v>
+        <v>801</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>757</v>
+        <v>802</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="E100" t="s">
-        <v>1514</v>
+        <v>803</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>1521</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>759</v>
+        <v>804</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>760</v>
+        <v>805</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -8152,91 +8158,91 @@
         <v>1365</v>
       </c>
       <c r="B101" t="s">
-        <v>958</v>
+        <v>933</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>959</v>
+        <v>934</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>960</v>
-      </c>
-      <c r="E101" t="s">
-        <v>1553</v>
+        <v>935</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>1547</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>962</v>
+        <v>937</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B102" t="s">
-        <v>1074</v>
+        <v>825</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>1075</v>
+        <v>826</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="E102" t="s">
-        <v>1574</v>
+        <v>827</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>1526</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>1077</v>
+        <v>828</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1078</v>
+        <v>829</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="B103" t="s">
-        <v>317</v>
+        <v>771</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>318</v>
+        <v>772</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>319</v>
+        <v>773</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>1436</v>
+        <v>1517</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>320</v>
+        <v>774</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>1643</v>
+        <v>775</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="B104" t="s">
-        <v>269</v>
+        <v>820</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>270</v>
+        <v>821</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>271</v>
+        <v>822</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>1434</v>
+        <v>1525</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>272</v>
+        <v>823</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>273</v>
+        <v>824</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
@@ -8244,45 +8250,45 @@
         <v>1365</v>
       </c>
       <c r="B105" t="s">
-        <v>830</v>
+        <v>766</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>831</v>
+        <v>767</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="E105" t="s">
-        <v>1529</v>
+        <v>768</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>1515</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>833</v>
+        <v>769</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1694</v>
+        <v>770</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B106" t="s">
-        <v>179</v>
+        <v>776</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>180</v>
+        <v>777</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>181</v>
+        <v>778</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>1419</v>
+        <v>1518</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>182</v>
+        <v>779</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>183</v>
+        <v>780</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
@@ -8290,68 +8296,68 @@
         <v>1365</v>
       </c>
       <c r="B107" t="s">
-        <v>786</v>
+        <v>928</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>787</v>
+        <v>929</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="E107" t="s">
-        <v>1520</v>
+        <v>930</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>1720</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>789</v>
+        <v>931</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>790</v>
+        <v>932</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="B108" t="s">
-        <v>1114</v>
+        <v>761</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>1115</v>
+        <v>762</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E108" t="s">
-        <v>1582</v>
+        <v>763</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>1516</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>1117</v>
+        <v>764</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>1118</v>
+        <v>765</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="B109" t="s">
-        <v>382</v>
+        <v>781</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>383</v>
+        <v>782</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>384</v>
+        <v>783</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>1432</v>
+        <v>1721</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>385</v>
+        <v>784</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>386</v>
+        <v>785</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
@@ -8359,22 +8365,22 @@
         <v>1365</v>
       </c>
       <c r="B110" t="s">
-        <v>844</v>
+        <v>879</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>845</v>
+        <v>880</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>846</v>
-      </c>
-      <c r="E110" t="s">
-        <v>1532</v>
+        <v>881</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>1537</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>847</v>
+        <v>882</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>848</v>
+        <v>883</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
@@ -8382,183 +8388,183 @@
         <v>1365</v>
       </c>
       <c r="B111" t="s">
-        <v>1708</v>
+        <v>810</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>1291</v>
+        <v>811</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>1292</v>
-      </c>
-      <c r="E111" t="s">
-        <v>1462</v>
+        <v>812</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>1523</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>1293</v>
+        <v>813</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>1294</v>
+        <v>814</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B112" t="s">
-        <v>587</v>
+        <v>806</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>588</v>
+        <v>807</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="E112" t="s">
-        <v>1434</v>
+        <v>808</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>1522</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>590</v>
+        <v>809</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>591</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="B113" t="s">
-        <v>1041</v>
+        <v>884</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>1042</v>
+        <v>885</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>1043</v>
-      </c>
-      <c r="E113" t="s">
-        <v>1567</v>
+        <v>886</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>1538</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>1044</v>
+        <v>887</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>1045</v>
+        <v>888</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="B114" t="s">
-        <v>1148</v>
+        <v>1709</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>1149</v>
+        <v>1302</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="E114" t="s">
-        <v>1456</v>
+        <v>1303</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>1454</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>1151</v>
+        <v>1304</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>1681</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>1365</v>
       </c>
       <c r="B115" t="s">
-        <v>815</v>
+        <v>1710</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>816</v>
+        <v>1306</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="E115" t="s">
-        <v>1526</v>
+        <v>1307</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>1454</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>818</v>
+        <v>1308</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>819</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="B116" t="s">
-        <v>1134</v>
+        <v>938</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>1135</v>
+        <v>939</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>1136</v>
-      </c>
-      <c r="E116" t="s">
-        <v>1584</v>
+        <v>940</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>1548</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>1137</v>
+        <v>941</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>1138</v>
+        <v>942</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B117" t="s">
-        <v>1707</v>
+        <v>751</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>1284</v>
+        <v>752</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>1285</v>
-      </c>
-      <c r="E117" t="s">
-        <v>1612</v>
+        <v>753</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>1514</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>1286</v>
+        <v>754</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>1685</v>
+        <v>755</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B118" t="s">
-        <v>646</v>
+        <v>756</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>647</v>
+        <v>757</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="E118" t="s">
-        <v>1475</v>
+        <v>758</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>1515</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>649</v>
+        <v>759</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>650</v>
+        <v>760</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
@@ -8566,68 +8572,68 @@
         <v>1365</v>
       </c>
       <c r="B119" t="s">
-        <v>766</v>
+        <v>958</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>767</v>
+        <v>959</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="E119" t="s">
-        <v>1516</v>
+        <v>960</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>1551</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>769</v>
+        <v>961</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>770</v>
+        <v>962</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B120" t="s">
-        <v>65</v>
+        <v>844</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>66</v>
+        <v>845</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>67</v>
+        <v>846</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>1397</v>
+        <v>1530</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>68</v>
+        <v>847</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>69</v>
+        <v>848</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B121" t="s">
-        <v>602</v>
+        <v>859</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>603</v>
+        <v>860</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="E121" t="s">
-        <v>1470</v>
+        <v>861</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>1533</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>605</v>
+        <v>862</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>606</v>
+        <v>863</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
@@ -8635,137 +8641,137 @@
         <v>1365</v>
       </c>
       <c r="B122" t="s">
-        <v>879</v>
+        <v>796</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>880</v>
+        <v>797</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="E122" t="s">
-        <v>1539</v>
+        <v>798</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>1520</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>882</v>
+        <v>799</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="B123" t="s">
-        <v>1022</v>
+        <v>894</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>1023</v>
+        <v>895</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>1024</v>
-      </c>
-      <c r="E123" t="s">
-        <v>1563</v>
+        <v>896</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>1540</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>11</v>
+        <v>897</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>1025</v>
+        <v>898</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B124" t="s">
-        <v>54</v>
+        <v>864</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>1650</v>
+        <v>865</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>55</v>
+        <v>866</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>1394</v>
+        <v>1534</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>56</v>
+        <v>867</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>1651</v>
+        <v>868</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1371</v>
+        <v>1365</v>
       </c>
       <c r="B125" t="s">
-        <v>1203</v>
+        <v>815</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>1204</v>
+        <v>816</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="E125" t="s">
-        <v>1596</v>
+        <v>817</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>1524</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>1206</v>
+        <v>818</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1371</v>
+        <v>1365</v>
       </c>
       <c r="B126" t="s">
-        <v>1203</v>
+        <v>948</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>1356</v>
+        <v>949</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>1357</v>
-      </c>
-      <c r="E126" t="s">
-        <v>1622</v>
+        <v>950</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>1524</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>1358</v>
+        <v>951</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>1359</v>
+        <v>952</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B127" t="s">
-        <v>95</v>
+        <v>918</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>96</v>
+        <v>919</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>97</v>
+        <v>920</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>1403</v>
+        <v>1545</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>98</v>
+        <v>921</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>1639</v>
+        <v>922</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
@@ -8773,1997 +8779,2000 @@
         <v>1365</v>
       </c>
       <c r="B128" t="s">
-        <v>806</v>
+        <v>834</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>807</v>
+        <v>835</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="E128" t="s">
-        <v>1524</v>
+        <v>836</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>1528</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>809</v>
+        <v>837</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>1693</v>
+        <v>838</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="B129" t="s">
-        <v>425</v>
+        <v>854</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>426</v>
+        <v>855</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>427</v>
+        <v>856</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>1459</v>
+        <v>1532</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>428</v>
+        <v>857</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>1663</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="B130" t="s">
-        <v>1344</v>
+        <v>953</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>1682</v>
+        <v>954</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>1345</v>
-      </c>
-      <c r="E130" t="s">
-        <v>1474</v>
+        <v>955</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>1550</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>1346</v>
+        <v>956</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>1683</v>
+        <v>957</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="B131" t="s">
-        <v>1036</v>
+        <v>923</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>1037</v>
+        <v>924</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E131" t="s">
-        <v>1566</v>
+        <v>925</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>1546</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>1039</v>
+        <v>926</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>1040</v>
+        <v>927</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B132" t="s">
-        <v>21</v>
+        <v>1706</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>22</v>
+        <v>1291</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>23</v>
+        <v>1292</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>1385</v>
+        <v>1462</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>24</v>
+        <v>1293</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>25</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="B133" t="s">
-        <v>993</v>
+        <v>1700</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>994</v>
+        <v>1272</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>995</v>
-      </c>
-      <c r="E133" t="s">
-        <v>1559</v>
+        <v>1273</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>1607</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>996</v>
+        <v>1274</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>997</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B134" t="s">
-        <v>70</v>
+        <v>908</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>71</v>
+        <v>909</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>72</v>
+        <v>910</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>1398</v>
+        <v>1543</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>73</v>
+        <v>911</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>74</v>
+        <v>912</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="B135" t="s">
-        <v>112</v>
+        <v>1704</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>113</v>
+        <v>1287</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>114</v>
+        <v>1288</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>1406</v>
+        <v>1611</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>115</v>
+        <v>1289</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>116</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B136" t="s">
-        <v>1709</v>
+        <v>719</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>1295</v>
+        <v>720</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>1296</v>
-      </c>
-      <c r="E136" t="s">
-        <v>1560</v>
+        <v>721</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>1509</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>1297</v>
+        <v>722</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B137" t="s">
-        <v>899</v>
+        <v>1718</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>900</v>
+        <v>1332</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="E137" t="s">
-        <v>1543</v>
+        <v>1333</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>1616</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>115</v>
+        <v>1334</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>902</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>1367</v>
+      </c>
       <c r="B138" t="s">
-        <v>1710</v>
+        <v>1097</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>1299</v>
+        <v>1098</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>1300</v>
-      </c>
-      <c r="E138" t="s">
-        <v>1614</v>
+        <v>1099</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>1577</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>1255</v>
+        <v>1100</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>1301</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B139" t="s">
-        <v>825</v>
+        <v>714</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>826</v>
+        <v>715</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="E139" t="s">
-        <v>1528</v>
+        <v>716</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>1631</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>828</v>
+        <v>717</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>829</v>
+        <v>718</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="B140" t="s">
-        <v>30</v>
+        <v>1684</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>31</v>
+        <v>1685</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>32</v>
+        <v>1686</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>1387</v>
+        <v>1689</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>1654</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>1655</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1687</v>
+      </c>
+      <c r="G140" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="B141" t="s">
-        <v>678</v>
+        <v>1719</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>679</v>
+        <v>1352</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="E141" t="s">
-        <v>1505</v>
+        <v>1353</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>1495</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>681</v>
+        <v>1354</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="B142" t="s">
-        <v>709</v>
+        <v>1716</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>710</v>
+        <v>1310</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="E142" t="s">
-        <v>1632</v>
+        <v>1311</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>1613</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>712</v>
+        <v>1312</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>713</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="B143" t="s">
-        <v>636</v>
+        <v>741</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>637</v>
+        <v>742</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="E143" t="s">
-        <v>1453</v>
+        <v>743</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>1513</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>639</v>
+        <v>744</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>640</v>
+        <v>745</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="B144" t="s">
-        <v>631</v>
+        <v>727</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>632</v>
+        <v>728</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E144" t="s">
-        <v>1498</v>
+        <v>729</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>1511</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>634</v>
+        <v>730</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>635</v>
+        <v>731</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="B145" t="s">
-        <v>420</v>
+        <v>723</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>421</v>
+        <v>724</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>422</v>
+        <v>725</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>1459</v>
+        <v>1510</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>423</v>
+        <v>726</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>424</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="B146" t="s">
-        <v>607</v>
+        <v>1713</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>608</v>
+        <v>737</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="E146" t="s">
-        <v>1635</v>
+        <v>738</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>1485</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>610</v>
+        <v>739</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>611</v>
+        <v>740</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="B147" t="s">
-        <v>1245</v>
+        <v>1705</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>1246</v>
+        <v>1284</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>1247</v>
-      </c>
-      <c r="E147" t="s">
-        <v>1605</v>
+        <v>1285</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>1610</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>1248</v>
+        <v>1286</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>1249</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="B148" t="s">
-        <v>411</v>
+        <v>732</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>412</v>
+        <v>733</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>413</v>
+        <v>734</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>1630</v>
+        <v>1512</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>414</v>
+        <v>735</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1662</v>
+        <v>736</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B149" t="s">
-        <v>849</v>
+        <v>1699</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>850</v>
+        <v>1262</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="E149" t="s">
-        <v>1533</v>
+        <v>1263</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>1623</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>852</v>
+        <v>1264</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>853</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="B150" t="s">
-        <v>1179</v>
+        <v>1697</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>1180</v>
+        <v>1376</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>1181</v>
-      </c>
-      <c r="E150" t="s">
-        <v>1591</v>
+        <v>1260</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>1622</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>6</v>
+        <v>1261</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="B151" t="s">
-        <v>1112</v>
+        <v>746</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>1341</v>
+        <v>747</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E151" t="s">
-        <v>1620</v>
+        <v>748</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>1632</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>1342</v>
+        <v>749</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>1343</v>
+        <v>750</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B152" t="s">
-        <v>781</v>
+        <v>464</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>782</v>
+        <v>465</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="E152" t="s">
-        <v>1519</v>
+        <v>466</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>1468</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>784</v>
+        <v>467</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B153" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>1306</v>
+        <v>1318</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>1307</v>
-      </c>
-      <c r="E153" t="s">
-        <v>1454</v>
+        <v>1319</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>1452</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>1308</v>
+        <v>1320</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B154" t="s">
-        <v>80</v>
+        <v>1717</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>81</v>
+        <v>1321</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>82</v>
+        <v>1322</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>1400</v>
+        <v>1490</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>83</v>
+        <v>1323</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>84</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B155" t="s">
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>1659</v>
+        <v>416</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>371</v>
+        <v>417</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>1451</v>
+        <v>1629</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>372</v>
+        <v>418</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>1660</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="B156" t="s">
-        <v>1051</v>
+        <v>669</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>1052</v>
+        <v>670</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>1053</v>
-      </c>
-      <c r="E156" t="s">
-        <v>1569</v>
+        <v>671</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>1503</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>1054</v>
+        <v>672</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>1055</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B157" t="s">
-        <v>298</v>
+        <v>656</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>299</v>
+        <v>657</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>300</v>
+        <v>658</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>1441</v>
+        <v>1501</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>2</v>
+        <v>659</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>301</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B158" t="s">
-        <v>953</v>
+        <v>660</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>954</v>
+        <v>661</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>955</v>
-      </c>
-      <c r="E158" t="s">
-        <v>1552</v>
+        <v>662</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>1502</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>956</v>
+        <v>663</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>957</v>
+        <v>664</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B159" t="s">
-        <v>859</v>
+        <v>665</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>860</v>
+        <v>666</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="E159" t="s">
-        <v>1535</v>
+        <v>667</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>1464</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>862</v>
+        <v>668</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>863</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B160" t="s">
-        <v>175</v>
+        <v>444</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>176</v>
+        <v>445</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>177</v>
+        <v>446</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>1418</v>
+        <v>1464</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>5</v>
+        <v>447</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>178</v>
+        <v>448</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B161" t="s">
-        <v>908</v>
+        <v>406</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>909</v>
+        <v>407</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>910</v>
-      </c>
-      <c r="E161" t="s">
-        <v>1545</v>
+        <v>408</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>1457</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>911</v>
+        <v>409</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>912</v>
+        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B162" t="s">
-        <v>928</v>
+        <v>396</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>929</v>
+        <v>397</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>930</v>
-      </c>
-      <c r="E162" t="s">
-        <v>1518</v>
+        <v>398</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>1455</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>931</v>
+        <v>399</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>932</v>
+        <v>400</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B163" t="s">
-        <v>1157</v>
+        <v>454</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>1158</v>
+        <v>455</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E163" t="s">
-        <v>1623</v>
+        <v>456</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>1466</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>1679</v>
+        <v>457</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>1680</v>
+        <v>458</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="B164" t="s">
-        <v>1008</v>
+        <v>401</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>1009</v>
+        <v>402</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>1010</v>
-      </c>
-      <c r="E164" t="s">
-        <v>1561</v>
+        <v>403</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>1456</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>1011</v>
+        <v>404</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>1012</v>
+        <v>405</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B165" t="s">
-        <v>963</v>
+        <v>673</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>964</v>
+        <v>674</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>965</v>
-      </c>
-      <c r="E165" t="s">
-        <v>1554</v>
+        <v>675</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>1504</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>966</v>
+        <v>676</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>967</v>
+        <v>677</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B166" t="s">
-        <v>612</v>
+        <v>709</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>613</v>
+        <v>710</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="E166" t="s">
-        <v>1636</v>
+        <v>711</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>1630</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>291</v>
+        <v>712</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>615</v>
+        <v>713</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B167" t="s">
-        <v>719</v>
+        <v>439</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>720</v>
+        <v>440</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="E167" t="s">
-        <v>1509</v>
+        <v>441</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>1458</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>722</v>
+        <v>442</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>1676</v>
+        <v>443</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B168" t="s">
-        <v>1706</v>
+        <v>696</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>1287</v>
+        <v>697</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>1288</v>
-      </c>
-      <c r="E168" t="s">
-        <v>1613</v>
+        <v>272</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>1508</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>1289</v>
+        <v>698</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>1290</v>
+        <v>699</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1373</v>
+        <v>1363</v>
       </c>
       <c r="B169" t="s">
-        <v>1216</v>
+        <v>693</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>1217</v>
+        <v>694</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>1218</v>
-      </c>
-      <c r="E169" t="s">
-        <v>1599</v>
+        <v>695</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>1508</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>1099</v>
+        <v>1672</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>1219</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B170" t="s">
-        <v>218</v>
+        <v>700</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>219</v>
+        <v>701</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>220</v>
+        <v>702</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>1628</v>
+        <v>1508</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>221</v>
+        <v>4</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>222</v>
+        <v>703</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B171" t="s">
-        <v>117</v>
+        <v>704</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>118</v>
+        <v>705</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>119</v>
+        <v>706</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>1407</v>
+        <v>1508</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>120</v>
+        <v>707</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B172" t="s">
-        <v>85</v>
+        <v>1715</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>86</v>
+        <v>1314</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>87</v>
+        <v>1315</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>1401</v>
+        <v>1467</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>88</v>
+        <v>1316</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>89</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="B173" t="s">
-        <v>1119</v>
+        <v>459</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>1120</v>
+        <v>460</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E173" t="s">
-        <v>1583</v>
+        <v>461</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>1467</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>1122</v>
+        <v>462</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>1123</v>
+        <v>463</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B174" t="s">
-        <v>791</v>
+        <v>678</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>792</v>
+        <v>679</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="E174" t="s">
-        <v>1521</v>
+        <v>680</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>1505</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>794</v>
+        <v>681</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>795</v>
+        <v>682</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B175" t="s">
-        <v>213</v>
+        <v>449</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>214</v>
+        <v>450</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>215</v>
+        <v>451</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>1426</v>
+        <v>1465</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>216</v>
+        <v>452</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>217</v>
+        <v>453</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B176" t="s">
-        <v>392</v>
+        <v>683</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>393</v>
+        <v>684</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>394</v>
+        <v>685</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>1454</v>
+        <v>1506</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>1</v>
+        <v>686</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>395</v>
+        <v>687</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B177" t="s">
-        <v>107</v>
+        <v>688</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>108</v>
+        <v>689</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>109</v>
+        <v>690</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>1405</v>
+        <v>1507</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>110</v>
+        <v>691</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>111</v>
+        <v>692</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B178" t="s">
-        <v>524</v>
+        <v>411</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>525</v>
+        <v>412</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="E178" t="s">
-        <v>1481</v>
+        <v>413</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>1628</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>527</v>
+        <v>414</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>528</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="B179" t="s">
-        <v>1705</v>
+        <v>434</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1276</v>
+        <v>435</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1277</v>
-      </c>
-      <c r="E179" t="s">
-        <v>1610</v>
+        <v>436</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>1463</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>1278</v>
+        <v>437</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>1279</v>
+        <v>438</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B180" t="s">
-        <v>550</v>
+        <v>429</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>551</v>
+        <v>430</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="E180" t="s">
-        <v>1486</v>
+        <v>431</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>1459</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>553</v>
+        <v>432</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>554</v>
+        <v>433</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B181" t="s">
-        <v>626</v>
+        <v>425</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>627</v>
+        <v>426</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="E181" t="s">
-        <v>1495</v>
+        <v>427</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>1459</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>629</v>
+        <v>428</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>630</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B182" t="s">
-        <v>336</v>
+        <v>420</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>337</v>
+        <v>421</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>338</v>
+        <v>422</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>1445</v>
+        <v>1459</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>339</v>
+        <v>423</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>340</v>
+        <v>424</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1361</v>
+        <v>1374</v>
       </c>
       <c r="B183" t="s">
-        <v>237</v>
+        <v>1702</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>238</v>
+        <v>1268</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>239</v>
+        <v>1269</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>1430</v>
+        <v>1495</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>240</v>
+        <v>1270</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1367</v>
+        <v>1374</v>
       </c>
       <c r="B184" t="s">
-        <v>714</v>
+        <v>1336</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>715</v>
+        <v>1337</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="E184" t="s">
-        <v>1633</v>
+        <v>1338</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>1617</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>717</v>
+        <v>1339</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>718</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B185" t="s">
-        <v>1065</v>
+        <v>1102</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>1066</v>
+        <v>1103</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>1067</v>
-      </c>
-      <c r="E185" t="s">
-        <v>1572</v>
+        <v>1104</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>1578</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>1068</v>
+        <v>1105</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1069</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B186" t="s">
-        <v>988</v>
+        <v>1107</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>989</v>
+        <v>1108</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>990</v>
-      </c>
-      <c r="E186" t="s">
-        <v>1558</v>
+        <v>1109</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>1579</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>991</v>
+        <v>1110</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="B187" t="s">
-        <v>365</v>
+        <v>1112</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>366</v>
+        <v>1341</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>367</v>
+        <v>1113</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>1434</v>
+        <v>1618</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>368</v>
+        <v>1342</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>369</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="B188" t="s">
-        <v>1198</v>
+        <v>1114</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>1199</v>
+        <v>1115</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>1200</v>
-      </c>
-      <c r="E188" t="s">
-        <v>1595</v>
+        <v>1116</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>1580</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>1201</v>
+        <v>1117</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="B189" t="s">
-        <v>1719</v>
+        <v>1170</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>1321</v>
+        <v>1171</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>1322</v>
-      </c>
-      <c r="E189" t="s">
-        <v>1490</v>
+        <v>1172</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>1587</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>1323</v>
+        <v>1173</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1324</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
       <c r="B190" t="s">
-        <v>592</v>
+        <v>1179</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>593</v>
+        <v>1180</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="E190" t="s">
-        <v>1494</v>
+        <v>1181</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>1589</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>595</v>
+        <v>6</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>596</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="B191" t="s">
-        <v>294</v>
+        <v>1143</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>295</v>
+        <v>1144</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>1460</v>
+        <v>1145</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>1440</v>
+        <v>1584</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>296</v>
+        <v>1146</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>297</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
-        <v>1366</v>
-      </c>
-      <c r="B192" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E192" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F192" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>1064</v>
+      <c r="A192" s="5" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E192" s="10" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G192" s="7" t="s">
+        <v>1164</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="B193" t="s">
-        <v>321</v>
+        <v>1193</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>322</v>
+        <v>1194</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>323</v>
+        <v>1195</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>1435</v>
+        <v>1592</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>324</v>
+        <v>1196</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>325</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
       <c r="B194" t="s">
-        <v>501</v>
+        <v>1148</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>502</v>
+        <v>1149</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="E194" t="s">
-        <v>1476</v>
+        <v>1150</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>1456</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>504</v>
+        <v>1151</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>505</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
       <c r="B195" t="s">
-        <v>621</v>
+        <v>1165</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>622</v>
+        <v>1166</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="E195" t="s">
-        <v>1497</v>
+        <v>1167</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>1586</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>624</v>
+        <v>1168</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>625</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
       <c r="B196" t="s">
-        <v>497</v>
+        <v>1188</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>498</v>
+        <v>1189</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="E196" t="s">
-        <v>1475</v>
+        <v>1190</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>1591</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>500</v>
+        <v>1191</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>1666</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="B197" t="s">
-        <v>854</v>
+        <v>1183</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>855</v>
+        <v>1184</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="E197" t="s">
-        <v>1534</v>
+        <v>1185</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>1590</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>857</v>
+        <v>1186</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>858</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="B198" t="s">
-        <v>449</v>
+        <v>1152</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>450</v>
+        <v>1153</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E198" t="s">
-        <v>1465</v>
+        <v>1154</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>1606</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>452</v>
+        <v>1155</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>453</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1363</v>
+        <v>1370</v>
       </c>
       <c r="B199" t="s">
-        <v>464</v>
+        <v>1157</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>465</v>
+        <v>1158</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="E199" t="s">
-        <v>1468</v>
+        <v>1159</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>1621</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>467</v>
+        <v>1677</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>468</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="B200" t="s">
-        <v>289</v>
+        <v>1175</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>290</v>
+        <v>1176</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>291</v>
+        <v>686</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>1440</v>
+        <v>1588</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>292</v>
+        <v>1177</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>293</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="B201" t="s">
-        <v>444</v>
+        <v>1046</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>445</v>
+        <v>1047</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E201" t="s">
-        <v>1464</v>
+        <v>1048</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>1566</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>447</v>
+        <v>1049</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>448</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B202" t="s">
-        <v>597</v>
+        <v>1013</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>598</v>
+        <v>1014</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="E202" t="s">
-        <v>1495</v>
+        <v>1015</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>1560</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>600</v>
+        <v>1016</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>601</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B203" t="s">
-        <v>515</v>
+        <v>1707</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>516</v>
+        <v>1295</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="E203" t="s">
-        <v>1479</v>
+        <v>1296</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>1558</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>13</v>
+        <v>1297</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>518</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B204" t="s">
-        <v>801</v>
+        <v>998</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>802</v>
+        <v>999</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="E204" t="s">
-        <v>1523</v>
+        <v>1000</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>1558</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>804</v>
+        <v>1001</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>805</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B205" t="s">
-        <v>903</v>
+        <v>993</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>904</v>
+        <v>994</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="E205" t="s">
-        <v>1544</v>
+        <v>995</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>1557</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>906</v>
+        <v>996</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>907</v>
+        <v>997</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B206" t="s">
-        <v>478</v>
+        <v>1041</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>479</v>
+        <v>1042</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E206" t="s">
-        <v>1471</v>
+        <v>1043</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>1565</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>481</v>
+        <v>1044</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="B207" t="s">
-        <v>1718</v>
+        <v>1060</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>1310</v>
+        <v>1061</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1311</v>
-      </c>
-      <c r="E207" t="s">
-        <v>1615</v>
+        <v>1062</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>1569</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>1312</v>
+        <v>1063</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>1313</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="B208" t="s">
-        <v>1193</v>
+        <v>988</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>1194</v>
+        <v>989</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1195</v>
-      </c>
-      <c r="E208" t="s">
-        <v>1594</v>
+        <v>990</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>1556</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>1196</v>
+        <v>991</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="B209" t="s">
-        <v>1717</v>
+        <v>968</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>1314</v>
+        <v>969</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E209" t="s">
-        <v>1467</v>
+        <v>970</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>1553</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>1316</v>
+        <v>971</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>1317</v>
+        <v>972</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="B210" t="s">
-        <v>351</v>
+        <v>1008</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>352</v>
+        <v>1009</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>353</v>
+        <v>1010</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>1448</v>
+        <v>1559</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>354</v>
+        <v>1011</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>1658</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="B211" t="s">
-        <v>1716</v>
+        <v>1051</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1318</v>
+        <v>1052</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1319</v>
-      </c>
-      <c r="E211" t="s">
-        <v>1452</v>
+        <v>1053</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>1567</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>1320</v>
+        <v>1054</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>1684</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="B212" t="s">
-        <v>1129</v>
+        <v>1070</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>1130</v>
+        <v>1071</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E212" t="s">
-        <v>1488</v>
+        <v>15</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>1571</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>1132</v>
+        <v>1072</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1133</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="B213" t="s">
-        <v>1220</v>
+        <v>978</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>1221</v>
+        <v>979</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1222</v>
-      </c>
-      <c r="E213" t="s">
-        <v>1600</v>
+        <v>980</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>1440</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>1223</v>
+        <v>981</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>1224</v>
+        <v>982</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="B214" t="s">
-        <v>454</v>
+        <v>1026</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>455</v>
+        <v>1027</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="E214" t="s">
-        <v>1466</v>
+        <v>1028</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>1562</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>457</v>
+        <v>1029</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>458</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
@@ -10771,528 +10780,528 @@
         <v>1366</v>
       </c>
       <c r="B215" t="s">
-        <v>998</v>
+        <v>1022</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>999</v>
+        <v>1023</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E215" t="s">
-        <v>1560</v>
+        <v>1024</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>1561</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>1001</v>
+        <v>11</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1002</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="B216" t="s">
-        <v>127</v>
+        <v>983</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>128</v>
+        <v>984</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>129</v>
+        <v>985</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>1408</v>
+        <v>1555</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>130</v>
+        <v>986</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>131</v>
+        <v>987</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B217" t="s">
-        <v>651</v>
+        <v>1036</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>652</v>
+        <v>1037</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="E217" t="s">
-        <v>1500</v>
+        <v>1038</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>1564</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>654</v>
+        <v>1039</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>655</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="B218" t="s">
-        <v>1097</v>
+        <v>1056</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>1098</v>
+        <v>1057</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E218" t="s">
-        <v>1579</v>
+        <v>1058</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>1568</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>1100</v>
+        <v>480</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>1101</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="B219" t="s">
-        <v>33</v>
+        <v>1017</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>34</v>
+        <v>1018</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>35</v>
+        <v>1019</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>1388</v>
+        <v>1488</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>36</v>
+        <v>1020</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>1678</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B220" t="s">
-        <v>1700</v>
+        <v>1031</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>1266</v>
+        <v>1032</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>1238</v>
-      </c>
-      <c r="E220" t="s">
-        <v>1608</v>
+        <v>1033</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>1563</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>4</v>
+        <v>1034</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>1267</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="B221" t="s">
-        <v>1208</v>
+        <v>1065</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>1209</v>
+        <v>1066</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>1210</v>
-      </c>
-      <c r="E221" t="s">
-        <v>1597</v>
+        <v>1067</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>1570</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>7</v>
+        <v>1068</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>1211</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B222" t="s">
-        <v>771</v>
+        <v>1003</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>772</v>
+        <v>1004</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="E222" t="s">
-        <v>1517</v>
+        <v>1005</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>1554</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>774</v>
+        <v>1006</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>775</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="B223" t="s">
-        <v>656</v>
+        <v>973</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>657</v>
+        <v>974</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="E223" t="s">
-        <v>1501</v>
+        <v>975</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>1554</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>659</v>
+        <v>976</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1671</v>
+        <v>977</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1363</v>
+        <v>1372</v>
       </c>
       <c r="B224" t="s">
-        <v>439</v>
+        <v>1212</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>440</v>
+        <v>1213</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="E224" t="s">
-        <v>1458</v>
+        <v>3</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>1596</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>442</v>
+        <v>1214</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>443</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1364</v>
+        <v>1373</v>
       </c>
       <c r="B225" t="s">
-        <v>1079</v>
+        <v>1245</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>1080</v>
+        <v>1246</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E225" t="s">
-        <v>1575</v>
+        <v>1247</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>1603</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>1082</v>
+        <v>1248</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>1083</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1361</v>
+        <v>1373</v>
       </c>
       <c r="B226" t="s">
-        <v>184</v>
+        <v>1225</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>185</v>
+        <v>1226</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>186</v>
+        <v>1227</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>1421</v>
+        <v>1599</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>187</v>
+        <v>1228</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>188</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
       <c r="B227" t="s">
-        <v>839</v>
+        <v>1230</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>840</v>
+        <v>1231</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="E227" t="s">
-        <v>1531</v>
+        <v>1232</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>1600</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>842</v>
+        <v>1233</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>843</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1364</v>
+        <v>1373</v>
       </c>
       <c r="B228" t="s">
-        <v>538</v>
+        <v>1240</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>539</v>
+        <v>1241</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="E228" t="s">
-        <v>1484</v>
+        <v>1242</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>1602</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>1668</v>
+        <v>1243</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>1669</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1361</v>
+        <v>1373</v>
       </c>
       <c r="B229" t="s">
-        <v>104</v>
+        <v>1216</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1647</v>
+        <v>1217</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>105</v>
+        <v>1218</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>1404</v>
+        <v>1597</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>106</v>
+        <v>1099</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1648</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1361</v>
+        <v>1373</v>
       </c>
       <c r="B230" t="s">
-        <v>242</v>
+        <v>1235</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>243</v>
+        <v>1236</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>244</v>
+        <v>1237</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>1431</v>
+        <v>1601</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>245</v>
+        <v>1238</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>246</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="B231" t="s">
-        <v>732</v>
+        <v>1712</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>733</v>
+        <v>1325</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="E231" t="s">
-        <v>1512</v>
+        <v>1326</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>1614</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>735</v>
+        <v>1327</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>736</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>1364</v>
+        <v>1373</v>
       </c>
       <c r="B232" t="s">
-        <v>529</v>
+        <v>1250</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>530</v>
+        <v>1251</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="E232" t="s">
-        <v>1482</v>
+        <v>1252</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>1604</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>532</v>
+        <v>1253</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>533</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="B233" t="s">
-        <v>1143</v>
+        <v>1220</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>1144</v>
+        <v>1221</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="E233" t="s">
-        <v>1586</v>
+        <v>1222</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>1598</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>1146</v>
+        <v>1223</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>1147</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B234" t="s">
-        <v>751</v>
+        <v>569</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>752</v>
+        <v>570</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="E234" t="s">
-        <v>1513</v>
+        <v>571</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>1490</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>754</v>
+        <v>572</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>755</v>
+        <v>573</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B235" t="s">
-        <v>864</v>
+        <v>524</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>865</v>
+        <v>525</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="E235" t="s">
-        <v>1536</v>
+        <v>526</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>1481</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>867</v>
+        <v>527</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>868</v>
+        <v>528</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B236" t="s">
-        <v>137</v>
+        <v>602</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>138</v>
+        <v>603</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>139</v>
+        <v>604</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>1410</v>
+        <v>1470</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>140</v>
+        <v>605</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>141</v>
+        <v>606</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1370</v>
+        <v>1364</v>
       </c>
       <c r="B237" t="s">
-        <v>1170</v>
+        <v>474</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1171</v>
+        <v>475</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E237" t="s">
-        <v>1589</v>
+        <v>476</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>1470</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>1173</v>
+        <v>477</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>1174</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -11300,183 +11309,183 @@
         <v>1364</v>
       </c>
       <c r="B238" t="s">
-        <v>541</v>
+        <v>641</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>542</v>
+        <v>642</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="E238" t="s">
-        <v>1485</v>
+        <v>643</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>1499</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>281</v>
+        <v>644</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>544</v>
+        <v>645</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="B239" t="s">
-        <v>1701</v>
+        <v>506</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>1262</v>
+        <v>507</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>1263</v>
-      </c>
-      <c r="E239" t="s">
-        <v>1625</v>
+        <v>508</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>1477</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>1264</v>
+        <v>1665</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>1265</v>
+        <v>509</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="B240" t="s">
-        <v>741</v>
+        <v>1092</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>742</v>
+        <v>1093</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="E240" t="s">
-        <v>1513</v>
+        <v>1094</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>1576</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>744</v>
+        <v>1095</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>745</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B241" t="s">
-        <v>1070</v>
+        <v>1087</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1071</v>
+        <v>1088</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E241" t="s">
-        <v>1573</v>
+        <v>1089</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>1575</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>1072</v>
+        <v>1090</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>1073</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1373</v>
+        <v>1364</v>
       </c>
       <c r="B242" t="s">
-        <v>1250</v>
+        <v>564</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>1251</v>
+        <v>565</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="E242" t="s">
-        <v>1606</v>
+        <v>566</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>1489</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>1253</v>
+        <v>567</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>1254</v>
+        <v>568</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B243" t="s">
-        <v>378</v>
+        <v>545</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>379</v>
+        <v>546</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>380</v>
+        <v>547</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>1453</v>
+        <v>1432</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>381</v>
+        <v>548</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>1661</v>
+        <v>549</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B244" t="s">
-        <v>284</v>
+        <v>579</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>285</v>
+        <v>580</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>286</v>
+        <v>581</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>1439</v>
+        <v>1492</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>287</v>
+        <v>12</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>288</v>
+        <v>582</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B245" t="s">
-        <v>259</v>
+        <v>651</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>260</v>
+        <v>652</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>261</v>
+        <v>653</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>1432</v>
+        <v>1500</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>262</v>
+        <v>654</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>263</v>
+        <v>655</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -11484,206 +11493,206 @@
         <v>1364</v>
       </c>
       <c r="B246" t="s">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>584</v>
+        <v>556</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="E246" t="s">
-        <v>1493</v>
+        <v>557</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>1487</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>586</v>
+        <v>9</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1670</v>
+        <v>558</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B247" t="s">
-        <v>1013</v>
+        <v>510</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1014</v>
+        <v>511</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E247" t="s">
-        <v>1562</v>
+        <v>512</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>1478</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>1016</v>
+        <v>513</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1695</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="B248" t="s">
-        <v>746</v>
+        <v>529</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>747</v>
+        <v>530</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="E248" t="s">
-        <v>1634</v>
+        <v>531</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>1482</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>749</v>
+        <v>532</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>750</v>
+        <v>533</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B249" t="s">
-        <v>264</v>
+        <v>534</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>265</v>
+        <v>535</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>266</v>
+        <v>536</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>1433</v>
+        <v>1483</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>268</v>
+        <v>537</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1373</v>
+        <v>1364</v>
       </c>
       <c r="B250" t="s">
-        <v>1225</v>
+        <v>538</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>1226</v>
+        <v>539</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>1227</v>
-      </c>
-      <c r="E250" t="s">
-        <v>1601</v>
+        <v>540</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>1484</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>1228</v>
+        <v>1666</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1229</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B251" t="s">
-        <v>26</v>
+        <v>492</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>27</v>
+        <v>493</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>28</v>
+        <v>494</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>1386</v>
+        <v>1474</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>29</v>
+        <v>495</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1382</v>
+        <v>496</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B252" t="s">
-        <v>247</v>
+        <v>626</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>248</v>
+        <v>627</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>249</v>
+        <v>628</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>1409</v>
+        <v>1495</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>1641</v>
+        <v>629</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>1640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B253" t="s">
-        <v>700</v>
+        <v>597</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>701</v>
+        <v>598</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="E253" t="s">
-        <v>1508</v>
+        <v>599</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>1495</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>4</v>
+        <v>600</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>703</v>
+        <v>601</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B254" t="s">
-        <v>1347</v>
+        <v>478</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>1348</v>
+        <v>479</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>1349</v>
-      </c>
-      <c r="E254" t="s">
-        <v>1621</v>
+        <v>480</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>1471</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>1350</v>
+        <v>481</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1351</v>
+        <v>482</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -11691,252 +11700,252 @@
         <v>1364</v>
       </c>
       <c r="B255" t="s">
-        <v>641</v>
+        <v>519</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>642</v>
+        <v>520</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="E255" t="s">
-        <v>1499</v>
+        <v>521</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>1480</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>644</v>
+        <v>522</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>645</v>
+        <v>523</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B256" t="s">
-        <v>704</v>
+        <v>559</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>705</v>
+        <v>560</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="E256" t="s">
-        <v>1508</v>
+        <v>561</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>1488</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>707</v>
+        <v>562</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>708</v>
+        <v>563</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1370</v>
+        <v>1364</v>
       </c>
       <c r="B257" t="s">
-        <v>1183</v>
+        <v>631</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1184</v>
+        <v>632</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="E257" t="s">
-        <v>1592</v>
+        <v>633</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>1498</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>1186</v>
+        <v>634</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>1187</v>
+        <v>635</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B258" t="s">
-        <v>199</v>
+        <v>636</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>200</v>
+        <v>637</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>201</v>
+        <v>638</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>1424</v>
+        <v>1453</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>202</v>
+        <v>639</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>203</v>
+        <v>640</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B259" t="s">
-        <v>189</v>
+        <v>616</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>190</v>
+        <v>617</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>191</v>
+        <v>618</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>1422</v>
+        <v>1496</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>192</v>
+        <v>619</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>193</v>
+        <v>620</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B260" t="s">
-        <v>913</v>
+        <v>612</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>914</v>
+        <v>613</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="E260" t="s">
-        <v>1546</v>
+        <v>614</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>1634</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>916</v>
+        <v>291</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>917</v>
+        <v>615</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B261" t="s">
-        <v>973</v>
+        <v>1074</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>974</v>
+        <v>1075</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>975</v>
-      </c>
-      <c r="E261" t="s">
-        <v>1556</v>
+        <v>1076</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>1572</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>976</v>
+        <v>1077</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>977</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B262" t="s">
-        <v>346</v>
+        <v>1079</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>347</v>
+        <v>1080</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>348</v>
+        <v>1081</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>1447</v>
+        <v>1573</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>349</v>
+        <v>1082</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>350</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="B263" t="s">
-        <v>1715</v>
+        <v>469</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>737</v>
+        <v>470</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="E263" t="s">
-        <v>1485</v>
+        <v>471</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>1469</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>739</v>
+        <v>472</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>740</v>
+        <v>473</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B264" t="s">
-        <v>796</v>
+        <v>541</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>797</v>
+        <v>542</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="E264" t="s">
-        <v>1522</v>
+        <v>543</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>1485</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>799</v>
+        <v>281</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>800</v>
+        <v>544</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B265" t="s">
-        <v>396</v>
+        <v>483</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>397</v>
+        <v>484</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>398</v>
+        <v>485</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>1455</v>
+        <v>1472</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>399</v>
+        <v>486</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>400</v>
+        <v>487</v>
       </c>
       <c r="L265" t="s">
         <v>1360</v>
@@ -11947,137 +11956,137 @@
         <v>1364</v>
       </c>
       <c r="B266" t="s">
-        <v>559</v>
+        <v>587</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="E266" t="s">
-        <v>1488</v>
+        <v>589</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>1434</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>563</v>
+        <v>591</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1373</v>
+        <v>1364</v>
       </c>
       <c r="B267" t="s">
-        <v>1714</v>
+        <v>592</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>1325</v>
+        <v>593</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1326</v>
-      </c>
-      <c r="E267" t="s">
-        <v>1616</v>
+        <v>594</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>1494</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>1327</v>
+        <v>595</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1328</v>
+        <v>596</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="B268" t="s">
-        <v>1139</v>
+        <v>1084</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>1140</v>
+        <v>1085</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E268" t="s">
-        <v>1585</v>
+        <v>1086</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>1574</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>1141</v>
+        <v>730</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1142</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="B269" t="s">
-        <v>1102</v>
+        <v>621</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>1103</v>
+        <v>622</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1104</v>
-      </c>
-      <c r="E269" t="s">
-        <v>1580</v>
+        <v>623</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>1497</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>1105</v>
+        <v>624</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1106</v>
+        <v>625</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B270" t="s">
-        <v>16</v>
+        <v>607</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>17</v>
+        <v>608</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>18</v>
+        <v>609</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>1384</v>
+        <v>1633</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>19</v>
+        <v>610</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>20</v>
+        <v>611</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B271" t="s">
-        <v>331</v>
+        <v>574</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>332</v>
+        <v>575</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>333</v>
+        <v>576</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>1629</v>
+        <v>1491</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>334</v>
+        <v>577</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>335</v>
+        <v>578</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
@@ -12085,510 +12094,510 @@
         <v>1364</v>
       </c>
       <c r="B272" t="s">
-        <v>474</v>
+        <v>515</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>475</v>
+        <v>516</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="E272" t="s">
-        <v>1470</v>
+        <v>517</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>1479</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>477</v>
+        <v>13</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1664</v>
+        <v>518</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B273" t="s">
-        <v>250</v>
+        <v>550</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>251</v>
+        <v>551</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>252</v>
+        <v>552</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>1437</v>
+        <v>1486</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>253</v>
+        <v>553</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1642</v>
+        <v>554</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B274" t="s">
-        <v>57</v>
+        <v>583</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>58</v>
+        <v>584</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>59</v>
+        <v>585</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>1395</v>
+        <v>1493</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>1652</v>
+        <v>586</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1374</v>
+        <v>1364</v>
       </c>
       <c r="B275" t="s">
-        <v>1336</v>
+        <v>488</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>1337</v>
+        <v>489</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>1338</v>
-      </c>
-      <c r="E275" t="s">
-        <v>1619</v>
+        <v>490</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>1473</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>1339</v>
+        <v>491</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>1340</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B276" t="s">
-        <v>46</v>
+        <v>646</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>47</v>
+        <v>647</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>48</v>
+        <v>648</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>1392</v>
+        <v>1475</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>49</v>
+        <v>649</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>50</v>
+        <v>650</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B277" t="s">
-        <v>142</v>
+        <v>497</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>143</v>
+        <v>498</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>144</v>
+        <v>499</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>1411</v>
+        <v>1475</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>145</v>
+        <v>500</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>146</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B278" t="s">
-        <v>415</v>
+        <v>501</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>416</v>
+        <v>502</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>417</v>
+        <v>503</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>1631</v>
+        <v>1476</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>418</v>
+        <v>504</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>419</v>
+        <v>505</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="B279" t="s">
-        <v>459</v>
+        <v>1208</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>460</v>
+        <v>1209</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="E279" t="s">
-        <v>1467</v>
+        <v>1210</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>1595</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>462</v>
+        <v>7</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>463</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>1362</v>
+        <v>1371</v>
       </c>
       <c r="B280" t="s">
-        <v>373</v>
+        <v>1198</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>374</v>
+        <v>1199</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>375</v>
+        <v>1200</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>1452</v>
+        <v>1593</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>376</v>
+        <v>1201</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>377</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>1365</v>
+        <v>1371</v>
       </c>
       <c r="B281" t="s">
-        <v>869</v>
+        <v>1203</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>870</v>
+        <v>1204</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="E281" t="s">
-        <v>1537</v>
+        <v>1205</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>1594</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>872</v>
+        <v>1206</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="B282" t="s">
-        <v>1087</v>
+        <v>1203</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>1088</v>
+        <v>1356</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E282" t="s">
-        <v>1577</v>
+        <v>1357</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>1620</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>1090</v>
+        <v>1358</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1091</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>1361</v>
+        <v>1375</v>
       </c>
       <c r="B283" t="s">
-        <v>151</v>
+        <v>1703</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>152</v>
+        <v>1276</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>153</v>
+        <v>1277</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>1413</v>
+        <v>1608</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>154</v>
+        <v>1278</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>155</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>1364</v>
+        <v>1375</v>
       </c>
       <c r="B284" t="s">
-        <v>519</v>
+        <v>1701</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>520</v>
+        <v>1280</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="E284" t="s">
-        <v>1480</v>
+        <v>1281</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>1609</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>522</v>
+        <v>1282</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>523</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>1365</v>
+        <v>1375</v>
       </c>
       <c r="B285" t="s">
-        <v>948</v>
+        <v>1696</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>949</v>
+        <v>1256</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="E285" t="s">
-        <v>1526</v>
+        <v>1257</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>1605</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>951</v>
+        <v>1258</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>952</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>1362</v>
+        <v>1369</v>
       </c>
       <c r="B286" t="s">
-        <v>274</v>
+        <v>1119</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>275</v>
+        <v>1120</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>276</v>
+        <v>1121</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>1435</v>
+        <v>1581</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>277</v>
+        <v>1122</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1362</v>
+        <v>1369</v>
       </c>
       <c r="B287" t="s">
-        <v>387</v>
+        <v>1344</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>388</v>
+        <v>1680</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>389</v>
+        <v>1345</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>1435</v>
+        <v>1474</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>390</v>
+        <v>1346</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>391</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="B288" t="s">
-        <v>983</v>
+        <v>1134</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>984</v>
+        <v>1135</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="E288" t="s">
-        <v>1557</v>
+        <v>1136</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>1582</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>986</v>
+        <v>1137</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>987</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B289" t="s">
-        <v>1107</v>
+        <v>1124</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>1108</v>
+        <v>1125</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E289" t="s">
-        <v>1581</v>
+        <v>1126</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>1480</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>1110</v>
+        <v>1127</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>1369</v>
       </c>
       <c r="B290" t="s">
-        <v>1713</v>
+        <v>1129</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>1329</v>
+        <v>1130</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>1330</v>
-      </c>
-      <c r="E290" t="s">
-        <v>1617</v>
+        <v>1131</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>1488</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>153</v>
+        <v>1132</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1331</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="B291" t="s">
-        <v>660</v>
+        <v>1139</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>661</v>
+        <v>1140</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="E291" t="s">
-        <v>1502</v>
+        <v>8</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>1583</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>663</v>
+        <v>1141</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="B292" t="s">
-        <v>44</v>
+        <v>1711</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>1645</v>
+        <v>1329</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>45</v>
+        <v>1330</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>1391</v>
+        <v>1615</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1646</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B293" t="s">
-        <v>37</v>
+        <v>1708</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>38</v>
+        <v>1299</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>39</v>
+        <v>1300</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>1389</v>
+        <v>1612</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>40</v>
+        <v>1255</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1644</v>
+        <v>1301</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G293">
-    <sortCondition ref="B1:B293"/>
+    <sortCondition ref="A1:A293"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/data/Russian_Words_Cards.xlsx
+++ b/public/data/Russian_Words_Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921BD1E2-3812-42F2-9863-D6610B177472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91E6152-B6FE-4C4F-BD79-120208E3D981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="1722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="1723">
   <si>
     <t>Topic</t>
   </si>
@@ -5437,6 +5437,9 @@
   </si>
   <si>
     <t>🐑</t>
+  </si>
+  <si>
+    <t>🐎</t>
   </si>
 </sst>
 </file>
@@ -8259,7 +8262,7 @@
         <v>768</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>1515</v>
+        <v>1722</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>769</v>

--- a/public/data/Russian_Words_Cards.xlsx
+++ b/public/data/Russian_Words_Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91E6152-B6FE-4C4F-BD79-120208E3D981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27B35CA-B2B3-4553-85FA-3CC4462BE3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="1723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="1718">
   <si>
     <t>Topic</t>
   </si>
@@ -695,9 +695,6 @@
     <t>пастила</t>
   </si>
   <si>
-    <t>פַּאסְטִילָה</t>
-  </si>
-  <si>
     <t>ממתק פירות יבש</t>
   </si>
   <si>
@@ -767,9 +764,6 @@
     <t>сметанник</t>
   </si>
   <si>
-    <t>סְמֶטָאנִיק</t>
-  </si>
-  <si>
     <t>עוגת שמנת</t>
   </si>
   <si>
@@ -3650,13 +3644,7 @@
     <t>машина</t>
   </si>
   <si>
-    <t>מָאשִׁינָה</t>
-  </si>
-  <si>
     <t>רכב</t>
-  </si>
-  <si>
-    <t>Machine</t>
   </si>
   <si>
     <t>המַאשִינָה נוסעת כמו machine משומנת, מוכנה לכבוש את הכביש.</t>
@@ -4117,9 +4105,6 @@
     </r>
   </si>
   <si>
-    <t>פַאמִילִיָה</t>
-  </si>
-  <si>
     <t>שם משפחה</t>
   </si>
   <si>
@@ -4298,38 +4283,9 @@
     <t>מָשִׁינָה</t>
   </si>
   <si>
-    <t>מכונית</t>
-  </si>
-  <si>
     <t>machine</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">בעתיד מָשִׁינָה תהיה </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>machine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> עצמאית לחלוטין</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -5110,9 +5066,6 @@
     <t>🌑</t>
   </si>
   <si>
-    <t>🚘</t>
-  </si>
-  <si>
     <t>🍁</t>
   </si>
   <si>
@@ -5219,9 +5172,6 @@
   </si>
   <si>
     <t>אסור לשכוח לנקות את הרָקוֹבִינָה. אחרת הכל נראה רקוב.</t>
-  </si>
-  <si>
-    <t>אָדִייָאלָה</t>
   </si>
   <si>
     <t>כשקר בחורף, המצב האידיאלי הוא להתעטף באָדִייָאלָה חמה וגדולה</t>
@@ -5440,6 +5390,18 @@
   </si>
   <si>
     <t>🐎</t>
+  </si>
+  <si>
+    <t>פַמִילִיָה</t>
+  </si>
+  <si>
+    <t>אָדִייָלָה</t>
+  </si>
+  <si>
+    <t>סְמֶטָנִיק</t>
+  </si>
+  <si>
+    <t>פַּסְטִילָה</t>
   </si>
 </sst>
 </file>
@@ -5844,7 +5806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L293"/>
+  <dimension ref="A1:L292"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -5861,27 +5823,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1624</v>
+        <v>1616</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1380</v>
+        <v>1373</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1379</v>
+        <v>1372</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1378</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B2" t="s">
         <v>209</v>
@@ -5893,18 +5855,18 @@
         <v>211</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1625</v>
+        <v>1617</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>212</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1635</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B3" t="s">
         <v>142</v>
@@ -5916,7 +5878,7 @@
         <v>144</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1411</v>
+        <v>1404</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>145</v>
@@ -5927,7 +5889,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B4" t="s">
         <v>204</v>
@@ -5939,7 +5901,7 @@
         <v>206</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>207</v>
@@ -5950,30 +5912,30 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1437</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B6" t="s">
         <v>179</v>
@@ -5985,7 +5947,7 @@
         <v>181</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>182</v>
@@ -5996,7 +5958,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B7" t="s">
         <v>189</v>
@@ -6008,7 +5970,7 @@
         <v>191</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>192</v>
@@ -6019,7 +5981,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B8" t="s">
         <v>156</v>
@@ -6031,7 +5993,7 @@
         <v>158</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1414</v>
+        <v>1407</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>159</v>
@@ -6042,7 +6004,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
@@ -6054,7 +6016,7 @@
         <v>77</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>78</v>
@@ -6065,7 +6027,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B10" t="s">
         <v>166</v>
@@ -6077,7 +6039,7 @@
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1416</v>
+        <v>1409</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>168</v>
@@ -6088,7 +6050,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B11" t="s">
         <v>161</v>
@@ -6100,7 +6062,7 @@
         <v>163</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>164</v>
@@ -6111,7 +6073,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B12" t="s">
         <v>60</v>
@@ -6123,7 +6085,7 @@
         <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1396</v>
+        <v>1389</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>63</v>
@@ -6134,30 +6096,30 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B13" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1643</v>
+        <v>1635</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1644</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B14" t="s">
         <v>90</v>
@@ -6169,7 +6131,7 @@
         <v>92</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -6180,7 +6142,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B15" t="s">
         <v>184</v>
@@ -6192,7 +6154,7 @@
         <v>186</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1421</v>
+        <v>1414</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>187</v>
@@ -6203,7 +6165,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B16" t="s">
         <v>170</v>
@@ -6215,7 +6177,7 @@
         <v>172</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1417</v>
+        <v>1410</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>173</v>
@@ -6226,7 +6188,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B17" t="s">
         <v>127</v>
@@ -6238,7 +6200,7 @@
         <v>129</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>130</v>
@@ -6249,30 +6211,30 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B18" t="s">
+        <v>236</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>1430</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
@@ -6284,7 +6246,7 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1384</v>
+        <v>1377</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>19</v>
@@ -6295,30 +6257,30 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B20" t="s">
         <v>218</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>1626</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B21" t="s">
         <v>112</v>
@@ -6330,7 +6292,7 @@
         <v>114</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1406</v>
+        <v>1399</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>115</v>
@@ -6341,7 +6303,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B22" t="s">
         <v>213</v>
@@ -6353,7 +6315,7 @@
         <v>215</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1426</v>
+        <v>1419</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>216</v>
@@ -6364,30 +6326,30 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B23" t="s">
+        <v>222</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>1427</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B24" t="s">
         <v>95</v>
@@ -6399,41 +6361,41 @@
         <v>97</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>98</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1637</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B25" t="s">
+        <v>241</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="E25" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>1431</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B26" t="s">
         <v>46</v>
@@ -6445,7 +6407,7 @@
         <v>48</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1392</v>
+        <v>1385</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>49</v>
@@ -6456,7 +6418,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B27" t="s">
         <v>199</v>
@@ -6468,7 +6430,7 @@
         <v>201</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1424</v>
+        <v>1417</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>202</v>
@@ -6479,7 +6441,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
@@ -6491,18 +6453,18 @@
         <v>35</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1388</v>
+        <v>1381</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B29" t="s">
         <v>51</v>
@@ -6514,18 +6476,18 @@
         <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1393</v>
+        <v>1386</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B30" t="s">
         <v>57</v>
@@ -6537,41 +6499,41 @@
         <v>59</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1395</v>
+        <v>1388</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>1650</v>
+        <v>1642</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1651</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B31" t="s">
+        <v>252</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="E31" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>1438</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B32" t="s">
         <v>80</v>
@@ -6583,7 +6545,7 @@
         <v>82</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>83</v>
@@ -6594,19 +6556,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B33" t="s">
-        <v>1695</v>
+        <v>1686</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1647</v>
+        <v>1639</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>42</v>
@@ -6617,7 +6579,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B34" t="s">
         <v>70</v>
@@ -6629,7 +6591,7 @@
         <v>72</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>73</v>
@@ -6640,30 +6602,30 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B35" t="s">
+        <v>231</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>1429</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B36" t="s">
         <v>37</v>
@@ -6675,18 +6637,18 @@
         <v>39</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1642</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B37" t="s">
         <v>21</v>
@@ -6698,7 +6660,7 @@
         <v>23</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>24</v>
@@ -6709,7 +6671,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B38" t="s">
         <v>175</v>
@@ -6721,7 +6683,7 @@
         <v>177</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1418</v>
+        <v>1411</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
@@ -6732,7 +6694,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
@@ -6744,7 +6706,7 @@
         <v>134</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>135</v>
@@ -6755,30 +6717,30 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B40" t="s">
+        <v>245</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="E40" s="2" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>1639</v>
+        <v>1631</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1638</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B41" t="s">
         <v>117</v>
@@ -6790,7 +6752,7 @@
         <v>119</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>120</v>
@@ -6801,7 +6763,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B42" t="s">
         <v>122</v>
@@ -6813,7 +6775,7 @@
         <v>124</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>125</v>
@@ -6824,30 +6786,30 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B43" t="s">
         <v>104</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1645</v>
+        <v>1637</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>105</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>106</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>1646</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B44" t="s">
         <v>107</v>
@@ -6859,7 +6821,7 @@
         <v>109</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>110</v>
@@ -6870,7 +6832,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B45" t="s">
         <v>30</v>
@@ -6882,41 +6844,41 @@
         <v>32</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1387</v>
+        <v>1380</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1653</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B46" t="s">
+        <v>227</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>1428</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="G46" s="1" t="s">
-        <v>1694</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B47" t="s">
         <v>147</v>
@@ -6928,18 +6890,18 @@
         <v>149</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>150</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B48" t="s">
         <v>26</v>
@@ -6951,18 +6913,18 @@
         <v>28</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1386</v>
+        <v>1379</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1382</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B49" t="s">
         <v>137</v>
@@ -6974,7 +6936,7 @@
         <v>139</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1410</v>
+        <v>1403</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>140</v>
@@ -6985,7 +6947,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B50" t="s">
         <v>151</v>
@@ -6997,7 +6959,7 @@
         <v>153</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1413</v>
+        <v>1406</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>154</v>
@@ -7008,7 +6970,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B51" t="s">
         <v>65</v>
@@ -7020,7 +6982,7 @@
         <v>67</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>68</v>
@@ -7031,30 +6993,30 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B52" t="s">
         <v>54</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1648</v>
+        <v>1640</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>1649</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B53" t="s">
         <v>85</v>
@@ -7066,7 +7028,7 @@
         <v>87</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>88</v>
@@ -7077,7 +7039,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B54" t="s">
         <v>99</v>
@@ -7089,7 +7051,7 @@
         <v>101</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1420</v>
+        <v>1413</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>102</v>
@@ -7100,7 +7062,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="B55" t="s">
         <v>194</v>
@@ -7112,7 +7074,7 @@
         <v>196</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1423</v>
+        <v>1416</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>197</v>
@@ -7123,5234 +7085,5234 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B56" t="s">
+        <v>371</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="E56" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="G56" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>1452</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B57" t="s">
+        <v>334</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="E57" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="G57" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>1445</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B58" t="s">
+        <v>380</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="E58" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="G58" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>1432</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B59" t="s">
+        <v>257</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="E59" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="G59" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>1432</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B60" t="s">
+        <v>292</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="G60" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>1460</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>1440</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B61" t="s">
+        <v>287</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="E61" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="G61" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>1440</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B62" t="s">
+        <v>376</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="E62" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>1453</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G62" s="1" t="s">
-        <v>1659</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B63" t="s">
+        <v>390</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="E63" s="2" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B64" t="s">
+        <v>358</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="E64" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="G64" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>1450</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B65" t="s">
+        <v>324</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="E65" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="G65" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>1444</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B66" t="s">
+        <v>319</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="E66" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="G66" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>1435</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B67" t="s">
+        <v>272</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="E67" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="G67" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>1435</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B68" t="s">
+        <v>385</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="E68" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="G68" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>1435</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B69" t="s">
+        <v>300</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="E69" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="G69" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>1442</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B70" t="s">
+        <v>349</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="E70" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>1448</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="G70" s="1" t="s">
-        <v>1656</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B71" t="s">
+        <v>344</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="E71" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="G71" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>1447</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B72" t="s">
+        <v>353</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="E72" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="G72" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>1449</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B73" t="s">
+        <v>339</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="E73" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="G73" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>1446</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B74" t="s">
+        <v>277</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="E74" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>1436</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B75" t="s">
+        <v>315</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="E75" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>1436</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="G75" s="1" t="s">
-        <v>1641</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B76" t="s">
+        <v>368</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>1657</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>1451</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>372</v>
-      </c>
       <c r="G76" s="1" t="s">
-        <v>1658</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B77" t="s">
+        <v>267</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="E77" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>1434</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B78" t="s">
+        <v>363</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="E78" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="G78" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>1434</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B79" t="s">
+        <v>329</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="E79" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="G79" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>1627</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B80" t="s">
+        <v>305</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="E80" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="G80" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B81" t="s">
+        <v>282</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="E81" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F81" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="G81" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>1439</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B82" t="s">
+        <v>262</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="E82" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F82" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="G82" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>1433</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B83" t="s">
+        <v>310</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="E83" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="G83" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>1443</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B84" t="s">
+        <v>296</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E84" s="2" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B85" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1619</v>
+        <v>1612</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B86" t="s">
-        <v>1698</v>
+        <v>1689</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B87" t="s">
+        <v>828</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="E87" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>1527</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>833</v>
-      </c>
       <c r="G87" s="1" t="s">
-        <v>1692</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B88" t="s">
+        <v>887</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="E88" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="G88" s="1" t="s">
         <v>891</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>1539</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B89" t="s">
+        <v>911</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="E89" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="F89" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="G89" s="1" t="s">
         <v>915</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>1544</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B90" t="s">
+        <v>872</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="E90" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F90" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="G90" s="1" t="s">
         <v>876</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>1536</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B91" t="s">
+        <v>784</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="E91" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="G91" s="1" t="s">
         <v>788</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>1518</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B92" t="s">
+        <v>847</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="E92" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="G92" s="1" t="s">
         <v>851</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>1531</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B93" t="s">
+        <v>789</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="E93" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F93" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="G93" s="1" t="s">
         <v>793</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>1519</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B94" t="s">
+        <v>941</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="E94" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="G94" s="1" t="s">
         <v>945</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>1549</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>946</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B95" t="s">
+        <v>837</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="E95" s="2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="F95" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="G95" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>1529</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B96" t="s">
+        <v>961</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>963</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="E96" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="G96" s="1" t="s">
         <v>965</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>1552</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>966</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B97" t="s">
+        <v>897</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>900</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>901</v>
-      </c>
       <c r="E97" s="2" t="s">
-        <v>1541</v>
+        <v>1534</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>115</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B98" t="s">
+        <v>901</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="E98" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="G98" s="1" t="s">
         <v>905</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>1542</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B99" t="s">
+        <v>867</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="E99" s="2" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F99" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="G99" s="1" t="s">
         <v>871</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>1535</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B100" t="s">
+        <v>799</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="E100" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="G100" s="1" t="s">
         <v>803</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>1521</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B101" t="s">
+        <v>931</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="E101" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="G101" s="1" t="s">
         <v>935</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>1547</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B102" t="s">
+        <v>823</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="E102" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="G102" s="1" t="s">
         <v>827</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>1526</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B103" t="s">
+        <v>769</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="E103" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F103" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="G103" s="1" t="s">
         <v>773</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>1517</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B104" t="s">
+        <v>818</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="E104" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="G104" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>1525</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B105" t="s">
+        <v>764</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="E105" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="F105" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="G105" s="1" t="s">
         <v>768</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>1722</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B106" t="s">
+        <v>774</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="E106" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F106" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="G106" s="1" t="s">
         <v>778</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>1518</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B107" t="s">
+        <v>926</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="E107" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="G107" s="1" t="s">
         <v>930</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>1720</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B108" t="s">
+        <v>759</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="E108" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F108" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="G108" s="1" t="s">
         <v>763</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>1516</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B109" t="s">
+        <v>779</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="E109" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="G109" s="1" t="s">
         <v>783</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>1721</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B110" t="s">
+        <v>877</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="E110" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="F110" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="G110" s="1" t="s">
         <v>881</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>1537</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B111" t="s">
+        <v>808</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="E111" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F111" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="G111" s="1" t="s">
         <v>812</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>1523</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B112" t="s">
+        <v>804</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="E112" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F112" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>1522</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>809</v>
-      </c>
       <c r="G112" s="1" t="s">
-        <v>1691</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B113" t="s">
+        <v>882</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="E113" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="F113" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="G113" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>1538</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B114" t="s">
-        <v>1709</v>
+        <v>1700</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B115" t="s">
-        <v>1710</v>
+        <v>1701</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B116" t="s">
+        <v>936</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="E116" s="2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F116" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="G116" s="1" t="s">
         <v>940</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>1548</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>941</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B117" t="s">
+        <v>749</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="E117" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="G117" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>1514</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B118" t="s">
+        <v>754</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="E118" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F118" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="G118" s="1" t="s">
         <v>758</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>1515</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B119" t="s">
+        <v>956</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="E119" s="2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F119" s="2" t="s">
         <v>959</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="G119" s="1" t="s">
         <v>960</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>1551</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B120" t="s">
+        <v>842</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="E120" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F120" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="G120" s="1" t="s">
         <v>846</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>1530</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B121" t="s">
+        <v>857</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="E121" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="F121" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="G121" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>1533</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B122" t="s">
+        <v>794</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="E122" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F122" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="G122" s="1" t="s">
         <v>798</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>1520</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B123" t="s">
+        <v>892</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="E123" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="G123" s="1" t="s">
         <v>896</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>897</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B124" t="s">
+        <v>862</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="E124" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F124" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="G124" s="1" t="s">
         <v>866</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>1534</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B125" t="s">
+        <v>813</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="E125" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F125" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="G125" s="1" t="s">
         <v>817</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>1524</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B126" t="s">
+        <v>946</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="E126" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F126" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="G126" s="1" t="s">
         <v>950</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>1524</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>951</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B127" t="s">
+        <v>916</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="E127" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F127" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="G127" s="1" t="s">
         <v>920</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>1545</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B128" t="s">
+        <v>832</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="E128" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="G128" s="1" t="s">
         <v>836</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>1528</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B129" t="s">
+        <v>852</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="E129" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="F129" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="G129" s="1" t="s">
         <v>856</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>1532</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B130" t="s">
+        <v>951</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="E130" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F130" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="G130" s="1" t="s">
         <v>955</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>1550</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B131" t="s">
+        <v>921</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="E131" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="G131" s="1" t="s">
         <v>925</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>1546</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>926</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B132" t="s">
-        <v>1706</v>
+        <v>1697</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>1462</v>
+        <v>1455</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B133" t="s">
-        <v>1700</v>
+        <v>1691</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>1607</v>
+        <v>1600</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="B134" t="s">
+        <v>906</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="E134" s="2" t="s">
+        <v>1536</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="G134" s="1" t="s">
         <v>910</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>1543</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B135" t="s">
-        <v>1704</v>
+        <v>1695</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>1611</v>
+        <v>1604</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B136" t="s">
+        <v>717</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="E136" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F136" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>1509</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>722</v>
-      </c>
       <c r="G136" s="1" t="s">
-        <v>1674</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B137" t="s">
-        <v>1718</v>
+        <v>1709</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>1616</v>
+        <v>1609</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B138" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="E138" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F138" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="G138" s="1" t="s">
         <v>1099</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>1577</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B139" t="s">
+        <v>712</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="E139" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F139" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="G139" s="1" t="s">
         <v>716</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>1631</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B140" t="s">
-        <v>1684</v>
+        <v>1675</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>1685</v>
+        <v>1676</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>1689</v>
+        <v>1680</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>1687</v>
+        <v>1678</v>
       </c>
       <c r="G140" t="s">
-        <v>1690</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B141" t="s">
-        <v>1719</v>
+        <v>1710</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B142" t="s">
-        <v>1716</v>
+        <v>1707</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B143" t="s">
+        <v>739</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="E143" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F143" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="G143" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>1513</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B144" t="s">
+        <v>725</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="E144" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F144" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="G144" s="1" t="s">
         <v>729</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>1511</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B145" t="s">
+        <v>721</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="E145" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F145" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="D145" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>1510</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>726</v>
-      </c>
       <c r="G145" s="1" t="s">
-        <v>1675</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B146" t="s">
-        <v>1713</v>
+        <v>1704</v>
       </c>
       <c r="C146" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="G146" s="1" t="s">
         <v>738</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>1485</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B147" t="s">
-        <v>1705</v>
+        <v>1696</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>1610</v>
+        <v>1603</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>1683</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B148" t="s">
+        <v>730</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="E148" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F148" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="G148" s="1" t="s">
         <v>734</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>1512</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B149" t="s">
-        <v>1699</v>
+        <v>1690</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B150" t="s">
-        <v>1697</v>
+        <v>1688</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>1376</v>
+        <v>1369</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>1377</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="B151" t="s">
+        <v>744</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="E151" s="2" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F151" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="G151" s="1" t="s">
         <v>748</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>1632</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B152" t="s">
+        <v>462</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="E152" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F152" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="G152" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>1468</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B153" t="s">
-        <v>1714</v>
+        <v>1705</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>1452</v>
+        <v>1445</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>1682</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B154" t="s">
-        <v>1717</v>
+        <v>1708</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>1490</v>
+        <v>1483</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B155" t="s">
+        <v>413</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="E155" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="G155" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>1629</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B156" t="s">
+        <v>667</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="E156" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="D156" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>1503</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>672</v>
-      </c>
       <c r="G156" s="1" t="s">
-        <v>1671</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B157" t="s">
+        <v>654</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="E157" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F157" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="D157" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>1501</v>
-      </c>
-      <c r="F157" s="2" t="s">
-        <v>659</v>
-      </c>
       <c r="G157" s="1" t="s">
-        <v>1669</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B158" t="s">
+        <v>658</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="E158" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F158" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="G158" s="1" t="s">
         <v>662</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>1502</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B159" t="s">
+        <v>663</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="E159" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F159" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="D159" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>1464</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>668</v>
-      </c>
       <c r="G159" s="1" t="s">
-        <v>1670</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B160" t="s">
+        <v>442</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="E160" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F160" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="G160" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>1464</v>
-      </c>
-      <c r="F160" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B161" t="s">
+        <v>404</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="E161" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F161" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="G161" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>1457</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B162" t="s">
+        <v>394</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="E162" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F162" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="G162" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B163" t="s">
+        <v>452</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="E163" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F163" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="D163" s="1" t="s">
+      <c r="G163" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>1466</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B164" t="s">
+        <v>399</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="E164" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F164" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="G164" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>1456</v>
-      </c>
-      <c r="F164" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="G164" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B165" t="s">
+        <v>671</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="E165" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F165" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="D165" s="1" t="s">
+      <c r="G165" s="1" t="s">
         <v>675</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>1504</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B166" t="s">
+        <v>707</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="E166" s="2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F166" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="D166" s="1" t="s">
+      <c r="G166" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>1630</v>
-      </c>
-      <c r="F166" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B167" t="s">
+        <v>437</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C167" s="1" t="s">
+      <c r="E167" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F167" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="D167" s="1" t="s">
+      <c r="G167" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>1458</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B168" t="s">
+        <v>694</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="G168" s="1" t="s">
         <v>697</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>1508</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B169" t="s">
+        <v>691</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>695</v>
-      </c>
       <c r="E169" s="2" t="s">
-        <v>1508</v>
+        <v>1501</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>1672</v>
+        <v>1663</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B170" t="s">
+        <v>698</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>702</v>
-      </c>
       <c r="E170" s="2" t="s">
-        <v>1508</v>
+        <v>1501</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B171" t="s">
+        <v>702</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="C171" s="1" t="s">
+      <c r="E171" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F171" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="D171" s="1" t="s">
+      <c r="G171" s="1" t="s">
         <v>706</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>1508</v>
-      </c>
-      <c r="F171" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B172" t="s">
-        <v>1715</v>
+        <v>1706</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>1467</v>
+        <v>1460</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B173" t="s">
+        <v>457</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C173" s="1" t="s">
+      <c r="E173" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F173" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D173" s="1" t="s">
+      <c r="G173" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>1467</v>
-      </c>
-      <c r="F173" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B174" t="s">
+        <v>676</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="C174" s="1" t="s">
+      <c r="E174" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F174" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="D174" s="1" t="s">
+      <c r="G174" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>1505</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B175" t="s">
+        <v>447</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="C175" s="1" t="s">
+      <c r="E175" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F175" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="D175" s="1" t="s">
+      <c r="G175" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>1465</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="G175" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B176" t="s">
+        <v>681</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="C176" s="1" t="s">
+      <c r="E176" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="G176" s="1" t="s">
         <v>685</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>1506</v>
-      </c>
-      <c r="F176" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B177" t="s">
+        <v>686</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="C177" s="1" t="s">
+      <c r="E177" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F177" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="D177" s="1" t="s">
+      <c r="G177" s="1" t="s">
         <v>690</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F177" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B178" t="s">
+        <v>409</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C178" s="1" t="s">
+      <c r="E178" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="F178" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="D178" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>1628</v>
-      </c>
-      <c r="F178" s="2" t="s">
-        <v>414</v>
-      </c>
       <c r="G178" s="1" t="s">
-        <v>1660</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B179" t="s">
+        <v>432</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C179" s="1" t="s">
+      <c r="E179" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F179" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="D179" s="1" t="s">
+      <c r="G179" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>1463</v>
-      </c>
-      <c r="F179" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B180" t="s">
+        <v>427</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C180" s="1" t="s">
+      <c r="E180" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="F180" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="G180" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="E180" s="2" t="s">
-        <v>1459</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B181" t="s">
+        <v>423</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C181" s="1" t="s">
+      <c r="E181" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="F181" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D181" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>1459</v>
-      </c>
-      <c r="F181" s="2" t="s">
-        <v>428</v>
-      </c>
       <c r="G181" s="1" t="s">
-        <v>1661</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="B182" t="s">
+        <v>418</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C182" s="1" t="s">
+      <c r="E182" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="F182" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D182" s="1" t="s">
+      <c r="G182" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>1459</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="B183" t="s">
-        <v>1702</v>
+        <v>1693</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="B184" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>1617</v>
+        <v>1610</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
       <c r="B185" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="C185" s="1" t="s">
+      <c r="E185" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F185" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="D185" s="1" t="s">
+      <c r="G185" s="1" t="s">
         <v>1104</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>1578</v>
-      </c>
-      <c r="F185" s="2" t="s">
-        <v>1105</v>
-      </c>
-      <c r="G185" s="1" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
       <c r="B186" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="C186" s="1" t="s">
+      <c r="E186" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F186" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="D186" s="1" t="s">
+      <c r="G186" s="1" t="s">
         <v>1109</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>1579</v>
-      </c>
-      <c r="F186" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
       <c r="B187" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
       <c r="B188" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="C188" s="1" t="s">
+      <c r="E188" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F188" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="D188" s="1" t="s">
+      <c r="G188" s="1" t="s">
         <v>1116</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>1580</v>
-      </c>
-      <c r="F188" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B189" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="E189" s="2" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F189" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="G189" s="1" t="s">
         <v>1172</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F189" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G189" s="1" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B190" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>1179</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>1181</v>
-      </c>
       <c r="E190" s="2" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B191" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="C191" s="1" t="s">
+      <c r="E191" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F191" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="D191" s="1" t="s">
+      <c r="G191" s="1" t="s">
         <v>1145</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="5" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B192" s="6" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D192" s="7" t="s">
         <v>1160</v>
       </c>
-      <c r="C192" s="7" t="s">
+      <c r="E192" s="10" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F192" s="8" t="s">
         <v>1161</v>
       </c>
-      <c r="D192" s="7" t="s">
+      <c r="G192" s="7" t="s">
         <v>1162</v>
-      </c>
-      <c r="E192" s="10" t="s">
-        <v>1585</v>
-      </c>
-      <c r="F192" s="8" t="s">
-        <v>1163</v>
-      </c>
-      <c r="G192" s="7" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B193" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="C193" s="1" t="s">
+      <c r="E193" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F193" s="2" t="s">
         <v>1194</v>
       </c>
-      <c r="D193" s="1" t="s">
+      <c r="G193" s="1" t="s">
         <v>1195</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>1592</v>
-      </c>
-      <c r="F193" s="2" t="s">
-        <v>1196</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B194" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>1148</v>
       </c>
-      <c r="C194" s="1" t="s">
+      <c r="E194" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F194" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="D194" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>1456</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>1151</v>
-      </c>
       <c r="G194" s="1" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B195" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>1165</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="E195" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F195" s="2" t="s">
         <v>1166</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="G195" s="1" t="s">
         <v>1167</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>1586</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>1168</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B196" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="C196" s="1" t="s">
+      <c r="E196" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F196" s="2" t="s">
         <v>1189</v>
       </c>
-      <c r="D196" s="1" t="s">
+      <c r="G196" s="1" t="s">
         <v>1190</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B197" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="C197" s="1" t="s">
+      <c r="E197" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F197" s="2" t="s">
         <v>1184</v>
       </c>
-      <c r="D197" s="1" t="s">
+      <c r="G197" s="1" t="s">
         <v>1185</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>1590</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>1186</v>
-      </c>
-      <c r="G197" s="1" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B198" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="C198" s="1" t="s">
+      <c r="E198" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F198" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="G198" s="1" t="s">
         <v>1154</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>1606</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B199" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>1159</v>
-      </c>
       <c r="E199" s="2" t="s">
-        <v>1621</v>
+        <v>1613</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>1677</v>
+        <v>1668</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B200" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="F200" s="2" t="s">
         <v>1175</v>
       </c>
-      <c r="C200" s="1" t="s">
+      <c r="G200" s="1" t="s">
         <v>1176</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>1588</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>1177</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B201" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="C201" s="1" t="s">
+      <c r="E201" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F201" s="2" t="s">
         <v>1047</v>
       </c>
-      <c r="D201" s="1" t="s">
+      <c r="G201" s="1" t="s">
         <v>1048</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>1566</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="G201" s="1" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B202" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="C202" s="1" t="s">
+      <c r="E202" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F202" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="D202" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>1560</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>1016</v>
-      </c>
       <c r="G202" s="1" t="s">
-        <v>1693</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B203" t="s">
-        <v>1707</v>
+        <v>1698</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>1558</v>
+        <v>1551</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B204" t="s">
+        <v>996</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="C204" s="1" t="s">
+      <c r="E204" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F204" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="D204" s="1" t="s">
+      <c r="G204" s="1" t="s">
         <v>1000</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>1558</v>
-      </c>
-      <c r="F204" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G204" s="1" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B205" t="s">
+        <v>991</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="C205" s="1" t="s">
+      <c r="E205" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F205" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="G205" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>1557</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B206" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="C206" s="1" t="s">
+      <c r="E206" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F206" s="2" t="s">
         <v>1042</v>
       </c>
-      <c r="D206" s="1" t="s">
+      <c r="G206" s="1" t="s">
         <v>1043</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>1565</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B207" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="C207" s="1" t="s">
+      <c r="E207" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F207" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="D207" s="1" t="s">
+      <c r="G207" s="1" t="s">
         <v>1062</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>1569</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B208" t="s">
+        <v>986</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="C208" s="1" t="s">
+      <c r="E208" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F208" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="G208" s="1" t="s">
         <v>990</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>991</v>
-      </c>
-      <c r="G208" s="1" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B209" t="s">
+        <v>966</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="C209" s="1" t="s">
+      <c r="E209" s="2" t="s">
+        <v>1546</v>
+      </c>
+      <c r="F209" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="G209" s="1" t="s">
         <v>970</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>1553</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="G209" s="1" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B210" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="C210" s="1" t="s">
+      <c r="E210" s="2" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F210" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="G210" s="1" t="s">
         <v>1010</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>1559</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G210" s="1" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B211" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="C211" s="1" t="s">
+      <c r="E211" s="2" t="s">
+        <v>1560</v>
+      </c>
+      <c r="F211" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="G211" s="1" t="s">
         <v>1053</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>1567</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>1054</v>
-      </c>
-      <c r="G211" s="1" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B212" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B213" t="s">
+        <v>976</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="C213" s="1" t="s">
+      <c r="E213" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F213" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="G213" s="1" t="s">
         <v>980</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>1440</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="G213" s="1" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B214" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D214" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="C214" s="1" t="s">
+      <c r="E214" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F214" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="G214" s="1" t="s">
         <v>1028</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>1562</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G214" s="1" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B215" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>1024</v>
-      </c>
       <c r="E215" s="2" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B216" t="s">
+        <v>981</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="C216" s="1" t="s">
+      <c r="E216" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F216" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="D216" s="1" t="s">
+      <c r="G216" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="G216" s="1" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B217" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D217" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="C217" s="1" t="s">
+      <c r="E217" s="2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F217" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="G217" s="1" t="s">
         <v>1038</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>1564</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="G217" s="1" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B218" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="C218" s="1" t="s">
+      <c r="E218" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G218" s="1" t="s">
         <v>1057</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>1568</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="G218" s="1" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B219" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>1017</v>
       </c>
-      <c r="C219" s="1" t="s">
+      <c r="E219" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F219" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="G219" s="1" t="s">
         <v>1019</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>1488</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B220" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>1031</v>
       </c>
-      <c r="C220" s="1" t="s">
+      <c r="E220" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F220" s="2" t="s">
         <v>1032</v>
       </c>
-      <c r="D220" s="1" t="s">
+      <c r="G220" s="1" t="s">
         <v>1033</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>1034</v>
-      </c>
-      <c r="G220" s="1" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B221" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="C221" s="1" t="s">
+      <c r="E221" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="D221" s="1" t="s">
+      <c r="G221" s="1" t="s">
         <v>1067</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>1570</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="G221" s="1" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B222" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="C222" s="1" t="s">
+      <c r="E222" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="D222" s="1" t="s">
+      <c r="G222" s="1" t="s">
         <v>1005</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>1554</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G222" s="1" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="B223" t="s">
+        <v>971</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="D223" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="C223" s="1" t="s">
+      <c r="E223" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F223" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="D223" s="1" t="s">
+      <c r="G223" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>1554</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="G223" s="1" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
       <c r="B224" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="B225" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G225" s="1" t="s">
         <v>1245</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>1246</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>1247</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>1603</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>1248</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="B226" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G226" s="1" t="s">
         <v>1225</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D226" s="1" t="s">
-        <v>1227</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>1599</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>1228</v>
-      </c>
-      <c r="G226" s="1" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="B227" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G227" s="1" t="s">
         <v>1230</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>1232</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>1600</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="G227" s="1" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="B228" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G228" s="1" t="s">
         <v>1240</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>1242</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>1602</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="G228" s="1" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="B229" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="B230" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G230" s="1" t="s">
         <v>1235</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>1236</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>1237</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>1601</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G230" s="1" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="B231" t="s">
-        <v>1712</v>
+        <v>1703</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>1325</v>
+        <v>1714</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>1614</v>
+        <v>1607</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="B232" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G232" s="1" t="s">
         <v>1250</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>1251</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>1604</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G232" s="1" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="B233" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G233" s="1" t="s">
         <v>1220</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>1222</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>1598</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G233" s="1" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B234" t="s">
+        <v>567</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="C234" s="1" t="s">
+      <c r="E234" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F234" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="D234" s="1" t="s">
+      <c r="G234" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>1490</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="G234" s="1" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B235" t="s">
+        <v>522</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="C235" s="1" t="s">
+      <c r="E235" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="D235" s="1" t="s">
+      <c r="G235" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>1481</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="G235" s="1" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B236" t="s">
+        <v>600</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="D236" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="C236" s="1" t="s">
+      <c r="E236" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F236" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="D236" s="1" t="s">
+      <c r="G236" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>1470</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="G236" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B237" t="s">
+        <v>472</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C237" s="1" t="s">
+      <c r="E237" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F237" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D237" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>1470</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G237" s="1" t="s">
-        <v>1662</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B238" t="s">
+        <v>639</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D238" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="C238" s="1" t="s">
+      <c r="E238" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F238" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="D238" s="1" t="s">
+      <c r="G238" s="1" t="s">
         <v>643</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="G238" s="1" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B239" t="s">
+        <v>504</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D239" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="C239" s="1" t="s">
+      <c r="E239" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="G239" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>1477</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>1665</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B240" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D240" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="C240" s="1" t="s">
+      <c r="E240" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="D240" s="1" t="s">
+      <c r="G240" s="1" t="s">
         <v>1094</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>1576</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G240" s="1" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B241" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D241" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="C241" s="1" t="s">
+      <c r="E241" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F241" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="D241" s="1" t="s">
+      <c r="G241" s="1" t="s">
         <v>1089</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>1575</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G241" s="1" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B242" t="s">
+        <v>562</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="C242" s="1" t="s">
+      <c r="E242" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F242" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="D242" s="1" t="s">
+      <c r="G242" s="1" t="s">
         <v>566</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="G242" s="1" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B243" t="s">
+        <v>543</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D243" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C243" s="1" t="s">
+      <c r="E243" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F243" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="D243" s="1" t="s">
+      <c r="G243" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>1432</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="G243" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B244" t="s">
+        <v>577</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D244" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="C244" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>581</v>
-      </c>
       <c r="E244" s="2" t="s">
-        <v>1492</v>
+        <v>1485</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B245" t="s">
+        <v>649</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="D245" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="C245" s="1" t="s">
+      <c r="E245" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F245" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="D245" s="1" t="s">
+      <c r="G245" s="1" t="s">
         <v>653</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="G245" s="1" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B246" t="s">
+        <v>553</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C246" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="E246" s="2" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B247" t="s">
+        <v>508</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D247" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="C247" s="1" t="s">
+      <c r="E247" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F247" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="D247" s="1" t="s">
+      <c r="G247" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="G247" s="1" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B248" t="s">
+        <v>527</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C248" s="1" t="s">
+      <c r="E248" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F248" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D248" s="1" t="s">
+      <c r="G248" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>1482</v>
-      </c>
-      <c r="F248" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="G248" s="1" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B249" t="s">
+        <v>532</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="D249" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="C249" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="E249" s="2" t="s">
-        <v>1483</v>
+        <v>1476</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B250" t="s">
+        <v>536</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D250" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C250" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="D250" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="E250" s="2" t="s">
-        <v>1484</v>
+        <v>1477</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1667</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B251" t="s">
+        <v>490</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D251" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C251" s="1" t="s">
+      <c r="E251" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F251" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="D251" s="1" t="s">
+      <c r="G251" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>1474</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="G251" s="1" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B252" t="s">
+        <v>624</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="D252" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="C252" s="1" t="s">
+      <c r="E252" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F252" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="D252" s="1" t="s">
+      <c r="G252" s="1" t="s">
         <v>628</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="G252" s="1" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B253" t="s">
+        <v>595</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="D253" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C253" s="1" t="s">
+      <c r="E253" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F253" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="D253" s="1" t="s">
+      <c r="G253" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="G253" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B254" t="s">
+        <v>476</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C254" s="1" t="s">
+      <c r="E254" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="D254" s="1" t="s">
+      <c r="G254" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>1471</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="G254" s="1" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B255" t="s">
+        <v>517</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D255" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C255" s="1" t="s">
+      <c r="E255" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F255" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="D255" s="1" t="s">
+      <c r="G255" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>1480</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="G255" s="1" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B256" t="s">
+        <v>557</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C256" s="1" t="s">
+      <c r="E256" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F256" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D256" s="1" t="s">
+      <c r="G256" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>1488</v>
-      </c>
-      <c r="F256" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="G256" s="1" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B257" t="s">
+        <v>629</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C257" s="1" t="s">
+      <c r="E257" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F257" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="D257" s="1" t="s">
+      <c r="G257" s="1" t="s">
         <v>633</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>1498</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="G257" s="1" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B258" t="s">
+        <v>634</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="D258" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="C258" s="1" t="s">
+      <c r="E258" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F258" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="D258" s="1" t="s">
+      <c r="G258" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>1453</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="G258" s="1" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B259" t="s">
+        <v>614</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="C259" s="1" t="s">
+      <c r="E259" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F259" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="D259" s="1" t="s">
+      <c r="G259" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>1496</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="G259" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B260" t="s">
+        <v>610</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="D260" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="C260" s="1" t="s">
+      <c r="E260" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G260" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="D260" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>1634</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="G260" s="1" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B261" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D261" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="C261" s="1" t="s">
+      <c r="E261" s="2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F261" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="D261" s="1" t="s">
+      <c r="G261" s="1" t="s">
         <v>1076</v>
-      </c>
-      <c r="E261" s="2" t="s">
-        <v>1572</v>
-      </c>
-      <c r="F261" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="G261" s="1" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B262" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="C262" s="1" t="s">
+      <c r="E262" s="2" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F262" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="D262" s="1" t="s">
+      <c r="G262" s="1" t="s">
         <v>1081</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>1573</v>
-      </c>
-      <c r="F262" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="G262" s="1" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B263" t="s">
+        <v>467</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C263" s="1" t="s">
+      <c r="E263" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F263" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D263" s="1" t="s">
+      <c r="G263" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="E263" s="2" t="s">
-        <v>1469</v>
-      </c>
-      <c r="F263" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="G263" s="1" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B264" t="s">
+        <v>539</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C264" s="1" t="s">
+      <c r="E264" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G264" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="E264" s="2" t="s">
-        <v>1485</v>
-      </c>
-      <c r="F264" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="G264" s="1" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B265" t="s">
+        <v>481</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="C265" s="1" t="s">
+      <c r="E265" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F265" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D265" s="1" t="s">
+      <c r="G265" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="E265" s="2" t="s">
-        <v>1472</v>
-      </c>
-      <c r="F265" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="G265" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="L265" t="s">
-        <v>1360</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B266" t="s">
+        <v>585</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C266" s="1" t="s">
+      <c r="E266" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F266" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="D266" s="1" t="s">
+      <c r="G266" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="E266" s="2" t="s">
-        <v>1434</v>
-      </c>
-      <c r="F266" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="G266" s="1" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B267" t="s">
+        <v>590</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D267" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="C267" s="1" t="s">
+      <c r="E267" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F267" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="D267" s="1" t="s">
+      <c r="G267" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F267" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="G267" s="1" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B268" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="C268" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>1086</v>
-      </c>
       <c r="E268" s="2" t="s">
-        <v>1574</v>
+        <v>1567</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1688</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B269" t="s">
+        <v>619</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="C269" s="1" t="s">
+      <c r="E269" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F269" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="D269" s="1" t="s">
+      <c r="G269" s="1" t="s">
         <v>623</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>1497</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="G269" s="1" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B270" t="s">
+        <v>605</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D270" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C270" s="1" t="s">
+      <c r="E270" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F270" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="D270" s="1" t="s">
+      <c r="G270" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>1633</v>
-      </c>
-      <c r="F270" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="G270" s="1" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B271" t="s">
+        <v>572</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="C271" s="1" t="s">
+      <c r="E271" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F271" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="D271" s="1" t="s">
+      <c r="G271" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>1491</v>
-      </c>
-      <c r="F271" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="G271" s="1" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B272" t="s">
+        <v>513</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D272" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C272" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="D272" s="1" t="s">
-        <v>517</v>
-      </c>
       <c r="E272" s="2" t="s">
-        <v>1479</v>
+        <v>1472</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B273" t="s">
+        <v>548</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D273" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="C273" s="1" t="s">
+      <c r="E273" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F273" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D273" s="1" t="s">
+      <c r="G273" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>1486</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="G273" s="1" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B274" t="s">
+        <v>581</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D274" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="C274" s="1" t="s">
+      <c r="E274" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F274" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="D274" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>1493</v>
-      </c>
-      <c r="F274" s="2" t="s">
-        <v>586</v>
-      </c>
       <c r="G274" s="1" t="s">
-        <v>1668</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B275" t="s">
+        <v>486</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D275" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="C275" s="1" t="s">
+      <c r="E275" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D275" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>1473</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>491</v>
-      </c>
       <c r="G275" s="1" t="s">
-        <v>1663</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B276" t="s">
+        <v>644</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="D276" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="C276" s="1" t="s">
+      <c r="E276" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F276" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="D276" s="1" t="s">
+      <c r="G276" s="1" t="s">
         <v>648</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>1475</v>
-      </c>
-      <c r="F276" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="G276" s="1" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B277" t="s">
+        <v>495</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C277" s="1" t="s">
+      <c r="E277" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F277" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="D277" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="E277" s="2" t="s">
-        <v>1475</v>
-      </c>
-      <c r="F277" s="2" t="s">
-        <v>500</v>
-      </c>
       <c r="G277" s="1" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B278" t="s">
+        <v>499</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D278" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C278" s="1" t="s">
+      <c r="E278" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D278" s="1" t="s">
+      <c r="G278" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>1476</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="G278" s="1" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>1371</v>
+        <v>1364</v>
       </c>
       <c r="B279" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>1595</v>
+        <v>1588</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>1371</v>
+        <v>1364</v>
       </c>
       <c r="B280" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D280" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="C280" s="1" t="s">
+      <c r="E280" s="2" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F280" s="2" t="s">
         <v>1199</v>
       </c>
-      <c r="D280" s="1" t="s">
+      <c r="G280" s="1" t="s">
         <v>1200</v>
-      </c>
-      <c r="E280" s="2" t="s">
-        <v>1593</v>
-      </c>
-      <c r="F280" s="2" t="s">
-        <v>1201</v>
-      </c>
-      <c r="G280" s="1" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>1371</v>
+        <v>1364</v>
       </c>
       <c r="B281" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F281" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G281" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="C281" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>1205</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="G281" s="1" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="B282" t="s">
-        <v>1203</v>
+        <v>1694</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>1356</v>
+        <v>1272</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>1357</v>
+        <v>1273</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>1620</v>
+        <v>1601</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>1358</v>
+        <v>1274</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1359</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>1375</v>
+        <v>1368</v>
       </c>
       <c r="B283" t="s">
-        <v>1703</v>
+        <v>1692</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>1276</v>
@@ -12359,7 +12321,7 @@
         <v>1277</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>1608</v>
+        <v>1602</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>1278</v>
@@ -12370,237 +12332,214 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>1375</v>
+        <v>1368</v>
       </c>
       <c r="B284" t="s">
-        <v>1701</v>
+        <v>1687</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>1280</v>
+        <v>1252</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>1281</v>
+        <v>1253</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>1609</v>
+        <v>1598</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>1282</v>
+        <v>1254</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>1283</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>1375</v>
+        <v>1362</v>
       </c>
       <c r="B285" t="s">
-        <v>1696</v>
+        <v>1117</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>1256</v>
+        <v>1118</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>1257</v>
+        <v>1119</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>1605</v>
+        <v>1574</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>1258</v>
+        <v>1120</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="B286" t="s">
-        <v>1119</v>
+        <v>1339</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>1120</v>
+        <v>1671</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>1121</v>
+        <v>1340</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>1581</v>
+        <v>1467</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>1122</v>
+        <v>1341</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="B287" t="s">
-        <v>1344</v>
+        <v>1132</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>1680</v>
+        <v>1133</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1345</v>
+        <v>1134</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>1474</v>
+        <v>1575</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>1346</v>
+        <v>1135</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1681</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="B288" t="s">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>1135</v>
+        <v>1123</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>1136</v>
+        <v>1124</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>1582</v>
+        <v>1473</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>1137</v>
+        <v>1125</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1138</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="B289" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="B290" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>1131</v>
+        <v>8</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>1488</v>
+        <v>1576</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="B291" t="s">
-        <v>1139</v>
+        <v>1702</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>1140</v>
+        <v>1324</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>8</v>
+        <v>1325</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>1583</v>
+        <v>1608</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>1141</v>
+        <v>153</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>1369</v>
+        <v>1355</v>
       </c>
       <c r="B292" t="s">
-        <v>1711</v>
+        <v>1699</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>1329</v>
+        <v>1295</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>1330</v>
+        <v>1296</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>1615</v>
+        <v>1605</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>153</v>
+        <v>1251</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
-        <v>1362</v>
-      </c>
-      <c r="B293" t="s">
-        <v>1708</v>
-      </c>
-      <c r="C293" s="1" t="s">
-        <v>1299</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>1300</v>
-      </c>
-      <c r="E293" s="2" t="s">
-        <v>1612</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>1255</v>
-      </c>
-      <c r="G293" s="1" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G293">
-    <sortCondition ref="A1:A293"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G292">
+    <sortCondition ref="A1:A292"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
